--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\crwisymposium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C93AADE-5E31-4633-866A-DC2550BAC25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60827B51-D94F-40C0-9BCF-E92630B6615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="365">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -77,16 +77,10 @@
     <t>Event_Start_Date</t>
   </si>
   <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
     <t>Used in Schema.org / JSON-LD</t>
   </si>
   <si>
     <t>Event_End_Date</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
   </si>
   <si>
     <t>Location_Name</t>
@@ -1181,11 +1175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1527,6 +1522,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="91.4140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1565,72 +1564,72 @@
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2">
+        <v>46148</v>
+      </c>
+      <c r="C4" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46150</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C3 A6:C9 A4 C4 A5 C5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1650,117 +1649,117 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="D1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D2" t="s">
         <v>235</v>
       </c>
-      <c r="D2" t="s">
-        <v>237</v>
-      </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -1768,22 +1767,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1791,22 +1790,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -1814,22 +1813,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D8" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -1837,22 +1836,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1860,22 +1859,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -1883,22 +1882,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
@@ -1906,22 +1905,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1929,22 +1928,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E13" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -1952,22 +1951,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F14" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1975,22 +1974,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -1998,22 +1997,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F16" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -2021,22 +2020,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D17" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2044,22 +2043,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C18" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F18" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2067,22 +2066,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
@@ -2090,22 +2089,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E20" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -2113,22 +2112,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -2136,22 +2135,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
@@ -2159,16 +2158,16 @@
         <v>22</v>
       </c>
       <c r="D23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E23" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2176,22 +2175,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2199,22 +2198,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F25" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2222,22 +2221,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F26" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2245,22 +2244,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C27" t="s">
+        <v>291</v>
+      </c>
+      <c r="D27" t="s">
         <v>293</v>
       </c>
-      <c r="D27" t="s">
-        <v>295</v>
-      </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
@@ -2268,16 +2267,16 @@
         <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E28" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -2285,22 +2284,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F29" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -2308,22 +2307,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -2331,22 +2330,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C31" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D31" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2354,22 +2353,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2377,22 +2376,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C33" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E33" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="62" x14ac:dyDescent="0.35">
@@ -2400,22 +2399,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D34" t="s">
+        <v>311</v>
+      </c>
+      <c r="E34" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" t="s">
+        <v>355</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>313</v>
-      </c>
-      <c r="E34" t="s">
-        <v>108</v>
-      </c>
-      <c r="F34" t="s">
-        <v>357</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="46.5" x14ac:dyDescent="0.35">
@@ -2423,22 +2422,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C35" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D35" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
@@ -2446,22 +2445,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C36" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
@@ -2469,22 +2468,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D37" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E37" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F37" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
@@ -2492,22 +2491,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C38" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D38" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F38" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2526,42 +2525,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" t="s">
         <v>154</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>156</v>
-      </c>
-      <c r="E1" t="s">
-        <v>157</v>
-      </c>
-      <c r="F1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D2" t="s">
         <v>159</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>160</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>161</v>
-      </c>
-      <c r="E2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -2579,121 +2578,121 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" t="s">
         <v>165</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D3" t="s">
         <v>169</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>170</v>
-      </c>
-      <c r="D3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" t="s">
         <v>173</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>174</v>
-      </c>
-      <c r="D4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
         <v>177</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>178</v>
-      </c>
-      <c r="D5" t="s">
-        <v>179</v>
-      </c>
-      <c r="E5" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" t="s">
         <v>181</v>
-      </c>
-      <c r="C6" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
+        <v>182</v>
+      </c>
+      <c r="C7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" t="s">
         <v>184</v>
-      </c>
-      <c r="C7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E7" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2711,189 +2710,189 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" t="s">
         <v>187</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>188</v>
-      </c>
-      <c r="D1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" t="s">
         <v>191</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>192</v>
-      </c>
-      <c r="D2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E2" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E3" t="s">
         <v>195</v>
-      </c>
-      <c r="D3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" t="s">
         <v>200</v>
       </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C8" t="s">
         <v>207</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>208</v>
       </c>
-      <c r="C8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D8" t="s">
-        <v>210</v>
-      </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D9" t="s">
         <v>211</v>
       </c>
-      <c r="B9" t="s">
-        <v>208</v>
-      </c>
-      <c r="C9" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" t="s">
-        <v>213</v>
-      </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
         <v>214</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>215</v>
       </c>
-      <c r="C10" t="s">
-        <v>216</v>
-      </c>
-      <c r="D10" t="s">
-        <v>217</v>
-      </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" t="s">
         <v>218</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>219</v>
       </c>
-      <c r="C11" t="s">
-        <v>220</v>
-      </c>
-      <c r="D11" t="s">
-        <v>221</v>
-      </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2919,48 +2918,48 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G2" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2978,86 +2977,86 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" t="s">
         <v>39</v>
-      </c>
-      <c r="C1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" t="s">
         <v>44</v>
       </c>
-      <c r="B3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s">
-        <v>46</v>
-      </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
         <v>50</v>
       </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3079,72 +3078,72 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -3162,42 +3161,42 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
         <v>65</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>66</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>67</v>
-      </c>
-      <c r="E1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" t="s">
         <v>70</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>71</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>72</v>
-      </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3218,62 +3217,62 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" t="s">
         <v>75</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>77</v>
-      </c>
-      <c r="E1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>81</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>82</v>
-      </c>
-      <c r="E2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F2" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>86</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>87</v>
-      </c>
-      <c r="E3" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -3296,13 +3295,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
@@ -3310,86 +3309,86 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" t="s">
         <v>92</v>
-      </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
         <v>95</v>
-      </c>
-      <c r="C3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" t="s">
         <v>98</v>
-      </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" t="s">
         <v>101</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
         <v>104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" t="s">
         <v>107</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3407,100 +3406,100 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D2" t="s">
         <v>113</v>
-      </c>
-      <c r="C2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" t="s">
         <v>116</v>
-      </c>
-      <c r="C3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
         <v>119</v>
-      </c>
-      <c r="C4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" t="s">
         <v>122</v>
-      </c>
-      <c r="C5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
         <v>125</v>
-      </c>
-      <c r="C6" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3518,104 +3517,104 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D1" t="s">
-        <v>132</v>
-      </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
         <v>133</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>134</v>
-      </c>
-      <c r="D2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E2" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D3" t="s">
         <v>137</v>
       </c>
-      <c r="C3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" t="s">
-        <v>139</v>
-      </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" t="s">
         <v>140</v>
       </c>
-      <c r="C4" t="s">
-        <v>141</v>
-      </c>
-      <c r="D4" t="s">
-        <v>142</v>
-      </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
         <v>143</v>
       </c>
-      <c r="C5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" t="s">
-        <v>145</v>
-      </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" t="s">
         <v>146</v>
       </c>
-      <c r="C6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\crwisymposium\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60827B51-D94F-40C0-9BCF-E92630B6615A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C47ED3C8-390A-4245-BBD9-811136D9DA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1180,7 +1180,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1524,7 +1526,7 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.58203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="91.4140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sympweb\crwisymposium-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{718D0075-37F2-4B8E-B7E6-0A43ECE315AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB12A8F-E54E-42BC-BAA6-C544289D7BD7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -1082,18 +1082,9 @@
     <t>Sr. Jincy Maria</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Jincy Arakkal George, a psychologist, holds a degree in Counseling Psychology Major in Clinical counseling from De La Salle University, Manila, Philippines. She also has a diploma in Family Counseling from Loyola School of Theology, Ateneo De Manila University. With her expertise, Dr. Jincy George has served in various leadership roles, including Headmistress and Principal </t>
-  </si>
-  <si>
     <t>Promoting education as a transformative tool for gender equity, ecological consciousness, and social renewal</t>
   </si>
   <si>
-    <t>Dr. Kripanjali Tellis Nayak is a Registered Nurse, Senior Living Consultant, soft skills trainer, and motivational speaker from Mangalore. With qualifications in Nursing, English Literature, and Healthcare Management, she is currently a PhD research scholar in Management. An author of “Mai and I,” she focuses on senior well-being and empowering young people and women through holistic healthcare and leadership developmen</t>
-  </si>
-  <si>
-    <t>Sr. Dr. Helen Mary, of the Sisters of St. Anne, Bangalore, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and certification in OBG ultrasonography. She has served in hospital and rural medical settings and has been Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002. She currently serves as Provincial Councilor and SM Apostolate Coordinator and holds leadership roles in SDFI and CRI.</t>
-  </si>
-  <si>
     <t>SLYI- A faith based model of skill development, social capital and womens ecnomic empowerment in india</t>
   </si>
   <si>
@@ -1109,27 +1100,12 @@
     <t>Radiating Hope: Sacred Presense in virtual spaces</t>
   </si>
   <si>
-    <t>Dedicated and accomplished professional belonging to the Congregation of the Apostolic Carmel, with a strong foundation in formative leadership. Trained in Formators Course, I have successfully served in various capacities, including the pivotal roles of overseeing Aspirants, Novices, and Juniors. My academic journey includes the completion of an MA in English, coupled with a rewarding teaching stint.</t>
-  </si>
-  <si>
-    <t>Dr. Sally John is a senior psychiatrist with over 20 years of experience and currently serves as Head of the Department and Associate Professor of Psychiatry at MGIMS, Sevagram. A graduate of St. John’s Medical College, Bangalore, she works extensively in community, geriatric, and psychosocial mental health. She is the Director of the Jeevadhara Psychospiritual Centre and founder of Treasure, a national mental health initiative for religious sisters.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Sr. Dr. Viji Poulose</t>
   </si>
   <si>
-    <t>Dr. Viji Poulose, of the Franciscan Clarist Congregation, is a paediatrician with extensive clinical experience. She holds an MBBS and DCH and has additional certifications in Sonology, Palliative Care, and Critical Care. She has been serving as Paediatrician and Sonologist at Dayasagar Hospital, Amravati, since 2010, and as Medical Superintendent since 2015, contributing significantly to both patient care and hospital administration.</t>
-  </si>
-  <si>
     <t>Sr. Jyoti Precy Pinto</t>
   </si>
   <si>
-    <t>Sr. Jyoti Precy Pinto, BS, of the Bethany Sisters, Mangalore, has served the congregation for over 55 years and currently serves as Directress of Saanidhya, Bethany Spirituality Centre, Mangaluru. A former Superior General, she has also contributed at national and international levels through CRI, CRWI, AMOR, and UISG. She is widely recognized for her work in women’s empowerment and anti-human trafficking initiatives through AMRAT–Talitha Kum India.</t>
-  </si>
-  <si>
-    <t>Sr. Lismy CMC, of the Congregation of the Mother of Carmel, is a Catholic media missionary from Kerala, popularly known as the “Camera Nun.” She uses filmmaking and digital media for evangelization and social awareness and has produced numerous films highlighting faith, human dignity, and social issues. She is also the recipient of the James Alberione Award for her contributions to Christian media.</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
@@ -1139,12 +1115,6 @@
     <t>Inactive</t>
   </si>
   <si>
-    <t>Sr. Sujata Jena, of the Congregation of the Sacred Hearts of Jesus and Mary, Odisha, is a grassroots activist, freelance journalist, and advocate for the rights of the poor, Dalits, Tribals, women, children, minorities, migrants, and the homeless. She is the recipient of the Best Journalist Award 2021 from the Indian Catholic Press Association and the Salvador Memorial Award 2022 from Bombay Catholic Sobha for her contributions to social justice and human rights</t>
-  </si>
-  <si>
-    <t>Sr. Maria Nirmalini AC is the Superior General of the Apostolic Carmel Congregation since February 2020 and currently serves as President of the Conference of Religious in India (CRWI) and Vice President of CRI. A postgraduate in Education and Commerce, she served for many years as Principal of Carmel Convent School, Delhi, and has received several awards for her contributions to education and human rights. She is a prominent voice for gender equality and represented Indian women religious at the global Synod on Synodality in Rome.</t>
-  </si>
-  <si>
     <t>CMI</t>
   </si>
   <si>
@@ -1448,9 +1418,6 @@
     <t>images/Speakers/Most Rev. Elias Gonsalves.png</t>
   </si>
   <si>
-    <t>Fr. V. Antony Bhyju, CMF, is a Claretian Missionary from the Independent Delegation of Kolkata with significant experience in both initial and ongoing formation. He holds a Licentiate in Formative Psychology from the Pontifical Gregorian University, Rome, integrating psychological insight with spiritual accompaniment in his ministry. He has served as Major Superior and has been actively involved in teaching and animating retreats for religious. Currently, he serves at the General Curia in Rome as Assistant to the General Consultors for Formation and Spirituality, contributing to formation and spiritual renewal within the Congregation.</t>
-  </si>
-  <si>
     <t>Thomas P. Gaunt, SJ.</t>
   </si>
   <si>
@@ -1517,9 +1484,6 @@
     <t>images/Presenters/38.png</t>
   </si>
   <si>
-    <t>Sr. Vijo Arul Selvi M, Research Coordinator at CRWI and Ph.D. scholar in Mathematics, is a Gold Medalist in both B.Ed. and M.Sc. with over a decade of academic leadership as Principal and Vice Principal. She combines international research training at Georgetown University with experience in mathematics education, classroom leadership, and spiritual accompaniment, making her a distinguished voice in both academic and faith‑based settings.</t>
-  </si>
-  <si>
     <t>SJB</t>
   </si>
   <si>
@@ -1598,16 +1562,6 @@
     <t>SJ</t>
   </si>
   <si>
-    <t>Fr. Joye James SJ is a Jesuit priest and renowned social work educator with extensive leadership experience. He served as Professor of Social Work at Loyola College of Social Sciences, Thiruvananthapuram, and has held key roles including Kerala Jesuit Provincial, Asia‑Pacific Adviser of IMCS, Chairman of the Child Welfare Committee (TVM), and Vice‑President of the Indian Social Institute, Bengaluru. He is currently President of ICTA, Kalamassery.</t>
-  </si>
-  <si>
-    <t>Fr. Jerin Peter Palatty is a scholar and priest with advanced studies in philosophy and theology, holding licentiates from Dharmaram Vidya Kshetram and the Pontifical Gregorian University, Rome, where he graduated Summa Cum Laude.
-He has served as Professor, Managing Editor, and currently as Head of the Department of Philosophy at Kristu Jyoti College, Bangalore, and is the author of several books and numerous scholarly articles in philosophy, theology, and spirituality.</t>
-  </si>
-  <si>
-    <t>Dr. Greta D’Souza is Professor and Chair, School of Education, and Associate Director, Global STEM Education Centre at CHRIST (Deemed to be University). Her research focuses on adolescence education, with strong international collaborations and a commitment to developing student leadership, communication, and social impact.</t>
-  </si>
-  <si>
     <t>Dr.Benny</t>
   </si>
   <si>
@@ -1744,6 +1698,52 @@
   </si>
   <si>
     <t>images/Volunteers/Sr, Grecy.jpeg</t>
+  </si>
+  <si>
+    <t>Fr. V. Antony Bhyju, CMF, is a Claretian Missionary with wide experience in initial and ongoing formation, currently serving at the General Curia in Rome as Assistant to the General Consultors for Formation and Spirituality.</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Helen Mary, SABS, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
+  </si>
+  <si>
+    <t>Sr. Lismy CMC, of the Congregation of the Mother of Carmel, is a Catholic media missionary from Kerala, popularly known as the “Camera Nun.” She uses filmmaking and digital media for evangelization and social awareness and has produced numerous films highlighting faith, human dignity, and social issues. She is a recipient of the James Alberione Award for her contributions to Christian media.</t>
+  </si>
+  <si>
+    <t>Grassroots activist and award‑winning journalist, Sr. Sujata Jena is a leading advocate for social justice and human rights among marginalized communities in India.</t>
+  </si>
+  <si>
+    <t>Former Superior General of the Bethany Sisters, Sr. Jyoti Precy Pinto, BS, is Directress of Saanidhya, Bethany Spirituality Centre, and a nationally recognized leader in women’s empowerment and anti‑human trafficking initiatives.</t>
+  </si>
+  <si>
+    <t>Paediatrician with extensive clinical experience, Dr. Viji Poulose serves as Paediatrician, Sonologist, and Medical Superintendent at Dayasagar Hospital, Amravati.</t>
+  </si>
+  <si>
+    <t>Senior psychiatrist with over 20 years of experience, Dr. Sally John is Head of the Department of Psychiatry at MGIMS, Sevagram, and founder of Treasure, a national mental health initiative for religious sisters.</t>
+  </si>
+  <si>
+    <t>Superior General of the Apostolic Carmel Congregation, Sr. Maria Nirmalini AC is President of CRWI and Vice President of CRI, with long experience in education, leadership, and advocacy for gender equality.</t>
+  </si>
+  <si>
+    <t>Research Coordinator at CRWI, Sr. Vijo Arul Selvi M is a Ph.D. scholar in Mathematics and experienced academic leader, combining international research training with education and spiritual accompaniment.</t>
+  </si>
+  <si>
+    <t>Fr. Jerin Peter Palatty is a philosopher‑theologian and priest, currently Head of the Department of Philosophy at Kristu Jyoti College, Bangalore, with advanced studies from Dharmaram Vidya Kshetram and the Pontifical Gregorian University, Rome, and is a published author in philosophy, theology, and spirituality.</t>
+  </si>
+  <si>
+    <t>Dr. Greta D’Souza is Professor and Chair, School of Education, and Associate Director, Global STEM Education Centre at CHRIST (Deemed to be University), with research expertise in adolescence education and a strong focus on student leadership, communication, and social impact.</t>
+  </si>
+  <si>
+    <t>Fr. Joye James SJ is a Jesuit priest and renowned social work educator with extensive leadership experience, currently serving as President of ICTA, Kalamassery, and as a key member of CRWI’s GRC and SRWI initiatives, with long‑standing engagement in social justice and child welfare.</t>
+  </si>
+  <si>
+    <t>Member of the Congregation of the Apostolic Carmel, Sr. Lavina Rodrigues AC is a trained formator with experience accompanying Aspirants, Novices, and Juniors, and holds an MA in English with extensive teaching and formative leadership experience.
+Provide your feedback on BizChat</t>
+  </si>
+  <si>
+    <t>Dr. Kripanjali Tellis Nayak is a Registered Nurse and Senior Living Consultant from Mangalore, currently a PhD research scholar in Management, focusing on senior well‑being and the empowerment of young people and women through holistic healthcare and leadership.</t>
+  </si>
+  <si>
+    <t>Dr. Jincy Arakkal George is a psychologist with a specialization in Clinical Counseling, trained at De La Salle University and Loyola School of Theology, Manila, and has served in key leadership roles including Headmistress and Principal.</t>
   </si>
 </sst>
 </file>
@@ -2365,7 +2365,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2376,7 +2376,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2398,13 +2398,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2421,36 +2421,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B10" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="C10" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D10" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="E10" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="H10" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I10" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="H11" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I11" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -2458,19 +2458,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E12" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="H12" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I12" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -2478,186 +2478,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" t="s">
         <v>373</v>
-      </c>
-      <c r="B14" t="s">
-        <v>382</v>
-      </c>
-      <c r="C14" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>364</v>
+      </c>
+      <c r="B15" t="s">
         <v>374</v>
       </c>
-      <c r="B15" t="s">
-        <v>384</v>
-      </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="B16" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C16" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B17" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="C17" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B18" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C18" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B19" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C19" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C20" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="C21" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="B22" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C22" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C23" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="C24" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C25" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B26" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C26" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B27" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C27" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="B28" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="C28" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="B29" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="C29" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -2701,13 +2701,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="C2" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2715,13 +2715,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E3" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2729,13 +2729,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E4" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2743,13 +2743,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C5" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="E5" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2757,13 +2757,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C6" t="s">
         <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2771,13 +2771,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="C7" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="E7" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2785,13 +2785,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C8" t="s">
         <v>133</v>
       </c>
       <c r="E8" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2799,13 +2799,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="C9" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -2827,6 +2827,7 @@
     <col min="6" max="6" width="36" customWidth="1"/>
     <col min="7" max="7" width="63.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="9" max="9" width="44.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -2852,7 +2853,7 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -2860,7 +2861,7 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="C2" t="s">
         <v>205</v>
@@ -2878,7 +2879,7 @@
         <v>263</v>
       </c>
       <c r="H2" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -2901,10 +2902,10 @@
         <v>133</v>
       </c>
       <c r="H3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
@@ -2924,18 +2925,18 @@
         <v>306</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>324</v>
+        <v>544</v>
       </c>
       <c r="H4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -2950,10 +2951,10 @@
         <v>277</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="H5" t="s">
         <v>333</v>
-      </c>
-      <c r="H5" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -2961,13 +2962,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="C6" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>91</v>
@@ -2979,15 +2980,15 @@
         <v>133</v>
       </c>
       <c r="H6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="139.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C7" t="s">
         <v>204</v>
@@ -3002,10 +3003,10 @@
         <v>309</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>446</v>
+        <v>530</v>
       </c>
       <c r="H7" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3016,7 +3017,7 @@
         <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D8" t="s">
         <v>212</v>
@@ -3031,7 +3032,7 @@
         <v>264</v>
       </c>
       <c r="H8" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3039,7 +3040,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -3057,10 +3058,10 @@
         <v>265</v>
       </c>
       <c r="H9" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3080,10 +3081,10 @@
         <v>281</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>326</v>
+        <v>543</v>
       </c>
       <c r="H10" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3094,7 +3095,7 @@
         <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D11" t="s">
         <v>218</v>
@@ -3109,7 +3110,7 @@
         <v>266</v>
       </c>
       <c r="H11" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -3117,7 +3118,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C12" t="s">
         <v>133</v>
@@ -3135,10 +3136,10 @@
         <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3158,10 +3159,10 @@
         <v>307</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>327</v>
+        <v>531</v>
       </c>
       <c r="H13" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3169,7 +3170,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="C14" t="s">
         <v>227</v>
@@ -3187,15 +3188,15 @@
         <v>266</v>
       </c>
       <c r="H14" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="124" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="C15" t="s">
         <v>203</v>
@@ -3207,13 +3208,13 @@
         <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>344</v>
+        <v>537</v>
       </c>
       <c r="H15" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3221,10 +3222,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="C16" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="D16" t="s">
         <v>229</v>
@@ -3239,7 +3240,7 @@
         <v>267</v>
       </c>
       <c r="H16" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3247,13 +3248,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="C17" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D17" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E17" t="s">
         <v>91</v>
@@ -3262,10 +3263,10 @@
         <v>286</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="H17" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3276,7 +3277,7 @@
         <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
         <v>230</v>
@@ -3291,7 +3292,7 @@
         <v>268</v>
       </c>
       <c r="H18" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3302,7 +3303,7 @@
         <v>224</v>
       </c>
       <c r="C19" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="D19" t="s">
         <v>231</v>
@@ -3317,10 +3318,10 @@
         <v>269</v>
       </c>
       <c r="H19" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3328,7 +3329,7 @@
         <v>232</v>
       </c>
       <c r="C20" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="D20" t="s">
         <v>236</v>
@@ -3340,10 +3341,10 @@
         <v>289</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>334</v>
+        <v>536</v>
       </c>
       <c r="H20" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -3369,15 +3370,15 @@
         <v>133</v>
       </c>
       <c r="H21" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C22" t="s">
         <v>225</v>
@@ -3392,10 +3393,10 @@
         <v>291</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>336</v>
+        <v>535</v>
       </c>
       <c r="H22" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3403,7 +3404,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>133</v>
@@ -3418,7 +3419,7 @@
         <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3438,13 +3439,13 @@
         <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3455,7 +3456,7 @@
         <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="D25" t="s">
         <v>240</v>
@@ -3470,7 +3471,7 @@
         <v>271</v>
       </c>
       <c r="H25" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3496,7 +3497,7 @@
         <v>272</v>
       </c>
       <c r="H26" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -3504,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D27" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
@@ -3522,7 +3523,7 @@
         <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -3530,7 +3531,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>133</v>
@@ -3542,7 +3543,7 @@
         <v>133</v>
       </c>
       <c r="H28" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -3550,7 +3551,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>133</v>
@@ -3562,15 +3563,15 @@
         <v>133</v>
       </c>
       <c r="H29" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C30" t="s">
         <v>246</v>
@@ -3582,16 +3583,16 @@
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>338</v>
+        <v>534</v>
       </c>
       <c r="H30" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3611,10 +3612,10 @@
         <v>298</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>343</v>
+        <v>533</v>
       </c>
       <c r="H31" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3634,13 +3635,13 @@
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>273</v>
       </c>
       <c r="H32" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3666,7 +3667,7 @@
         <v>274</v>
       </c>
       <c r="H33" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3674,13 +3675,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C34" t="s">
         <v>258</v>
       </c>
       <c r="D34" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E34" t="s">
         <v>104</v>
@@ -3692,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="H34" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3700,7 +3701,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C35" t="s">
         <v>259</v>
@@ -3718,7 +3719,7 @@
         <v>275</v>
       </c>
       <c r="H35" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
@@ -3726,7 +3727,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C36" t="s">
         <v>133</v>
@@ -3741,7 +3742,7 @@
         <v>133</v>
       </c>
       <c r="H36" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -3764,10 +3765,10 @@
         <v>303</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>339</v>
+        <v>532</v>
       </c>
       <c r="H37" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3781,7 +3782,7 @@
         <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E38" t="s">
         <v>104</v>
@@ -3793,85 +3794,85 @@
         <v>308</v>
       </c>
       <c r="H38" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C39" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="D39" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="E39" t="s">
         <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>469</v>
+        <v>538</v>
       </c>
       <c r="H39" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="124" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>497</v>
+        <v>539</v>
       </c>
       <c r="H40" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C41" t="s">
         <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E41" t="s">
         <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>498</v>
+        <v>540</v>
       </c>
       <c r="H41" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -3879,25 +3880,25 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="C42" t="s">
         <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E42" t="s">
         <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -3905,51 +3906,51 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="C43" t="s">
         <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E43" t="s">
         <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="C44" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="D44" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E44" t="s">
         <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>496</v>
+        <v>541</v>
       </c>
       <c r="H44" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -3957,25 +3958,25 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="E45" t="s">
         <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +3984,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G1 A2:A5 E2 G3 G6 A1:D1 F1" numberStoredAsText="1"/>
+    <ignoredError sqref="G1 A2:A5 E2 A1:D1 F1" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -4313,7 +4314,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4324,7 +4325,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -4338,7 +4339,7 @@
         <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="D4" t="s">
         <v>294</v>
@@ -4352,7 +4353,7 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D5" t="s">
         <v>285</v>
@@ -4366,7 +4367,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D6" t="s">
         <v>280</v>
@@ -4377,13 +4378,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D7" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4391,13 +4392,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="C8" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D8" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4405,13 +4406,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D9" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4419,13 +4420,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="C10" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D10" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4433,13 +4434,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="C11" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4447,13 +4448,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="C12" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D12" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4461,18 +4462,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C13" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="D13" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4480,13 +4481,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C15" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D15" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -4494,13 +4495,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="C16" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D16" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4508,13 +4509,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="C17" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D17" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4522,13 +4523,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="C18" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D18" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4536,13 +4537,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="C19" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D19" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4550,13 +4551,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="C20" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D20" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4564,13 +4565,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="C21" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D21" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4578,13 +4579,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C22" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4592,13 +4593,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="C23" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D23" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4606,13 +4607,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="C24" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D24" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4620,13 +4621,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="C25" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D25" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4634,13 +4635,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="C26" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D26" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4648,13 +4649,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
+        <v>498</v>
+      </c>
+      <c r="C27" t="s">
+        <v>427</v>
+      </c>
+      <c r="D27" t="s">
         <v>513</v>
-      </c>
-      <c r="C27" t="s">
-        <v>437</v>
-      </c>
-      <c r="D27" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4662,13 +4663,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="C28" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="D28" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -4851,7 +4852,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5538,16 +5539,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D2" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E2" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5555,16 +5556,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C3" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D3" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E3" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5572,16 +5573,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D4" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E4" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5589,16 +5590,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="D5" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E5" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5609,13 +5610,13 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="D6" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E6" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5623,16 +5624,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D7" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E7" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5640,16 +5641,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E8" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5657,16 +5658,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="C9" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="D9" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E9" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5674,16 +5675,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
+        <v>394</v>
+      </c>
+      <c r="C10" t="s">
+        <v>464</v>
+      </c>
+      <c r="D10" t="s">
+        <v>432</v>
+      </c>
+      <c r="E10" t="s">
         <v>404</v>
-      </c>
-      <c r="C10" t="s">
-        <v>476</v>
-      </c>
-      <c r="D10" t="s">
-        <v>442</v>
-      </c>
-      <c r="E10" t="s">
-        <v>414</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sympweb\crwisymposium-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C047BF89-6150-4A44-B731-66EDE049307C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="548">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -1550,9 +1550,6 @@
     <t xml:space="preserve">Sr. Dr. Mary Paul </t>
   </si>
   <si>
-    <t>Dr. Alphonsa K. K.</t>
-  </si>
-  <si>
     <t>Fr. Dr. Sajith Cyriac, SSP</t>
   </si>
   <si>
@@ -1725,9 +1722,6 @@
   </si>
   <si>
     <t>Research Coordinator at CRWI, Sr. Vijo Arul Selvi M is a Ph.D. scholar in Mathematics and experienced academic leader, combining international research training with education and spiritual accompaniment.</t>
-  </si>
-  <si>
-    <t>Fr. Jerin Peter Palatty is a philosopher‑theologian and priest, currently Head of the Department of Philosophy at Kristu Jyoti College, Bangalore, with advanced studies from Dharmaram Vidya Kshetram and the Pontifical Gregorian University, Rome, and is a published author in philosophy, theology, and spirituality.</t>
   </si>
   <si>
     <t>Dr. Greta D’Souza is Professor and Chair, School of Education, and Associate Director, Global STEM Education Centre at CHRIST (Deemed to be University), with research expertise in adolescence education and a strong focus on student leadership, communication, and social impact.</t>
@@ -1744,6 +1738,21 @@
   </si>
   <si>
     <t>Dr. Jincy Arakkal George is a psychologist with a specialization in Clinical Counseling, trained at De La Salle University and Loyola School of Theology, Manila, and has served in key leadership roles including Headmistress and Principal.</t>
+  </si>
+  <si>
+    <t>Fr. Jerin Peter Palatty is a philosopher‑theologian and priest, serving as Head of the Department of Philosophy at Kristu Jyoti College, Bangalore, with advanced studies from Dharmaram Vidya Kshetram and the Pontifical Gregorian University, Rome, and is a published author in philosophy, theology, and spirituality.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Associate CARA, Vietnam  </t>
+  </si>
+  <si>
+    <t>Sr. Dr. Alphonsa K. K.</t>
+  </si>
+  <si>
+    <t>Research Associate</t>
+  </si>
+  <si>
+    <t>images/Speakers/Bibina.jpg</t>
   </si>
 </sst>
 </file>
@@ -2643,7 +2652,7 @@
         <v>357</v>
       </c>
       <c r="B28" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C28" t="s">
         <v>358</v>
@@ -2654,7 +2663,7 @@
         <v>359</v>
       </c>
       <c r="B29" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C29" t="s">
         <v>360</v>
@@ -2760,7 +2769,7 @@
         <v>452</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>544</v>
       </c>
       <c r="E6" t="s">
         <v>439</v>
@@ -2788,10 +2797,10 @@
         <v>441</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>546</v>
       </c>
       <c r="E8" t="s">
-        <v>428</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2925,7 +2934,7 @@
         <v>306</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H4" t="s">
         <v>333</v>
@@ -2951,7 +2960,7 @@
         <v>277</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="H5" t="s">
         <v>333</v>
@@ -3003,7 +3012,7 @@
         <v>309</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H7" t="s">
         <v>333</v>
@@ -3081,7 +3090,7 @@
         <v>281</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="H10" t="s">
         <v>333</v>
@@ -3159,7 +3168,7 @@
         <v>307</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H13" t="s">
         <v>333</v>
@@ -3170,7 +3179,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>480</v>
+        <v>545</v>
       </c>
       <c r="C14" t="s">
         <v>227</v>
@@ -3211,7 +3220,7 @@
         <v>416</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H15" t="s">
         <v>333</v>
@@ -3341,7 +3350,7 @@
         <v>289</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H20" t="s">
         <v>333</v>
@@ -3393,7 +3402,7 @@
         <v>291</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H22" t="s">
         <v>333</v>
@@ -3583,10 +3592,10 @@
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H30" t="s">
         <v>333</v>
@@ -3612,7 +3621,7 @@
         <v>298</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H31" t="s">
         <v>333</v>
@@ -3701,7 +3710,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C35" t="s">
         <v>259</v>
@@ -3765,7 +3774,7 @@
         <v>303</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H37" t="s">
         <v>333</v>
@@ -3817,7 +3826,7 @@
         <v>457</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H39" t="s">
         <v>333</v>
@@ -3840,10 +3849,10 @@
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="H40" t="s">
         <v>333</v>
@@ -3866,10 +3875,10 @@
         <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="H41" t="s">
         <v>333</v>
@@ -3880,7 +3889,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C42" t="s">
         <v>133</v>
@@ -3906,7 +3915,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C43" t="s">
         <v>133</v>
@@ -3932,10 +3941,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>481</v>
+      </c>
+      <c r="C44" t="s">
         <v>482</v>
-      </c>
-      <c r="C44" t="s">
-        <v>483</v>
       </c>
       <c r="D44" t="s">
         <v>466</v>
@@ -3944,10 +3953,10 @@
         <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="H44" t="s">
         <v>333</v>
@@ -3958,7 +3967,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
@@ -4392,13 +4401,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
         <v>423</v>
       </c>
       <c r="D8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4412,7 +4421,7 @@
         <v>423</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4426,7 +4435,7 @@
         <v>423</v>
       </c>
       <c r="D10" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4440,7 +4449,7 @@
         <v>423</v>
       </c>
       <c r="D11" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4448,13 +4457,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C12" t="s">
         <v>423</v>
       </c>
       <c r="D12" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4468,7 +4477,7 @@
         <v>423</v>
       </c>
       <c r="D13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -4481,13 +4490,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C15" t="s">
         <v>427</v>
       </c>
       <c r="D15" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -4495,13 +4504,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C16" t="s">
         <v>427</v>
       </c>
       <c r="D16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4509,13 +4518,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C17" t="s">
         <v>427</v>
       </c>
       <c r="D17" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4523,13 +4532,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C18" t="s">
         <v>427</v>
       </c>
       <c r="D18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4537,13 +4546,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C19" t="s">
         <v>427</v>
       </c>
       <c r="D19" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4551,13 +4560,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C20" t="s">
         <v>427</v>
       </c>
       <c r="D20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4565,13 +4574,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C21" t="s">
         <v>427</v>
       </c>
       <c r="D21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4579,13 +4588,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C22" t="s">
         <v>427</v>
       </c>
       <c r="D22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4593,13 +4602,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C23" t="s">
         <v>427</v>
       </c>
       <c r="D23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4607,13 +4616,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C24" t="s">
         <v>427</v>
       </c>
       <c r="D24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4621,13 +4630,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C25" t="s">
         <v>427</v>
       </c>
       <c r="D25" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4635,13 +4644,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C26" t="s">
         <v>427</v>
       </c>
       <c r="D26" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4649,13 +4658,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C27" t="s">
         <v>427</v>
       </c>
       <c r="D27" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4663,13 +4672,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C28" t="s">
         <v>427</v>
       </c>
       <c r="D28" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -4852,7 +4861,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C047BF89-6150-4A44-B731-66EDE049307C}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AA5F9-83BE-4C46-89CD-79D0F6FE2D3F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="547">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -944,9 +944,6 @@
     <t>images/Presenters/4.jpg</t>
   </si>
   <si>
-    <t>images/Presenters/5.jpg</t>
-  </si>
-  <si>
     <t>images/Presenters/7.jpg</t>
   </si>
   <si>
@@ -1553,19 +1550,10 @@
     <t>Fr. Dr. Sajith Cyriac, SSP</t>
   </si>
   <si>
-    <t>Fr. Joye James</t>
-  </si>
-  <si>
     <t>SJ</t>
   </si>
   <si>
     <t>Dr.Benny</t>
-  </si>
-  <si>
-    <t>Dr. Fr.Mathew</t>
-  </si>
-  <si>
-    <t>Dr. Fr. Emanuel</t>
   </si>
   <si>
     <t>images/Presenters/modrators/Jerin.jpg</t>
@@ -1753,6 +1741,15 @@
   </si>
   <si>
     <t>images/Speakers/Bibina.jpg</t>
+  </si>
+  <si>
+    <t>Dr. Fr. Dominic</t>
+  </si>
+  <si>
+    <t>Dr. Fr. Joye James</t>
+  </si>
+  <si>
+    <t>images/Presenters/5.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2371,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2385,7 +2382,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2407,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>0</v>
@@ -2422,7 +2419,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2430,36 +2427,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>444</v>
+      </c>
+      <c r="B10" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E10" t="s">
         <v>445</v>
       </c>
-      <c r="B10" t="s">
-        <v>449</v>
-      </c>
-      <c r="C10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>333</v>
       </c>
-      <c r="E10" t="s">
-        <v>446</v>
-      </c>
-      <c r="H10" t="s">
-        <v>334</v>
-      </c>
       <c r="I10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -2467,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>344</v>
-      </c>
       <c r="E12" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -2487,186 +2484,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>369</v>
+      </c>
+      <c r="C13" t="s">
         <v>370</v>
-      </c>
-      <c r="C13" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B14" t="s">
+        <v>371</v>
+      </c>
+      <c r="C14" t="s">
         <v>372</v>
-      </c>
-      <c r="C14" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C15" t="s">
         <v>374</v>
-      </c>
-      <c r="C15" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C16" t="s">
         <v>345</v>
-      </c>
-      <c r="B16" t="s">
-        <v>376</v>
-      </c>
-      <c r="C16" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>354</v>
+      </c>
+      <c r="B17" t="s">
+        <v>391</v>
+      </c>
+      <c r="C17" t="s">
         <v>355</v>
-      </c>
-      <c r="B17" t="s">
-        <v>392</v>
-      </c>
-      <c r="C17" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>350</v>
+      </c>
+      <c r="B18" t="s">
+        <v>376</v>
+      </c>
+      <c r="C18" t="s">
         <v>351</v>
-      </c>
-      <c r="B18" t="s">
-        <v>377</v>
-      </c>
-      <c r="C18" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B19" t="s">
+        <v>377</v>
+      </c>
+      <c r="C19" t="s">
         <v>378</v>
-      </c>
-      <c r="C19" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>352</v>
+      </c>
+      <c r="B20" t="s">
+        <v>379</v>
+      </c>
+      <c r="C20" t="s">
         <v>353</v>
-      </c>
-      <c r="B20" t="s">
-        <v>380</v>
-      </c>
-      <c r="C20" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>346</v>
+      </c>
+      <c r="B21" t="s">
+        <v>380</v>
+      </c>
+      <c r="C21" t="s">
         <v>347</v>
-      </c>
-      <c r="B21" t="s">
-        <v>381</v>
-      </c>
-      <c r="C21" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>348</v>
+      </c>
+      <c r="B22" t="s">
+        <v>381</v>
+      </c>
+      <c r="C22" t="s">
         <v>349</v>
-      </c>
-      <c r="B22" t="s">
-        <v>382</v>
-      </c>
-      <c r="C22" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" t="s">
         <v>383</v>
-      </c>
-      <c r="C23" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" t="s">
+        <v>384</v>
+      </c>
+      <c r="C24" t="s">
         <v>361</v>
-      </c>
-      <c r="B24" t="s">
-        <v>385</v>
-      </c>
-      <c r="C24" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C25" t="s">
         <v>386</v>
-      </c>
-      <c r="C25" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B26" t="s">
+        <v>387</v>
+      </c>
+      <c r="C26" t="s">
         <v>388</v>
-      </c>
-      <c r="C26" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B27" t="s">
+        <v>389</v>
+      </c>
+      <c r="C27" t="s">
         <v>390</v>
-      </c>
-      <c r="C27" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>356</v>
+      </c>
+      <c r="B28" t="s">
+        <v>516</v>
+      </c>
+      <c r="C28" t="s">
         <v>357</v>
-      </c>
-      <c r="B28" t="s">
-        <v>520</v>
-      </c>
-      <c r="C28" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>358</v>
+      </c>
+      <c r="B29" t="s">
+        <v>517</v>
+      </c>
+      <c r="C29" t="s">
         <v>359</v>
-      </c>
-      <c r="B29" t="s">
-        <v>521</v>
-      </c>
-      <c r="C29" t="s">
-        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -2710,13 +2707,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2724,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2738,13 +2735,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>410</v>
+      </c>
+      <c r="C4" t="s">
         <v>411</v>
       </c>
-      <c r="C4" t="s">
-        <v>412</v>
-      </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2752,13 +2749,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" t="s">
         <v>436</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>437</v>
-      </c>
-      <c r="E5" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2766,13 +2763,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C6" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2780,13 +2777,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" t="s">
         <v>453</v>
       </c>
-      <c r="C7" t="s">
-        <v>454</v>
-      </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2794,13 +2791,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C8" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E8" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2808,13 +2805,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E9" t="s">
         <v>443</v>
-      </c>
-      <c r="E9" t="s">
-        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -2825,6 +2822,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2862,15 +2860,15 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C2" t="s">
         <v>205</v>
@@ -2882,16 +2880,16 @@
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>263</v>
       </c>
       <c r="H2" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
@@ -2911,15 +2909,15 @@
         <v>133</v>
       </c>
       <c r="H3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C4" t="s">
         <v>225</v>
@@ -2931,21 +2929,21 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="H4" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -2960,10 +2958,10 @@
         <v>277</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="H5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -2971,33 +2969,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C6" t="s">
+        <v>334</v>
+      </c>
+      <c r="D6" t="s">
         <v>335</v>
-      </c>
-      <c r="D6" t="s">
-        <v>336</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>546</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C7" t="s">
         <v>204</v>
@@ -3009,16 +3007,16 @@
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="H7" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3026,7 +3024,7 @@
         <v>202</v>
       </c>
       <c r="C8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D8" t="s">
         <v>212</v>
@@ -3035,21 +3033,21 @@
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>264</v>
       </c>
       <c r="H8" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C9" t="s">
         <v>225</v>
@@ -3061,16 +3059,16 @@
         <v>97</v>
       </c>
       <c r="F9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>265</v>
       </c>
       <c r="H9" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3087,16 +3085,16 @@
         <v>97</v>
       </c>
       <c r="F10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="H10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3104,7 +3102,7 @@
         <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D11" t="s">
         <v>218</v>
@@ -3113,21 +3111,21 @@
         <v>97</v>
       </c>
       <c r="F11" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>266</v>
       </c>
       <c r="H11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
         <v>133</v>
@@ -3139,16 +3137,16 @@
         <v>97</v>
       </c>
       <c r="F12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H12" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3165,21 +3163,21 @@
         <v>97</v>
       </c>
       <c r="F13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="H13" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C14" t="s">
         <v>227</v>
@@ -3191,13 +3189,13 @@
         <v>97</v>
       </c>
       <c r="F14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>266</v>
       </c>
       <c r="H14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3205,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C15" t="s">
         <v>203</v>
@@ -3217,13 +3215,13 @@
         <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="H15" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3231,10 +3229,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>469</v>
+      </c>
+      <c r="C16" t="s">
         <v>470</v>
-      </c>
-      <c r="C16" t="s">
-        <v>471</v>
       </c>
       <c r="D16" t="s">
         <v>229</v>
@@ -3243,13 +3241,13 @@
         <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>267</v>
       </c>
       <c r="H16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3257,25 +3255,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E17" t="s">
         <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H17" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3286,7 +3284,7 @@
         <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D18" t="s">
         <v>230</v>
@@ -3295,13 +3293,13 @@
         <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>268</v>
       </c>
       <c r="H18" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3312,7 +3310,7 @@
         <v>224</v>
       </c>
       <c r="C19" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D19" t="s">
         <v>231</v>
@@ -3321,16 +3319,16 @@
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>269</v>
       </c>
       <c r="H19" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3338,7 +3336,7 @@
         <v>232</v>
       </c>
       <c r="C20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D20" t="s">
         <v>236</v>
@@ -3347,16 +3345,16 @@
         <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="H20" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3373,21 +3371,21 @@
         <v>94</v>
       </c>
       <c r="F21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C22" t="s">
         <v>225</v>
@@ -3399,21 +3397,21 @@
         <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="H22" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>133</v>
@@ -3422,16 +3420,16 @@
         <v>238</v>
       </c>
       <c r="F23" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H23" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3448,16 +3446,16 @@
         <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>270</v>
       </c>
       <c r="H24" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3465,7 +3463,7 @@
         <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D25" t="s">
         <v>240</v>
@@ -3474,16 +3472,16 @@
         <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>271</v>
       </c>
       <c r="H25" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3500,87 +3498,87 @@
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>272</v>
       </c>
       <c r="H26" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F28" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H28" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F29" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H29" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C30" t="s">
         <v>246</v>
@@ -3592,16 +3590,16 @@
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="H30" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3618,16 +3616,16 @@
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="H31" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3644,16 +3642,16 @@
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>273</v>
       </c>
       <c r="H32" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3670,47 +3668,47 @@
         <v>100</v>
       </c>
       <c r="F33" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>274</v>
       </c>
       <c r="H33" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C34" t="s">
         <v>258</v>
       </c>
       <c r="D34" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E34" t="s">
         <v>104</v>
       </c>
       <c r="F34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>262</v>
       </c>
       <c r="H34" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C35" t="s">
         <v>259</v>
@@ -3722,21 +3720,21 @@
         <v>104</v>
       </c>
       <c r="F35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>275</v>
       </c>
       <c r="H35" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C36" t="s">
         <v>133</v>
@@ -3745,16 +3743,16 @@
         <v>254</v>
       </c>
       <c r="F36" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H36" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="93" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3771,16 +3769,16 @@
         <v>104</v>
       </c>
       <c r="F37" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="H37" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3791,71 +3789,71 @@
         <v>260</v>
       </c>
       <c r="D38" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E38" t="s">
         <v>104</v>
       </c>
       <c r="F38" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H38" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C39" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D39" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E39" t="s">
         <v>88</v>
       </c>
       <c r="F39" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="H39" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E40" t="s">
         <v>88</v>
       </c>
       <c r="F40" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="H40" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3863,133 +3861,139 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C41" t="s">
         <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E41" t="s">
         <v>91</v>
       </c>
       <c r="F41" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="H41" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>485</v>
+        <v>544</v>
       </c>
       <c r="C42" t="s">
         <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E42" t="s">
         <v>104</v>
       </c>
       <c r="F42" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>484</v>
+      <c r="B43" s="11" t="s">
+        <v>545</v>
       </c>
       <c r="C43" t="s">
         <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E43" t="s">
         <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
-        <v>481</v>
+      <c r="B44" s="11" t="s">
+        <v>545</v>
       </c>
       <c r="C44" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D44" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E44" t="s">
         <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="H44" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E45" t="s">
         <v>97</v>
       </c>
       <c r="F45" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E45" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
+  <autoFilter ref="E1:E45" xr:uid="{00000000-0001-0000-0900-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Education"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -4212,13 +4216,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" t="s">
         <v>310</v>
       </c>
-      <c r="C2" t="s">
-        <v>311</v>
-      </c>
       <c r="D2" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4226,13 +4230,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C3" t="s">
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4240,13 +4244,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4254,13 +4258,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C5" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4268,13 +4272,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
         <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4282,13 +4286,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
         <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4323,7 +4327,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4334,7 +4338,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -4345,13 +4349,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4362,10 +4366,10 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4376,10 +4380,10 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4387,13 +4391,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4401,13 +4405,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C8" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4415,13 +4419,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D9" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4429,13 +4433,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4443,13 +4447,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D11" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4457,13 +4461,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D12" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4471,18 +4475,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>421</v>
+      </c>
+      <c r="C13" t="s">
         <v>422</v>
       </c>
-      <c r="C13" t="s">
-        <v>423</v>
-      </c>
       <c r="D13" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4490,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C15" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D15" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -4504,13 +4508,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C16" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D16" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4518,13 +4522,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
+        <v>497</v>
+      </c>
+      <c r="C17" t="s">
+        <v>426</v>
+      </c>
+      <c r="D17" t="s">
         <v>501</v>
-      </c>
-      <c r="C17" t="s">
-        <v>427</v>
-      </c>
-      <c r="D17" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4532,13 +4536,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C18" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D18" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4546,13 +4550,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C19" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D19" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4560,13 +4564,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D20" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4574,13 +4578,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C21" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D21" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4588,13 +4592,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D22" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4602,13 +4606,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D23" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4616,13 +4620,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D24" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4630,13 +4634,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C25" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D25" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4644,13 +4648,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="C26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D26" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4658,13 +4662,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D27" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4672,13 +4676,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C28" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D28" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -4861,7 +4865,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5548,16 +5552,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C2" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D2" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5565,16 +5569,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" t="s">
         <v>398</v>
       </c>
-      <c r="C3" t="s">
-        <v>399</v>
-      </c>
       <c r="D3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5582,16 +5586,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="C4" t="s">
         <v>433</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" t="s">
         <v>434</v>
-      </c>
-      <c r="D4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E4" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5599,16 +5603,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="C5" t="s">
         <v>401</v>
       </c>
-      <c r="C5" t="s">
-        <v>402</v>
-      </c>
       <c r="D5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5619,13 +5623,13 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5633,16 +5637,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5650,16 +5654,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5667,16 +5671,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5684,16 +5688,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{583AA5F9-83BE-4C46-89CD-79D0F6FE2D3F}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D88676A8-7DEE-4B9E-A475-47AE74C7ACAE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1718,10 +1718,6 @@
     <t>Fr. Joye James SJ is a Jesuit priest and renowned social work educator with extensive leadership experience, currently serving as President of ICTA, Kalamassery, and as a key member of CRWI’s GRC and SRWI initiatives, with long‑standing engagement in social justice and child welfare.</t>
   </si>
   <si>
-    <t>Member of the Congregation of the Apostolic Carmel, Sr. Lavina Rodrigues AC is a trained formator with experience accompanying Aspirants, Novices, and Juniors, and holds an MA in English with extensive teaching and formative leadership experience.
-Provide your feedback on BizChat</t>
-  </si>
-  <si>
     <t>Dr. Kripanjali Tellis Nayak is a Registered Nurse and Senior Living Consultant from Mangalore, currently a PhD research scholar in Management, focusing on senior well‑being and the empowerment of young people and women through holistic healthcare and leadership.</t>
   </si>
   <si>
@@ -1750,6 +1746,9 @@
   </si>
   <si>
     <t>images/Presenters/5.jpeg</t>
+  </si>
+  <si>
+    <t>Member of the Congregation of the Apostolic Carmel, Sr. Lavina Rodrigues AC is a trained formator with experience accompanying Aspirants, Novices, and Juniors, and holds an MA in English with extensive teaching and formative leadership experience.</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2765,7 @@
         <v>451</v>
       </c>
       <c r="C6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E6" t="s">
         <v>438</v>
@@ -2794,10 +2793,10 @@
         <v>440</v>
       </c>
       <c r="C8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E8" t="s">
         <v>542</v>
-      </c>
-      <c r="E8" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2822,7 +2821,6 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2863,7 +2861,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>28</v>
       </c>
@@ -2889,7 +2887,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
@@ -2912,7 +2910,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
@@ -2932,13 +2930,13 @@
         <v>305</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H4" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
@@ -2958,7 +2956,7 @@
         <v>277</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="H5" t="s">
         <v>332</v>
@@ -2981,7 +2979,7 @@
         <v>91</v>
       </c>
       <c r="F6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>133</v>
@@ -2990,7 +2988,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -3016,7 +3014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -3042,7 +3040,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -3068,7 +3066,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -3088,13 +3086,13 @@
         <v>280</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H10" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -3120,7 +3118,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -3146,7 +3144,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -3172,12 +3170,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C14" t="s">
         <v>227</v>
@@ -3328,7 +3326,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3354,7 +3352,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3380,7 +3378,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3406,7 +3404,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3429,7 +3427,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3455,7 +3453,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3481,7 +3479,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3507,7 +3505,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3533,7 +3531,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3553,7 +3551,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3573,7 +3571,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3599,7 +3597,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3625,7 +3623,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3651,7 +3649,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3677,7 +3675,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3703,7 +3701,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3729,7 +3727,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3752,7 +3750,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="93" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3778,7 +3776,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3804,7 +3802,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="46.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3830,7 +3828,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="77.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3850,7 +3848,7 @@
         <v>482</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H40" t="s">
         <v>332</v>
@@ -3882,12 +3880,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C42" t="s">
         <v>133</v>
@@ -3908,12 +3906,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C43" t="s">
         <v>133</v>
@@ -3934,12 +3932,12 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="62" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C44" t="s">
         <v>480</v>
@@ -3960,7 +3958,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -3987,13 +3985,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E45" xr:uid="{00000000-0001-0000-0900-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Education"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="E1:E45" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D88676A8-7DEE-4B9E-A475-47AE74C7ACAE}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E678AA4-A905-489F-82E3-5207D6D419EA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="8" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
     <author>Religiouswomen India</author>
   </authors>
   <commentList>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{BF718063-9DB4-4990-8D93-69F27DF27465}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{BF718063-9DB4-4990-8D93-69F27DF27465}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="548">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -740,9 +740,6 @@
     <t>Addressing psychological well-being, intercultural living, and the responsible use of technology</t>
   </si>
   <si>
-    <t>Intercultural and intergenerational community living</t>
-  </si>
-  <si>
     <t>Reimagining structures to integrate spiritual, human, intellectual, and pastoral dimensions.</t>
   </si>
   <si>
@@ -1067,9 +1064,6 @@
     <t>images/Trustees/3.jpg</t>
   </si>
   <si>
-    <t>images/Trustees/4.jpg</t>
-  </si>
-  <si>
     <t>images/Trustees/5.jpg</t>
   </si>
   <si>
@@ -1541,9 +1535,6 @@
     <t>Fr. Dr. Johnson</t>
   </si>
   <si>
-    <t>Fr. V. Antony Bhyju</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr. Dr. Mary Paul </t>
   </si>
   <si>
@@ -1739,9 +1730,6 @@
     <t>images/Speakers/Bibina.jpg</t>
   </si>
   <si>
-    <t>Dr. Fr. Dominic</t>
-  </si>
-  <si>
     <t>Dr. Fr. Joye James</t>
   </si>
   <si>
@@ -1749,6 +1737,22 @@
   </si>
   <si>
     <t>Member of the Congregation of the Apostolic Carmel, Sr. Lavina Rodrigues AC is a trained formator with experience accompanying Aspirants, Novices, and Juniors, and holds an MA in English with extensive teaching and formative leadership experience.</t>
+  </si>
+  <si>
+    <t>Unity in Diversity: A Convergent Walking in a Divergent Context
+A Critical Analysis of Synodal, Inter-Congregational, and Inter-Cultural Formation in Theological Education at Institute Mater Dei (IMD), Goa, India</t>
+  </si>
+  <si>
+    <t>Fr. Augustin  Bhayju</t>
+  </si>
+  <si>
+    <t>Fr. Mathew Abraham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mr. Ronald </t>
+  </si>
+  <si>
+    <t>Logos/Logo 6.jpg</t>
   </si>
 </sst>
 </file>
@@ -1901,6 +1905,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2370,7 +2378,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2381,7 +2389,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2403,13 +2411,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>0</v>
@@ -2418,7 +2426,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2426,36 +2434,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B10" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="H10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I10" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="H11" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I11" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -2463,19 +2471,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="I12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -2483,186 +2491,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C13" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B15" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C15" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C16" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B17" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C17" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B18" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C19" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B20" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C21" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B22" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C22" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C23" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B24" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C24" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B25" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B26" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C26" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B27" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C27" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C28" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B29" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C29" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -2706,13 +2714,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2720,13 +2728,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2734,13 +2742,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2748,13 +2756,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" t="s">
+        <v>434</v>
+      </c>
+      <c r="E5" t="s">
         <v>435</v>
-      </c>
-      <c r="C5" t="s">
-        <v>436</v>
-      </c>
-      <c r="E5" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2762,13 +2770,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2776,13 +2784,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C7" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2790,13 +2798,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E8" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2804,13 +2812,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E9" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -2858,67 +2866,70 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>28</v>
+      <c r="A2" s="3">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>207</v>
+        <v>463</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>304</v>
+        <v>479</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>263</v>
+        <v>535</v>
       </c>
       <c r="H2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>466</v>
       </c>
       <c r="C3" t="s">
-        <v>133</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
+      </c>
+      <c r="D3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>133</v>
+        <v>262</v>
       </c>
       <c r="H3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>43</v>
+      <c r="A4" s="3">
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D4" t="s">
         <v>209</v>
@@ -2927,24 +2938,24 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H4" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="62" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>46</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>473</v>
+        <v>544</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
         <v>210</v>
@@ -2953,143 +2964,143 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>546</v>
+        <v>522</v>
       </c>
       <c r="H5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>476</v>
+      <c r="B6" t="s">
+        <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>457</v>
       </c>
       <c r="D6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>91</v>
+        <v>211</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>545</v>
+        <v>277</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="H6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>211</v>
+        <v>543</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="H7" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>416</v>
       </c>
       <c r="C8" t="s">
-        <v>459</v>
+        <v>422</v>
       </c>
       <c r="D8" t="s">
-        <v>212</v>
+        <v>453</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>278</v>
+        <v>454</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>264</v>
+        <v>530</v>
       </c>
       <c r="H8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>478</v>
+      <c r="B9" s="11" t="s">
+        <v>545</v>
       </c>
       <c r="C9" t="s">
-        <v>225</v>
+        <v>133</v>
       </c>
       <c r="D9" t="s">
-        <v>221</v>
+        <v>463</v>
       </c>
       <c r="E9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>425</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="H9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C10" t="s">
-        <v>206</v>
+        <v>455</v>
       </c>
       <c r="D10" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="H10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3097,103 +3108,103 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="C11" t="s">
-        <v>459</v>
+        <v>215</v>
       </c>
       <c r="D11" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="E11" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>281</v>
+        <v>428</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="H11" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>325</v>
+      <c r="B12" t="s">
+        <v>327</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>133</v>
+        <v>527</v>
       </c>
       <c r="H12" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>526</v>
+        <v>270</v>
       </c>
       <c r="H13" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>540</v>
+      <c r="B14" s="11" t="s">
+        <v>546</v>
       </c>
       <c r="C14" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>222</v>
+        <v>463</v>
       </c>
       <c r="E14" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>283</v>
+        <v>425</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3201,25 +3212,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C15" t="s">
-        <v>203</v>
+        <v>258</v>
       </c>
       <c r="D15" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>415</v>
+        <v>299</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>532</v>
+        <v>274</v>
       </c>
       <c r="H15" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3227,51 +3238,51 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>469</v>
+        <v>324</v>
       </c>
       <c r="C16" t="s">
-        <v>470</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H16" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>461</v>
+        <v>255</v>
       </c>
       <c r="C17" t="s">
-        <v>475</v>
+        <v>226</v>
       </c>
       <c r="D17" t="s">
-        <v>323</v>
+        <v>254</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>471</v>
+        <v>524</v>
       </c>
       <c r="H17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3279,25 +3290,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="C18" t="s">
-        <v>458</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>230</v>
+        <v>325</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="H18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3305,25 +3316,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>465</v>
       </c>
       <c r="C19" t="s">
-        <v>459</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>231</v>
+        <v>463</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>287</v>
+        <v>480</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>269</v>
+        <v>531</v>
       </c>
       <c r="H19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3331,100 +3342,103 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>232</v>
+        <v>472</v>
       </c>
       <c r="C20" t="s">
-        <v>457</v>
+        <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="E20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>288</v>
+        <v>413</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H20" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>206</v>
+      <c r="B21" t="s">
+        <v>467</v>
+      </c>
+      <c r="C21" t="s">
+        <v>468</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="H21" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>329</v>
+      <c r="B22" s="11" t="s">
+        <v>474</v>
       </c>
       <c r="C22" t="s">
-        <v>225</v>
+        <v>332</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
-      </c>
-      <c r="E22" t="s">
-        <v>94</v>
+        <v>333</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>290</v>
+        <v>541</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>530</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>238</v>
+      <c r="B23" t="s">
+        <v>223</v>
+      </c>
+      <c r="C23" t="s">
+        <v>457</v>
+      </c>
+      <c r="D23" t="s">
+        <v>230</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>133</v>
+        <v>268</v>
       </c>
       <c r="H23" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3432,25 +3446,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>234</v>
+        <v>459</v>
       </c>
       <c r="C24" t="s">
-        <v>216</v>
+        <v>473</v>
       </c>
       <c r="D24" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>430</v>
+        <v>284</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>270</v>
+        <v>469</v>
       </c>
       <c r="H24" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3458,117 +3472,129 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="C25" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D25" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H25" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>242</v>
+      <c r="B26" s="11" t="s">
+        <v>540</v>
       </c>
       <c r="C26" t="s">
-        <v>203</v>
+        <v>477</v>
       </c>
       <c r="D26" t="s">
-        <v>249</v>
+        <v>463</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>293</v>
+        <v>481</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>272</v>
+        <v>532</v>
       </c>
       <c r="H26" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>462</v>
+      <c r="B27" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27" t="s">
+        <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>133</v>
+        <v>271</v>
       </c>
       <c r="H27" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>133</v>
+      <c r="B28" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" t="s">
+        <v>245</v>
+      </c>
+      <c r="D28" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" t="s">
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>295</v>
+        <v>506</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>133</v>
+        <v>526</v>
       </c>
       <c r="H28" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>133</v>
+      <c r="B29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C29" t="s">
+        <v>247</v>
+      </c>
+      <c r="D29" t="s">
+        <v>252</v>
+      </c>
+      <c r="E29" t="s">
+        <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>296</v>
+        <v>427</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>133</v>
+        <v>272</v>
       </c>
       <c r="H29" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3576,25 +3602,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>330</v>
+        <v>244</v>
       </c>
       <c r="C30" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="D30" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>509</v>
+        <v>297</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>529</v>
+        <v>273</v>
       </c>
       <c r="H30" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3602,178 +3628,181 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C31" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H31" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" t="s">
-        <v>244</v>
-      </c>
-      <c r="C32" t="s">
-        <v>248</v>
+      <c r="B32" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="D32" t="s">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>429</v>
+        <v>293</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>245</v>
+        <v>478</v>
       </c>
       <c r="C33" t="s">
-        <v>206</v>
+        <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>252</v>
+        <v>463</v>
       </c>
       <c r="E33" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>298</v>
+        <v>425</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>274</v>
+        <v>133</v>
       </c>
       <c r="H33" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>326</v>
+        <v>214</v>
       </c>
       <c r="C34" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="D34" t="s">
-        <v>328</v>
+        <v>219</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>262</v>
+        <v>523</v>
       </c>
       <c r="H34" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>479</v>
+        <v>537</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="D35" t="s">
-        <v>261</v>
+        <v>221</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H35" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>325</v>
+      <c r="B36" t="s">
+        <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>457</v>
       </c>
       <c r="D36" t="s">
-        <v>254</v>
+        <v>217</v>
+      </c>
+      <c r="E36" t="s">
+        <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>133</v>
+        <v>265</v>
       </c>
       <c r="H36" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="93" x14ac:dyDescent="0.35">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>475</v>
       </c>
       <c r="C37" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D37" t="s">
-        <v>255</v>
+        <v>220</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>527</v>
+        <v>264</v>
       </c>
       <c r="H37" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3781,25 +3810,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="C38" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>327</v>
+        <v>216</v>
       </c>
       <c r="E38" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>307</v>
+        <v>533</v>
       </c>
       <c r="H38" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3807,181 +3836,160 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>418</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>424</v>
-      </c>
-      <c r="D39" t="s">
-        <v>455</v>
-      </c>
-      <c r="E39" t="s">
-        <v>88</v>
+        <v>133</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>456</v>
+        <v>275</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>533</v>
+        <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>466</v>
+      <c r="B40" s="6" t="s">
+        <v>323</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>465</v>
+        <v>218</v>
       </c>
       <c r="E40" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>482</v>
+        <v>281</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>538</v>
+        <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" t="s">
-        <v>467</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B41" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D41" t="s">
+        <v>236</v>
+      </c>
+      <c r="E41" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" t="s">
+        <v>288</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D41" t="s">
-        <v>465</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" t="s">
-        <v>483</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>534</v>
-      </c>
       <c r="H41" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B42" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D42" t="s">
-        <v>465</v>
-      </c>
-      <c r="E42" t="s">
-        <v>104</v>
+      <c r="D42" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="F42" t="s">
-        <v>427</v>
+        <v>290</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="B43" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D43" t="s">
-        <v>465</v>
-      </c>
-      <c r="E43" t="s">
-        <v>94</v>
-      </c>
       <c r="F43" t="s">
-        <v>427</v>
+        <v>294</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="62" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="C44" t="s">
-        <v>480</v>
-      </c>
-      <c r="D44" t="s">
-        <v>465</v>
-      </c>
-      <c r="E44" t="s">
-        <v>100</v>
+      <c r="B44" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>484</v>
+        <v>295</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>535</v>
+        <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" t="s">
-        <v>481</v>
+      <c r="B45" s="6" t="s">
+        <v>323</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>465</v>
-      </c>
-      <c r="E45" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="F45" t="s">
-        <v>427</v>
+        <v>300</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -3989,7 +3997,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="G1 A2:A5 E2 A1:D1 F1" numberStoredAsText="1"/>
+    <ignoredError sqref="E3 A1:D1 F1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -4208,13 +4216,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C2" t="s">
         <v>309</v>
       </c>
-      <c r="C2" t="s">
-        <v>310</v>
-      </c>
       <c r="D2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4222,13 +4230,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C3" t="s">
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4236,13 +4244,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4250,13 +4258,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C5" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4264,13 +4272,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C6" t="s">
         <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4278,13 +4286,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C7" t="s">
         <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -4319,7 +4327,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4330,7 +4338,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -4341,13 +4349,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4358,10 +4366,10 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4372,10 +4380,10 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4383,13 +4391,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D7" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4397,13 +4405,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>518</v>
+      </c>
+      <c r="C8" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" t="s">
         <v>521</v>
-      </c>
-      <c r="C8" t="s">
-        <v>422</v>
-      </c>
-      <c r="D8" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4411,13 +4419,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C9" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D9" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4425,13 +4433,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D10" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4439,13 +4447,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>418</v>
+      </c>
+      <c r="C11" t="s">
         <v>420</v>
       </c>
-      <c r="C11" t="s">
-        <v>422</v>
-      </c>
       <c r="D11" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4453,13 +4461,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C12" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D12" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4467,18 +4475,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C13" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4486,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C15" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D15" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -4500,13 +4508,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C16" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D16" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4514,13 +4522,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D17" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4528,13 +4536,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C18" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D18" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4542,13 +4550,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D19" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4556,13 +4564,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D20" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4570,13 +4578,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C21" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D21" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4584,13 +4592,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C22" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D22" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4598,13 +4606,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C23" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D23" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4612,13 +4620,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C24" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D24" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4626,13 +4634,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C25" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D25" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4640,13 +4648,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C26" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D26" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4654,13 +4662,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C27" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D27" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4668,13 +4676,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C28" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D28" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -4857,7 +4865,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -4957,8 +4965,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="27.4140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -5042,6 +5053,20 @@
       </c>
       <c r="D6" t="s">
         <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5544,16 +5569,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5561,16 +5586,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5578,16 +5603,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E4" t="s">
         <v>432</v>
-      </c>
-      <c r="C4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" t="s">
-        <v>431</v>
-      </c>
-      <c r="E4" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5595,16 +5620,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5615,13 +5640,13 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5629,16 +5654,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5646,16 +5671,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D8" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5663,16 +5688,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C9" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E9" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5680,16 +5705,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C10" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D10" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E10" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,30 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E678AA4-A905-489F-82E3-5207D6D419EA}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899542C2-763A-4FAE-919D-044D94BEFCD0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
     <sheet name="Hero_Section" sheetId="2" r:id="rId2"/>
     <sheet name="Collaborator_Logos" sheetId="3" r:id="rId3"/>
     <sheet name="Important_Dates" sheetId="4" r:id="rId4"/>
-    <sheet name="About_Section" sheetId="5" r:id="rId5"/>
-    <sheet name="Thematic_Areas" sheetId="7" r:id="rId6"/>
-    <sheet name="Objectives" sheetId="8" r:id="rId7"/>
-    <sheet name="Leadership_Messages" sheetId="6" r:id="rId8"/>
-    <sheet name="Key_Speakers" sheetId="9" r:id="rId9"/>
-    <sheet name="Development Partners" sheetId="15" r:id="rId10"/>
-    <sheet name="Presenters" sheetId="10" r:id="rId11"/>
-    <sheet name="Call_For_Papers" sheetId="11" r:id="rId12"/>
-    <sheet name="Executive_Council" sheetId="12" r:id="rId13"/>
-    <sheet name="Trustees" sheetId="14" r:id="rId14"/>
-    <sheet name="The Invisible Engines" sheetId="16" r:id="rId15"/>
-    <sheet name="Contacts_And_Footer" sheetId="13" r:id="rId16"/>
+    <sheet name="Time Table" sheetId="17" r:id="rId5"/>
+    <sheet name="About_Section" sheetId="5" r:id="rId6"/>
+    <sheet name="Thematic_Areas" sheetId="7" r:id="rId7"/>
+    <sheet name="Objectives" sheetId="8" r:id="rId8"/>
+    <sheet name="Leadership_Messages" sheetId="6" r:id="rId9"/>
+    <sheet name="Key_Speakers" sheetId="9" r:id="rId10"/>
+    <sheet name="Development Partners" sheetId="15" r:id="rId11"/>
+    <sheet name="Presenters" sheetId="10" r:id="rId12"/>
+    <sheet name="Call_For_Papers" sheetId="11" r:id="rId13"/>
+    <sheet name="Executive_Council" sheetId="12" r:id="rId14"/>
+    <sheet name="Trustees" sheetId="14" r:id="rId15"/>
+    <sheet name="The Invisible Engines" sheetId="16" r:id="rId16"/>
+    <sheet name="Contacts_And_Footer" sheetId="13" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Presenters!$E$1:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Presenters!$E$1:$E$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="622">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -752,9 +753,6 @@
     <t>Dr. Joice Steffi Y</t>
   </si>
   <si>
-    <t>Sr. Helen Mary</t>
-  </si>
-  <si>
     <t>Sister</t>
   </si>
   <si>
@@ -836,12 +834,6 @@
     <t>Sr. Dr. Doris D Souza</t>
   </si>
   <si>
-    <t>Sr. Sujata Jena</t>
-  </si>
-  <si>
-    <t>Sr. Rushila Rebello</t>
-  </si>
-  <si>
     <t>Mrs. Anita Cheria</t>
   </si>
   <si>
@@ -1070,9 +1062,6 @@
     <t>images/Trustees/6.jpg</t>
   </si>
   <si>
-    <t>Sr. Jincy Maria</t>
-  </si>
-  <si>
     <t>Promoting education as a transformative tool for gender equity, ecological consciousness, and social renewal</t>
   </si>
   <si>
@@ -1112,9 +1101,6 @@
     <t>New Education Policy</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. Jane Wakahiu  </t>
-  </si>
-  <si>
     <t xml:space="preserve">Fr. Saju Chackalakkal </t>
   </si>
   <si>
@@ -1289,9 +1275,6 @@
     <t>Ms. Sabrina Wong</t>
   </si>
   <si>
-    <t>Fr. Varghese</t>
-  </si>
-  <si>
     <t>His Eminence Anthony Poola</t>
   </si>
   <si>
@@ -1397,9 +1380,6 @@
     <t>images/Presenters/23.jpg</t>
   </si>
   <si>
-    <t>Message</t>
-  </si>
-  <si>
     <t>Most Rev. Elias Gonsalves</t>
   </si>
   <si>
@@ -1409,9 +1389,6 @@
     <t>images/Speakers/Most Rev. Elias Gonsalves.png</t>
   </si>
   <si>
-    <t>Thomas P. Gaunt, SJ.</t>
-  </si>
-  <si>
     <t>Executive director at CARA</t>
   </si>
   <si>
@@ -1424,9 +1401,6 @@
     <t>images/Speakers/Sr. Cadita Njeri Mukundi.jpg</t>
   </si>
   <si>
-    <t>Sr. Bibiana Munini Ngundo</t>
-  </si>
-  <si>
     <t>Background image for non hero section</t>
   </si>
   <si>
@@ -1457,18 +1431,9 @@
     <t>Spped</t>
   </si>
   <si>
-    <t>Sr. Thu T. Do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Candida   Mukundi </t>
-  </si>
-  <si>
     <t>CERRA</t>
   </si>
   <si>
-    <t>Fr. Luis Fernando Falcó, MsPs.</t>
-  </si>
-  <si>
     <t>A Synodal Path toward Authentic Consecrated Living: Perceived Stress and the Role of Social Support &amp; Accompaniment among Perpetually Professed Sisters in India</t>
   </si>
   <si>
@@ -1502,9 +1467,6 @@
     <t>Moderator</t>
   </si>
   <si>
-    <t>Dr. Fr. Jerin SDB</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dr. Greta D'Souza </t>
   </si>
   <si>
@@ -1532,9 +1494,6 @@
     <t xml:space="preserve">Professor </t>
   </si>
   <si>
-    <t>Fr. Dr. Johnson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr. Dr. Mary Paul </t>
   </si>
   <si>
@@ -1662,9 +1621,6 @@
   </si>
   <si>
     <t>images/Volunteers/Sr. Juli mate.jpeg</t>
-  </si>
-  <si>
-    <t>Sr. Grecy</t>
   </si>
   <si>
     <t>Mr. Arun</t>
@@ -1743,23 +1699,295 @@
 A Critical Analysis of Synodal, Inter-Congregational, and Inter-Cultural Formation in Theological Education at Institute Mater Dei (IMD), Goa, India</t>
   </si>
   <si>
-    <t>Fr. Augustin  Bhayju</t>
-  </si>
-  <si>
-    <t>Fr. Mathew Abraham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Ronald </t>
-  </si>
-  <si>
     <t>Logos/Logo 6.jpg</t>
+  </si>
+  <si>
+    <t>Chief Guest - Cultural Event</t>
+  </si>
+  <si>
+    <t>Special Guest</t>
+  </si>
+  <si>
+    <t>Special Guest/ Celebrant</t>
+  </si>
+  <si>
+    <t>Bishop of Kurnool</t>
+  </si>
+  <si>
+    <t>Chief Guest - Inaugural Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. DJ Margaret </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Maria Nirmalini </t>
+  </si>
+  <si>
+    <t>Most Rev. Johannes Gorantla</t>
+  </si>
+  <si>
+    <t>Executive Council CRWI</t>
+  </si>
+  <si>
+    <t>Sr. Molly Attully</t>
+  </si>
+  <si>
+    <t>Mother General - CCR</t>
+  </si>
+  <si>
+    <t>Guest of Honor</t>
+  </si>
+  <si>
+    <t>Sr. Sheela Nicholas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Dr. Jane Wakahiu  </t>
+  </si>
+  <si>
+    <t>Fr. Dr. Thomas P. Gaunt, SJ.</t>
+  </si>
+  <si>
+    <t>Sr.Dr.  Thu T. Do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr. Dr.Candida   Mukundi </t>
+  </si>
+  <si>
+    <t>Sr. Dr. Bibiana Munini Ngundo</t>
+  </si>
+  <si>
+    <t>Fr. Dr Luis Fernando Falcó, MsPs.</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Jincy Maria</t>
+  </si>
+  <si>
+    <t>Fr. Dr.  Augustin  Bhayju</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Mathew Abraham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Ronald </t>
+  </si>
+  <si>
+    <t>Sr. Adv. Rushila Rebello</t>
+  </si>
+  <si>
+    <t>Sr. Adv. Sujata Jena</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Helen Mary</t>
+  </si>
+  <si>
+    <t>Sr.Stella Zimik</t>
+  </si>
+  <si>
+    <t>Fr.Dr. Varghese K J</t>
+  </si>
+  <si>
+    <t>images/Volunteers/Sr.Stella Zimik.jpeg</t>
+  </si>
+  <si>
+    <t>Sr. Grecy Lily</t>
+  </si>
+  <si>
+    <t>images/Speakers/Most Rev. Johannes Gorantla.jpeg</t>
+  </si>
+  <si>
+    <t>Chairperson</t>
+  </si>
+  <si>
+    <t>images/Speakers/Molly attully.jpeg</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Particulars</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Registration</t>
+  </si>
+  <si>
+    <t>16-00 - 18:15</t>
+  </si>
+  <si>
+    <t>Greet &amp; Meet and Welcome Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.30 - 21.00 </t>
+  </si>
+  <si>
+    <t>Eucharistic Celebration</t>
+  </si>
+  <si>
+    <t>Most Reverend Ivan Pereira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:30 - 07:30 </t>
+  </si>
+  <si>
+    <t>Breakfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:30- 08:30 </t>
+  </si>
+  <si>
+    <t>Inaugural Function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:45 - 10:45 </t>
+  </si>
+  <si>
+    <t>Tea Break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:50 - 11:10 </t>
+  </si>
+  <si>
+    <t>Plenary Session: Research updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11:15 - 13:00</t>
+  </si>
+  <si>
+    <t>Lunch Break</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:00-14.00 </t>
+  </si>
+  <si>
+    <t>Panel Discussion : Religious Women in the 21st Century: Challenges, Opportunities, and New 
+Pathways</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00 - 15:30 </t>
+  </si>
+  <si>
+    <t>Technical Session -  Formation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00 - 17:45 </t>
+  </si>
+  <si>
+    <t>Technical Session -  Health</t>
+  </si>
+  <si>
+    <t>Technical Session -  Social Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catch Up and Connect </t>
+  </si>
+  <si>
+    <t>18:30 - 19:15</t>
+  </si>
+  <si>
+    <t>Dinner</t>
+  </si>
+  <si>
+    <t>19:30 - 20:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most Rev. Elias Gonsalves, </t>
+  </si>
+  <si>
+    <t>06:30 - 07:30</t>
+  </si>
+  <si>
+    <t>07:30 - 08:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Echoes of Hope: Messages </t>
+  </si>
+  <si>
+    <t>08:45 - 09:45</t>
+  </si>
+  <si>
+    <t>Panel Discussion: A Ministry of Care: Addressing Inequality, Resources, and New Pathways in Caring for Elderly Sisters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00 - 11:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:30 - 11:45 </t>
+  </si>
+  <si>
+    <t>Technical Session -  Elderly Care</t>
+  </si>
+  <si>
+    <t>11:45- 13:45</t>
+  </si>
+  <si>
+    <t>Technical Session -  Education</t>
+  </si>
+  <si>
+    <t>Technical Session -  Social Ministry</t>
+  </si>
+  <si>
+    <t>13:45 -14:45</t>
+  </si>
+  <si>
+    <t>Transvergence: Coverging for Trasnformative 
+Renewal (Sharing by the Moderators)</t>
+  </si>
+  <si>
+    <t>14:45 - 16:05</t>
+  </si>
+  <si>
+    <t>Valedictory Function</t>
+  </si>
+  <si>
+    <t>16:05 - 17:00</t>
+  </si>
+  <si>
+    <t>Pilgrim Walk</t>
+  </si>
+  <si>
+    <t>17:00 - 17:30</t>
+  </si>
+  <si>
+    <t>Tea, Talk &amp; Take Off</t>
+  </si>
+  <si>
+    <t>17:30 - 18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESEARCH SYMPOSIUM </t>
+  </si>
+  <si>
+    <t>images/Presenters/39.jpg</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Mathew Abraham is a medical doctor and Catholic priest with extensive leadership in public health. As former Director General of CHAI, he championed compassionate, affordable healthcare for marginalized communities, bringing both medical expertise and moral clarity to symposium discussions.</t>
+  </si>
+  <si>
+    <t>C.Ss.R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dr. Fr. Jerin </t>
+  </si>
+  <si>
+    <t>SDB</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Johnson S. V is an academic leader with a Ph.D. in Education and over two decades of service at Christ College, Bhopal. Recently honored for his contributions to NEP 2020 reforms, he continues to champion holistic education, faculty development, and student empowerment.</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Johnson S V</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
+  </numFmts>
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1827,16 +2055,75 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF2E1A47"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1859,11 +2146,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1890,6 +2231,93 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1905,10 +2333,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2378,7 +2802,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2389,7 +2813,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2411,13 +2835,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>0</v>
@@ -2426,7 +2850,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2434,36 +2858,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B10" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="C10" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E10" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="H10" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I10" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="H11" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I11" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -2471,19 +2895,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="E12" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="H12" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I12" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -2491,186 +2915,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C13" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B14" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C14" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B15" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C15" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B17" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C17" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B18" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C18" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B19" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C19" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B20" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C20" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C21" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B22" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B23" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C23" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B24" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B25" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C25" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B26" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C26" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B27" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C27" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B28" t="s">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C28" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="C29" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -2683,6 +3107,266 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.25" customWidth="1"/>
+    <col min="3" max="3" width="32.75" customWidth="1"/>
+    <col min="4" max="4" width="27.83203125" customWidth="1"/>
+    <col min="486" max="486" width="2.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D3" t="s">
+        <v>532</v>
+      </c>
+      <c r="E3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" t="s">
+        <v>532</v>
+      </c>
+      <c r="E4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="C5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D5" t="s">
+        <v>534</v>
+      </c>
+      <c r="E5" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" t="s">
+        <v>531</v>
+      </c>
+      <c r="E6" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D7" t="s">
+        <v>561</v>
+      </c>
+      <c r="E7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" t="s">
+        <v>401</v>
+      </c>
+      <c r="D8" t="s">
+        <v>541</v>
+      </c>
+      <c r="E8" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" t="s">
+        <v>541</v>
+      </c>
+      <c r="E9" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C10" t="s">
+        <v>399</v>
+      </c>
+      <c r="D10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E10" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B11" t="s">
+        <v>535</v>
+      </c>
+      <c r="C11" t="s">
+        <v>538</v>
+      </c>
+      <c r="D11" t="s">
+        <v>541</v>
+      </c>
+      <c r="E11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>539</v>
+      </c>
+      <c r="C12" t="s">
+        <v>540</v>
+      </c>
+      <c r="D12" t="s">
+        <v>541</v>
+      </c>
+      <c r="E12" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>542</v>
+      </c>
+      <c r="C13" t="s">
+        <v>538</v>
+      </c>
+      <c r="D13" t="s">
+        <v>541</v>
+      </c>
+      <c r="E13" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>386</v>
+      </c>
+      <c r="C14" t="s">
+        <v>449</v>
+      </c>
+      <c r="D14" t="s">
+        <v>541</v>
+      </c>
+      <c r="E14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:E1 A2 A3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F408643-EE4E-4A6C-A3B2-9DA3CE87AD80}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -2714,13 +3398,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>543</v>
       </c>
       <c r="C2" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="E2" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -2728,13 +3412,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C3" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E3" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -2742,13 +3426,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -2756,13 +3440,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>433</v>
+        <v>544</v>
       </c>
       <c r="C5" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="E5" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2770,13 +3454,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>449</v>
+        <v>545</v>
       </c>
       <c r="C6" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="E6" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -2784,13 +3468,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>450</v>
+        <v>546</v>
       </c>
       <c r="C7" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -2798,13 +3482,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>438</v>
+        <v>547</v>
       </c>
       <c r="C8" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="E8" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -2812,13 +3496,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>452</v>
+        <v>548</v>
       </c>
       <c r="C9" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="E9" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -2827,7 +3511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -2866,7 +3550,7 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -2874,33 +3558,33 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>464</v>
+        <v>618</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>619</v>
       </c>
       <c r="D2" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="H2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
-        <v>466</v>
+      <c r="B3" s="44" t="s">
+        <v>453</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -2912,13 +3596,13 @@
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -2926,10 +3610,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>320</v>
+        <v>549</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D4" t="s">
         <v>209</v>
@@ -2938,13 +3622,13 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="H4" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -2952,7 +3636,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -2964,24 +3648,24 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="H5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="44" t="s">
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -2990,13 +3674,13 @@
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3004,181 +3688,181 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="H7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="C8" t="s">
         <v>416</v>
       </c>
-      <c r="C8" t="s">
-        <v>422</v>
-      </c>
       <c r="D8" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="H8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>617</v>
       </c>
       <c r="D9" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>425</v>
+        <v>615</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>133</v>
+        <v>616</v>
       </c>
       <c r="H9" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
-        <v>231</v>
+      <c r="B10" s="44" t="s">
+        <v>230</v>
       </c>
       <c r="C10" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="H10" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
-        <v>233</v>
+      <c r="B11" s="44" t="s">
+        <v>232</v>
       </c>
       <c r="C11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H11" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>327</v>
+      <c r="B12" s="44" t="s">
+        <v>323</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="H12" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>234</v>
+      <c r="B13" s="44" t="s">
+        <v>233</v>
       </c>
       <c r="C13" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="D13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H13" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -3186,129 +3870,129 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="C14" t="s">
         <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>476</v>
+      <c r="B15" s="44" t="s">
+        <v>462</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D15" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H15" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>324</v>
+      <c r="B16" s="44" t="s">
+        <v>320</v>
       </c>
       <c r="C16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D16" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>255</v>
+      <c r="B17" s="44" t="s">
+        <v>252</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D17" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="H17" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" t="s">
         <v>256</v>
       </c>
-      <c r="C18" t="s">
-        <v>259</v>
-      </c>
       <c r="D18" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H18" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3316,129 +4000,129 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>465</v>
+        <v>452</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="H19" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>472</v>
+      <c r="B20" s="44" t="s">
+        <v>459</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="H20" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" t="s">
-        <v>467</v>
+      <c r="B21" s="44" t="s">
+        <v>454</v>
       </c>
       <c r="C21" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="D21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H21" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>474</v>
+        <v>621</v>
       </c>
       <c r="C22" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D22" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>133</v>
+        <v>620</v>
       </c>
       <c r="H22" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" t="s">
-        <v>223</v>
+      <c r="B23" s="44" t="s">
+        <v>222</v>
       </c>
       <c r="C23" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s">
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H23" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3446,51 +4130,51 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="C24" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="D24" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="H24" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>222</v>
+      <c r="B25" s="44" t="s">
+        <v>221</v>
       </c>
       <c r="C25" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="D25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H25" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3498,155 +4182,155 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="C26" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="D26" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="H26" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" t="s">
-        <v>241</v>
+      <c r="B27" s="44" t="s">
+        <v>240</v>
       </c>
       <c r="C27" t="s">
         <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="H27" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>328</v>
+      <c r="B28" s="44" t="s">
+        <v>324</v>
       </c>
       <c r="C28" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="H28" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" t="s">
-        <v>243</v>
+      <c r="B29" s="44" t="s">
+        <v>553</v>
       </c>
       <c r="C29" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D29" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H29" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>244</v>
+      <c r="B30" s="44" t="s">
+        <v>241</v>
       </c>
       <c r="C30" t="s">
         <v>206</v>
       </c>
       <c r="D30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="H30" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" t="s">
-        <v>242</v>
+      <c r="B31" s="44" t="s">
+        <v>554</v>
       </c>
       <c r="C31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D31" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="H31" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -3654,25 +4338,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="D32" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -3680,129 +4364,129 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="C33" t="s">
         <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H33" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>214</v>
+      <c r="B34" s="44" t="s">
+        <v>555</v>
       </c>
       <c r="C34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D34" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E34" t="s">
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="H34" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" t="s">
-        <v>537</v>
+      <c r="B35" s="44" t="s">
+        <v>522</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E35" t="s">
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H35" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="44" t="s">
         <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="D36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E36" t="s">
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H36" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" t="s">
-        <v>475</v>
+      <c r="B37" s="44" t="s">
+        <v>461</v>
       </c>
       <c r="C37" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H37" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3816,19 +4500,19 @@
         <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E38" t="s">
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="H38" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3845,13 +4529,13 @@
         <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -3859,25 +4543,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E40" t="s">
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -3885,25 +4569,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>206</v>
       </c>
       <c r="D41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3911,22 +4595,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F42" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -3934,19 +4618,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -3954,19 +4638,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -3974,22 +4658,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4003,7 +4687,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4056,10 +4740,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="22.9140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -4189,7 +4876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B4301E-B4F1-4F6C-84B3-E69F1BFD510E}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4216,13 +4903,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4230,13 +4917,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C3" t="s">
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4244,13 +4931,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4258,13 +4945,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C5" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4272,13 +4959,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C6" t="s">
         <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4286,13 +4973,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C7" t="s">
         <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4301,9 +4988,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE87D73C-0C6D-4F11-B208-F394024872E3}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.58203125" style="3"/>
@@ -4327,7 +5014,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4338,7 +5025,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -4349,13 +5036,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4366,10 +5053,10 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4380,10 +5067,10 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4391,13 +5078,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C7" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D7" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -4405,13 +5092,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D8" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -4419,13 +5106,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D9" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -4433,13 +5120,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D10" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -4447,13 +5134,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D11" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -4461,13 +5148,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D12" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -4475,18 +5162,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C13" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D13" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -4494,13 +5181,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="C15" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D15" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -4508,13 +5195,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="C16" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D16" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -4522,13 +5209,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D17" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -4536,13 +5223,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="C18" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D18" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -4550,13 +5237,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="C19" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D19" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -4564,13 +5251,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
       <c r="C20" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D20" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -4578,13 +5265,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="C21" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D21" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -4592,13 +5279,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
       <c r="C22" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D22" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -4606,13 +5293,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="C23" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D23" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -4620,13 +5307,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="C24" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D24" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -4634,13 +5321,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="C25" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D25" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -4648,13 +5335,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>491</v>
+        <v>556</v>
       </c>
       <c r="C26" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D26" t="s">
-        <v>503</v>
+        <v>558</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -4662,13 +5349,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="C27" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D27" t="s">
-        <v>505</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -4676,13 +5363,27 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C28" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D28" t="s">
-        <v>504</v>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>481</v>
+      </c>
+      <c r="C29" t="s">
+        <v>418</v>
+      </c>
+      <c r="D29" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -4692,7 +5393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4865,7 +5566,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5060,7 +5761,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -5165,6 +5866,322 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BEC9B0-00AF-4DEF-B451-AE6CF232DD3E}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.08203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="12"/>
+      <c r="B1" s="13" t="s">
+        <v>614</v>
+      </c>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20" t="s">
+        <v>568</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>46149</v>
+      </c>
+      <c r="B5" s="23" t="s">
+        <v>570</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20" t="s">
+        <v>573</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="25" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20" t="s">
+        <v>575</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="22" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="20"/>
+      <c r="B8" s="20" t="s">
+        <v>577</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20" t="s">
+        <v>579</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="26" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20" t="s">
+        <v>581</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="26" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="20"/>
+      <c r="B11" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="26" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12" t="s">
+        <v>585</v>
+      </c>
+      <c r="C12" s="12"/>
+      <c r="D12" s="28" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="C13" s="12"/>
+      <c r="D13" s="28" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12" t="s">
+        <v>588</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="28" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="15">
+        <v>46150</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>570</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>593</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="32" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="12"/>
+      <c r="B19" s="36" t="s">
+        <v>596</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="37" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="12"/>
+      <c r="B20" s="38" t="s">
+        <v>598</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="40" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="12"/>
+      <c r="B21" s="41" t="s">
+        <v>577</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12" t="s">
+        <v>601</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="42" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="42" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12" t="s">
+        <v>604</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="42" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="42" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A26" s="12"/>
+      <c r="B26" s="43" t="s">
+        <v>606</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="28" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="42" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="28" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="28" t="s">
+        <v>613</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5227,7 +6244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5343,7 +6360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5459,7 +6476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5534,195 +6551,4 @@
     <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="2.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="27.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="C3" t="s">
-        <v>396</v>
-      </c>
-      <c r="D3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="C4" t="s">
-        <v>431</v>
-      </c>
-      <c r="D4" t="s">
-        <v>429</v>
-      </c>
-      <c r="E4" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="C5" t="s">
-        <v>399</v>
-      </c>
-      <c r="D5" t="s">
-        <v>429</v>
-      </c>
-      <c r="E5" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" t="s">
-        <v>462</v>
-      </c>
-      <c r="D6" t="s">
-        <v>429</v>
-      </c>
-      <c r="E6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C8" t="s">
-        <v>406</v>
-      </c>
-      <c r="D8" t="s">
-        <v>429</v>
-      </c>
-      <c r="E8" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" t="s">
-        <v>393</v>
-      </c>
-      <c r="C9" t="s">
-        <v>405</v>
-      </c>
-      <c r="D9" t="s">
-        <v>429</v>
-      </c>
-      <c r="E9" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B10" t="s">
-        <v>391</v>
-      </c>
-      <c r="C10" t="s">
-        <v>461</v>
-      </c>
-      <c r="D10" t="s">
-        <v>429</v>
-      </c>
-      <c r="E10" t="s">
-        <v>401</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:E1 A2 A3" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899542C2-763A-4FAE-919D-044D94BEFCD0}"/>
+  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D62CD29-499E-4104-8244-CD7A3772FD88}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -18,21 +18,22 @@
     <sheet name="Collaborator_Logos" sheetId="3" r:id="rId3"/>
     <sheet name="Important_Dates" sheetId="4" r:id="rId4"/>
     <sheet name="Time Table" sheetId="17" r:id="rId5"/>
-    <sheet name="About_Section" sheetId="5" r:id="rId6"/>
-    <sheet name="Thematic_Areas" sheetId="7" r:id="rId7"/>
-    <sheet name="Objectives" sheetId="8" r:id="rId8"/>
-    <sheet name="Leadership_Messages" sheetId="6" r:id="rId9"/>
-    <sheet name="Key_Speakers" sheetId="9" r:id="rId10"/>
-    <sheet name="Development Partners" sheetId="15" r:id="rId11"/>
-    <sheet name="Presenters" sheetId="10" r:id="rId12"/>
-    <sheet name="Call_For_Papers" sheetId="11" r:id="rId13"/>
-    <sheet name="Executive_Council" sheetId="12" r:id="rId14"/>
-    <sheet name="Trustees" sheetId="14" r:id="rId15"/>
-    <sheet name="The Invisible Engines" sheetId="16" r:id="rId16"/>
-    <sheet name="Contacts_And_Footer" sheetId="13" r:id="rId17"/>
+    <sheet name="Cultural" sheetId="18" r:id="rId6"/>
+    <sheet name="About_Section" sheetId="5" r:id="rId7"/>
+    <sheet name="Thematic_Areas" sheetId="7" r:id="rId8"/>
+    <sheet name="Objectives" sheetId="8" r:id="rId9"/>
+    <sheet name="Leadership_Messages" sheetId="6" r:id="rId10"/>
+    <sheet name="Key_Speakers" sheetId="9" r:id="rId11"/>
+    <sheet name="Development Partners" sheetId="15" r:id="rId12"/>
+    <sheet name="Presenters" sheetId="10" r:id="rId13"/>
+    <sheet name="Call_For_Papers" sheetId="11" r:id="rId14"/>
+    <sheet name="Executive_Council" sheetId="12" r:id="rId15"/>
+    <sheet name="Trustees" sheetId="14" r:id="rId16"/>
+    <sheet name="The Invisible Engines" sheetId="16" r:id="rId17"/>
+    <sheet name="Contacts_And_Footer" sheetId="13" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Presenters!$E$1:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Presenters!$E$1:$E$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -109,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="641">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -747,9 +748,6 @@
     <t>Cascading Response and Support Model to Enhance Psychological Integration among Women Religious in India.</t>
   </si>
   <si>
-    <t>Dr. Kripanjali</t>
-  </si>
-  <si>
     <t>Dr. Joice Steffi Y</t>
   </si>
   <si>
@@ -799,9 +797,6 @@
   </si>
   <si>
     <t>Advancing Justice through Education: A Capacity-Building Intervention for Religious Sisters to Promote Child Mental Health in Educational Institutions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Dr. Sally </t>
   </si>
   <si>
     <t>Dr.  John Tharakan</t>
@@ -1762,9 +1757,6 @@
     <t>Sr. Dr. Jincy Maria</t>
   </si>
   <si>
-    <t>Fr. Dr.  Augustin  Bhayju</t>
-  </si>
-  <si>
     <t>Fr. Dr. Mathew Abraham</t>
   </si>
   <si>
@@ -1978,6 +1970,72 @@
   </si>
   <si>
     <t>Fr. Dr. Johnson S V</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Sally John</t>
+  </si>
+  <si>
+    <t>Fr. Dr. V. Antony Bhyju</t>
+  </si>
+  <si>
+    <t>Dr. Kripanjali Tellis Nayak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MC </t>
+  </si>
+  <si>
+    <t>Sr. Rushila Rebello</t>
+  </si>
+  <si>
+    <t>Programms- Cultural Event</t>
+  </si>
+  <si>
+    <t>Prayer Dance</t>
+  </si>
+  <si>
+    <t>Sacred Heart TTI</t>
+  </si>
+  <si>
+    <t>Welcome &amp; Inaugural Address</t>
+  </si>
+  <si>
+    <t>Symposium Theme Song</t>
+  </si>
+  <si>
+    <t>Pushpa Sadan</t>
+  </si>
+  <si>
+    <t>Message</t>
+  </si>
+  <si>
+    <t>Fr. Mathew Koyickal</t>
+  </si>
+  <si>
+    <t>Karnataka Cultural Dance</t>
+  </si>
+  <si>
+    <t>St. Antonys Com'ty</t>
+  </si>
+  <si>
+    <t>Solo Song</t>
+  </si>
+  <si>
+    <t>Cardinal Antony Poola</t>
+  </si>
+  <si>
+    <t>Tribal  Dance</t>
+  </si>
+  <si>
+    <t>Carmel Students</t>
+  </si>
+  <si>
+    <t>Vote of Thanks</t>
+  </si>
+  <si>
+    <t>Sr. Noella</t>
+  </si>
+  <si>
+    <t>Sonia lamngaihchiin neihsiel</t>
   </si>
 </sst>
 </file>
@@ -1987,7 +2045,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2096,8 +2154,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2119,6 +2191,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2204,7 +2282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2229,7 +2307,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2318,6 +2395,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2802,7 +2903,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2813,7 +2914,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2835,13 +2936,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>0</v>
@@ -2850,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2858,36 +2959,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B10" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="H11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -2895,19 +2996,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="I12" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -2915,186 +3016,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C13" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C14" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C15" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C16" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C18" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B20" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B21" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C21" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B22" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B23" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C23" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B24" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B25" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C25" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B26" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C26" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C27" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B28" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C28" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B29" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C29" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -3107,6 +3208,83 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="33.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3140,16 +3318,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3157,16 +3335,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3174,16 +3352,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C4" t="s">
+        <v>422</v>
+      </c>
+      <c r="D4" t="s">
+        <v>530</v>
+      </c>
+      <c r="E4" t="s">
         <v>423</v>
-      </c>
-      <c r="C4" t="s">
-        <v>424</v>
-      </c>
-      <c r="D4" t="s">
-        <v>532</v>
-      </c>
-      <c r="E4" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3191,16 +3369,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E5" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3208,16 +3386,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D6" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3225,16 +3403,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C7" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D7" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3242,16 +3420,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D8" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3259,16 +3437,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C9" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3276,16 +3454,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C10" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D10" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3293,13 +3471,13 @@
         <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C11" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D11" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E11" t="s">
         <v>163</v>
@@ -3310,16 +3488,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>537</v>
+      </c>
+      <c r="C12" t="s">
+        <v>538</v>
+      </c>
+      <c r="D12" t="s">
         <v>539</v>
       </c>
-      <c r="C12" t="s">
-        <v>540</v>
-      </c>
-      <c r="D12" t="s">
-        <v>541</v>
-      </c>
       <c r="E12" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3327,13 +3505,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D13" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
@@ -3344,16 +3522,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C14" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D14" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F408643-EE4E-4A6C-A3B2-9DA3CE87AD80}">
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3398,13 +3576,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3412,13 +3590,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3426,13 +3604,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3440,69 +3618,69 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>545</v>
+      <c r="B6" s="45" t="s">
+        <v>543</v>
       </c>
       <c r="C6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>546</v>
+      <c r="B7" s="45" t="s">
+        <v>544</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>547</v>
+      <c r="B8" s="43" t="s">
+        <v>545</v>
       </c>
       <c r="C8" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E8" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>548</v>
+      <c r="B9" s="43" t="s">
+        <v>546</v>
       </c>
       <c r="C9" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E9" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -3511,7 +3689,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:H45"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -3550,7 +3728,7 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3558,33 +3736,33 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="D2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="H2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
-        <v>453</v>
+      <c r="B3" s="43" t="s">
+        <v>451</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3596,24 +3774,24 @@
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>549</v>
+      <c r="B4" s="43" t="s">
+        <v>547</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
         <v>209</v>
@@ -3622,21 +3800,21 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>550</v>
+      <c r="B5" s="43" t="s">
+        <v>620</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3648,24 +3826,24 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="44" t="s">
+      <c r="B6" s="43" t="s">
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -3674,325 +3852,325 @@
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>458</v>
+      <c r="B7" s="43" t="s">
+        <v>456</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>410</v>
+      <c r="B8" s="43" t="s">
+        <v>408</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="H8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>551</v>
+      <c r="B9" s="10" t="s">
+        <v>548</v>
       </c>
       <c r="C9" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="H9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="44" t="s">
-        <v>230</v>
+      <c r="B10" s="43" t="s">
+        <v>619</v>
       </c>
       <c r="C10" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="44" t="s">
-        <v>232</v>
+      <c r="B11" s="43" t="s">
+        <v>230</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H11" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="44" t="s">
-        <v>323</v>
+      <c r="B12" s="43" t="s">
+        <v>321</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="H12" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="44" t="s">
-        <v>233</v>
+      <c r="B13" s="43" t="s">
+        <v>231</v>
       </c>
       <c r="C13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H13" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>552</v>
+      <c r="B14" s="10" t="s">
+        <v>549</v>
       </c>
       <c r="C14" t="s">
         <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="44" t="s">
-        <v>462</v>
+      <c r="B15" s="43" t="s">
+        <v>460</v>
       </c>
       <c r="C15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D15" t="s">
         <v>255</v>
-      </c>
-      <c r="D15" t="s">
-        <v>257</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="43" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D16" t="s">
         <v>320</v>
-      </c>
-      <c r="C16" t="s">
-        <v>254</v>
-      </c>
-      <c r="D16" t="s">
-        <v>322</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="44" t="s">
-        <v>252</v>
+      <c r="B17" s="43" t="s">
+        <v>250</v>
       </c>
       <c r="C17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H17" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="44" t="s">
-        <v>253</v>
+      <c r="B18" s="43" t="s">
+        <v>251</v>
       </c>
       <c r="C18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D18" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H18" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4000,363 +4178,363 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="44" t="s">
-        <v>459</v>
+      <c r="B20" s="43" t="s">
+        <v>457</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="H20" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="44" t="s">
-        <v>454</v>
+      <c r="B21" s="43" t="s">
+        <v>452</v>
       </c>
       <c r="C21" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>621</v>
+      <c r="B22" s="46" t="s">
+        <v>618</v>
       </c>
       <c r="C22" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D22" t="s">
-        <v>329</v>
-      </c>
-      <c r="E22" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H22" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="44" t="s">
-        <v>222</v>
+      <c r="B23" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="C23" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E23" t="s">
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>447</v>
+      <c r="B24" s="43" t="s">
+        <v>445</v>
       </c>
       <c r="C24" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H24" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="44" t="s">
-        <v>221</v>
+      <c r="B25" s="43" t="s">
+        <v>220</v>
       </c>
       <c r="C25" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H25" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>525</v>
+      <c r="B26" s="10" t="s">
+        <v>523</v>
       </c>
       <c r="C26" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D26" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H26" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="44" t="s">
-        <v>240</v>
+      <c r="B27" s="43" t="s">
+        <v>238</v>
       </c>
       <c r="C27" t="s">
         <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H27" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="44" t="s">
-        <v>324</v>
+      <c r="B28" s="43" t="s">
+        <v>322</v>
       </c>
       <c r="C28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="H28" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="44" t="s">
-        <v>553</v>
+      <c r="B29" s="43" t="s">
+        <v>550</v>
       </c>
       <c r="C29" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H29" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="44" t="s">
-        <v>241</v>
+      <c r="B30" s="43" t="s">
+        <v>239</v>
       </c>
       <c r="C30" t="s">
         <v>206</v>
       </c>
       <c r="D30" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H30" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="44" t="s">
-        <v>554</v>
+      <c r="B31" s="43" t="s">
+        <v>551</v>
       </c>
       <c r="C31" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H31" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>457</v>
+      <c r="B32" s="44" t="s">
+        <v>455</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D32" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -4364,155 +4542,155 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C33" t="s">
         <v>133</v>
       </c>
       <c r="D33" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H33" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="44" t="s">
-        <v>555</v>
+      <c r="B34" s="43" t="s">
+        <v>552</v>
       </c>
       <c r="C34" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E34" t="s">
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H34" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="44" t="s">
-        <v>522</v>
+      <c r="B35" s="43" t="s">
+        <v>520</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E35" t="s">
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H35" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="44" t="s">
-        <v>213</v>
+      <c r="B36" s="43" t="s">
+        <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D36" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E36" t="s">
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H36" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="44" t="s">
-        <v>461</v>
+      <c r="B37" s="43" t="s">
+        <v>459</v>
       </c>
       <c r="C37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H37" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" t="s">
-        <v>212</v>
+      <c r="B38" s="43" t="s">
+        <v>621</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H38" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4529,13 +4707,13 @@
         <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -4543,25 +4721,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E40" t="s">
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4569,25 +4747,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>206</v>
       </c>
       <c r="D41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4595,22 +4773,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F42" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -4618,19 +4796,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -4638,19 +4816,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -4658,22 +4836,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F45" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -4687,7 +4865,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4740,7 +4918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4876,7 +5054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25B4301E-B4F1-4F6C-84B3-E69F1BFD510E}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -4903,13 +5081,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -4917,13 +5095,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C3" t="s">
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -4931,13 +5109,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -4945,13 +5123,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C5" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -4959,13 +5137,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
         <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -4973,13 +5151,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C7" t="s">
         <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4988,7 +5166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE87D73C-0C6D-4F11-B208-F394024872E3}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5014,7 +5192,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5025,7 +5203,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5036,13 +5214,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5053,10 +5231,10 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5067,10 +5245,10 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5078,13 +5256,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5092,13 +5270,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D8" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5106,13 +5284,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C9" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D9" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5120,13 +5298,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D10" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5134,13 +5312,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" t="s">
         <v>412</v>
       </c>
-      <c r="C11" t="s">
-        <v>414</v>
-      </c>
       <c r="D11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5148,13 +5326,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C12" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D12" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5162,18 +5340,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C13" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5181,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C15" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5195,13 +5373,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C16" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D16" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5209,13 +5387,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C17" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D17" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5223,13 +5401,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C18" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D18" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5237,13 +5415,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5251,13 +5429,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C20" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D20" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5265,13 +5443,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D21" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5279,13 +5457,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C22" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D22" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5293,13 +5471,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C23" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D23" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5307,13 +5485,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C24" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D24" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5321,13 +5499,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C25" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5335,13 +5513,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C26" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D26" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5349,13 +5527,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5363,13 +5541,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D28" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5377,13 +5555,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C29" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D29" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -5393,7 +5571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -5566,7 +5744,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5761,7 +5939,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -5877,303 +6055,303 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="12"/>
-      <c r="B1" s="13" t="s">
-        <v>614</v>
-      </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="A1" s="11"/>
+      <c r="B1" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>561</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>46148</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C3" s="16"/>
+      <c r="D3" s="17" t="s">
         <v>564</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="18"/>
+      <c r="B4" s="19" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
-        <v>46148</v>
-      </c>
-      <c r="B3" s="16" t="s">
+      <c r="C4" s="20"/>
+      <c r="D4" s="21" t="s">
         <v>566</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>46149</v>
+      </c>
+      <c r="B5" s="22" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20" t="s">
+      <c r="C5" s="16" t="s">
         <v>568</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="22" t="s">
+      <c r="D5" s="23" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
-        <v>46149</v>
-      </c>
-      <c r="B5" s="23" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="18"/>
+      <c r="B6" s="19" t="s">
         <v>570</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="24" t="s">
         <v>571</v>
       </c>
-      <c r="D5" s="24" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="19"/>
+      <c r="B7" s="19" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="19"/>
-      <c r="B6" s="20" t="s">
+      <c r="C7" s="19"/>
+      <c r="D7" s="21" t="s">
         <v>573</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="25" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="22" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="19"/>
+      <c r="B9" s="19" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="25" t="s">
         <v>577</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="26" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="19"/>
+      <c r="B10" s="19" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="25" t="s">
         <v>579</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="26" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="19"/>
+      <c r="B11" s="26" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="26" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="20"/>
-      <c r="B11" s="27" t="s">
+      <c r="C12" s="11"/>
+      <c r="D12" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="26" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12" t="s">
+      <c r="C13" s="11"/>
+      <c r="D13" s="27" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="28" t="s">
+      <c r="C14" s="11"/>
+      <c r="D14" s="27" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12" t="s">
+      <c r="C15" s="28"/>
+      <c r="D15" s="29" t="s">
         <v>587</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="28" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12" t="s">
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="28" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12" t="s">
+      <c r="C16" s="30"/>
+      <c r="D16" s="31" t="s">
         <v>589</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="30" t="s">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="14">
+        <v>46150</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>567</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12" t="s">
+      <c r="D17" s="33" t="s">
         <v>591</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32" t="s">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11" t="s">
+        <v>570</v>
+      </c>
+      <c r="C18" s="34"/>
+      <c r="D18" s="31" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="15">
-        <v>46150</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>570</v>
-      </c>
-      <c r="C17" s="33" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="11"/>
+      <c r="B19" s="35" t="s">
         <v>593</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="C19" s="11"/>
+      <c r="D19" s="36" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12" t="s">
-        <v>573</v>
-      </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="32" t="s">
+    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="11"/>
+      <c r="B20" s="37" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="12"/>
-      <c r="B19" s="36" t="s">
+      <c r="C20" s="38"/>
+      <c r="D20" s="39" t="s">
         <v>596</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="37" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="11"/>
+      <c r="B21" s="40" t="s">
+        <v>574</v>
+      </c>
+      <c r="C21" s="38"/>
+      <c r="D21" s="39" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="12"/>
-      <c r="B20" s="38" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="40" t="s">
+      <c r="C22" s="11"/>
+      <c r="D22" s="41" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="12"/>
-      <c r="B21" s="41" t="s">
-        <v>577</v>
-      </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11" t="s">
         <v>600</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12" t="s">
+      <c r="C23" s="11"/>
+      <c r="D23" s="41" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="42" t="s">
+      <c r="C24" s="11"/>
+      <c r="D24" s="41" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11" t="s">
+        <v>578</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="41" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12" t="s">
+    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A26" s="11"/>
+      <c r="B26" s="42" t="s">
         <v>603</v>
       </c>
-      <c r="C23" s="12"/>
-      <c r="D23" s="42" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12" t="s">
+      <c r="C26" s="11"/>
+      <c r="D26" s="27" t="s">
         <v>604</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="42" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12" t="s">
-        <v>581</v>
-      </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="42" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A26" s="12"/>
-      <c r="B26" s="43" t="s">
+      <c r="C27" s="11"/>
+      <c r="D27" s="41" t="s">
         <v>606</v>
       </c>
-      <c r="C26" s="12"/>
-      <c r="D26" s="28" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11" t="s">
         <v>607</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12" t="s">
+      <c r="C28" s="11"/>
+      <c r="D28" s="27" t="s">
         <v>608</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="42" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="27" t="s">
         <v>610</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="28" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="12"/>
-      <c r="B29" s="12" t="s">
-        <v>612</v>
-      </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="28" t="s">
-        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -6182,6 +6360,136 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE4A1D8B-6AAB-48EA-AC2A-7DED15787E74}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="1.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.9140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="48"/>
+      <c r="B1" s="48" t="s">
+        <v>622</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="47"/>
+      <c r="B2" s="50" t="s">
+        <v>624</v>
+      </c>
+      <c r="C2" s="51"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="47">
+        <v>1</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>625</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
+      <c r="A4" s="47">
+        <v>2</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>627</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="47">
+        <v>3</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="47">
+        <v>4</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="C6" s="52" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="47">
+        <v>4</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>632</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="47">
+        <v>5</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="47">
+        <v>6</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="48">
+        <v>7</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>636</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="53">
+        <v>8</v>
+      </c>
+      <c r="B11" s="53" t="s">
+        <v>638</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>639</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -6244,7 +6552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -6360,7 +6668,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
@@ -6474,81 +6782,4 @@
     <ignoredError sqref="A1:D5 A7:D7 A6:C6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="5" max="5" width="33.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:F3" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
 </file>
--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="266" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D62CD29-499E-4104-8244-CD7A3772FD88}"/>
+  <xr:revisionPtr revIDLastSave="282" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272F69DA-681F-49FC-ABEF-8566C276D1AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="643">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -751,9 +751,6 @@
     <t>Dr. Joice Steffi Y</t>
   </si>
   <si>
-    <t>Sister</t>
-  </si>
-  <si>
     <t>Establishing sustainable and faith -rooted eldercare models that uphold diginity and independence</t>
   </si>
   <si>
@@ -871,9 +868,6 @@
     <t>MSMHC</t>
   </si>
   <si>
-    <t>St.Pauls</t>
-  </si>
-  <si>
     <t>CSsR</t>
   </si>
   <si>
@@ -1099,18 +1093,12 @@
     <t xml:space="preserve">Fr. Saju Chackalakkal </t>
   </si>
   <si>
-    <t xml:space="preserve">Fr. Jose Palely   </t>
-  </si>
-  <si>
     <t>images/Speakers/Sr. Jane.jpg</t>
   </si>
   <si>
     <t>images/Speakers/Fr. Saju.jpg</t>
   </si>
   <si>
-    <t>images/Speakers/Fr. Jose Palely.jpg</t>
-  </si>
-  <si>
     <t>Example Setting_Value</t>
   </si>
   <si>
@@ -1306,9 +1294,6 @@
     <t xml:space="preserve">Administrator Christ University </t>
   </si>
   <si>
-    <t>Vice Chancelor, ADBU, Guwahati</t>
-  </si>
-  <si>
     <t>CRI President</t>
   </si>
   <si>
@@ -1492,15 +1477,9 @@
     <t xml:space="preserve">Sr. Dr. Mary Paul </t>
   </si>
   <si>
-    <t>Fr. Dr. Sajith Cyriac, SSP</t>
-  </si>
-  <si>
     <t>SJ</t>
   </si>
   <si>
-    <t>Dr.Benny</t>
-  </si>
-  <si>
     <t>images/Presenters/modrators/Jerin.jpg</t>
   </si>
   <si>
@@ -1628,9 +1607,6 @@
   </si>
   <si>
     <t>Fr. V. Antony Bhyju, CMF, is a Claretian Missionary with wide experience in initial and ongoing formation, currently serving at the General Curia in Rome as Assistant to the General Consultors for Formation and Spirituality.</t>
-  </si>
-  <si>
-    <t>Sr. Dr. Helen Mary, SABS, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
   </si>
   <si>
     <t>Sr. Lismy CMC, of the Congregation of the Mother of Carmel, is a Catholic media missionary from Kerala, popularly known as the “Camera Nun.” She uses filmmaking and digital media for evangelization and social awareness and has produced numerous films highlighting faith, human dignity, and social issues. She is a recipient of the James Alberione Award for her contributions to Christian media.</t>
@@ -2036,6 +2012,37 @@
   </si>
   <si>
     <t>Sonia lamngaihchiin neihsiel</t>
+  </si>
+  <si>
+    <t>FDCC</t>
+  </si>
+  <si>
+    <t>SSP</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Sajith Cyriac</t>
+  </si>
+  <si>
+    <t>Dr. Benny Joseph Neelankavil</t>
+  </si>
+  <si>
+    <t>CEO, Jubilee Mission Health Care Institutions</t>
+  </si>
+  <si>
+    <t>Dr. Benny Joseph Neelankavil CEO, Jubilee Mission Health Care Institutions
+Healthcare leader with 25+ years in management and academics. Oversees seven institutions including a 1,700-bed hospital. Ph.D. in Management (IIM Ahmedabad). President, AHPI Kerala Chapter; Board Member, CHAI Kerala.</t>
+  </si>
+  <si>
+    <t>Fr. Viju Painadath</t>
+  </si>
+  <si>
+    <t>Pro Vice Chancellor, Christ</t>
+  </si>
+  <si>
+    <t>images/Speakers/Dr Fr Viju P D.jpg</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Helen Mary, SAB, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
   </si>
 </sst>
 </file>
@@ -2282,7 +2289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2297,9 +2304,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2395,11 +2399,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2419,6 +2419,18 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2844,13 +2856,13 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2903,7 +2915,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2914,7 +2926,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2936,22 +2948,22 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>325</v>
-      </c>
-      <c r="E9" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>437</v>
+      <c r="G9" s="6" t="s">
+        <v>432</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2959,56 +2971,56 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B10" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="H10" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I10" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="H11" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I11" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>334</v>
+      <c r="B12" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>330</v>
       </c>
       <c r="E12" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="H12" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="I12" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3016,186 +3028,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B14" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C14" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B15" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C15" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B16" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B17" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C17" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C18" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C19" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B20" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C20" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B21" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B22" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C22" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B23" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C23" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B24" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C24" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B25" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C25" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B26" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C26" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B27" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C27" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B28" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C28" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B29" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C29" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -3318,84 +3330,84 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D2" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="E2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>387</v>
+      <c r="B3" s="7" t="s">
+        <v>383</v>
       </c>
       <c r="C3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D3" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E3" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>421</v>
+      <c r="B4" s="8" t="s">
+        <v>416</v>
       </c>
       <c r="C4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="D4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>535</v>
+      <c r="B5" s="8" t="s">
+        <v>527</v>
       </c>
       <c r="C5" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D5" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="E5" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>390</v>
+      <c r="B6" s="8" t="s">
+        <v>386</v>
       </c>
       <c r="C6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E6" t="s">
         <v>391</v>
-      </c>
-      <c r="D6" t="s">
-        <v>529</v>
-      </c>
-      <c r="E6" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3403,16 +3415,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="C7" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D7" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="E7" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3420,16 +3432,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" t="s">
+        <v>394</v>
+      </c>
+      <c r="D8" t="s">
+        <v>531</v>
+      </c>
+      <c r="E8" t="s">
         <v>328</v>
-      </c>
-      <c r="C8" t="s">
-        <v>399</v>
-      </c>
-      <c r="D8" t="s">
-        <v>539</v>
-      </c>
-      <c r="E8" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3437,16 +3449,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>639</v>
       </c>
       <c r="C9" t="s">
-        <v>398</v>
+        <v>640</v>
       </c>
       <c r="D9" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E9" t="s">
-        <v>332</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3454,16 +3466,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C10" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D10" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E10" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3471,13 +3483,13 @@
         <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C11" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D11" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E11" t="s">
         <v>163</v>
@@ -3488,16 +3500,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C12" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D12" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E12" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3505,13 +3517,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="C13" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D13" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
@@ -3522,16 +3534,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C14" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="D14" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="E14" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -3576,13 +3588,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3590,13 +3602,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E3" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3604,13 +3616,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C4" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3618,69 +3630,69 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C5" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="E5" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="45" t="s">
-        <v>543</v>
+      <c r="B6" s="43" t="s">
+        <v>535</v>
       </c>
       <c r="C6" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="E6" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="45" t="s">
-        <v>544</v>
+      <c r="B7" s="43" t="s">
+        <v>536</v>
       </c>
       <c r="C7" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E7" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>545</v>
+      <c r="B8" s="42" t="s">
+        <v>537</v>
       </c>
       <c r="C8" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E8" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="43" t="s">
-        <v>546</v>
+      <c r="B9" s="42" t="s">
+        <v>538</v>
       </c>
       <c r="C9" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="E9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -3695,12 +3707,12 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.08203125" customWidth="1"/>
+    <col min="2" max="2" width="26.08203125" style="51" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="31.08203125" customWidth="1"/>
     <col min="5" max="5" width="23.25" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="63.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" style="56" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="44.1640625" customWidth="1"/>
   </cols>
@@ -3709,7 +3721,7 @@
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="51" t="s">
         <v>129</v>
       </c>
       <c r="C1" t="s">
@@ -3724,45 +3736,45 @@
       <c r="F1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="56" t="s">
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>615</v>
+      <c r="B2" s="51" t="s">
+        <v>607</v>
       </c>
       <c r="C2" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="D2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>518</v>
+        <v>456</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>510</v>
       </c>
       <c r="H2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="43" t="s">
-        <v>451</v>
+      <c r="B3" s="51" t="s">
+        <v>446</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3774,24 +3786,24 @@
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>298</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>257</v>
+        <v>296</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>255</v>
       </c>
       <c r="H3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="43" t="s">
-        <v>547</v>
+      <c r="B4" s="51" t="s">
+        <v>539</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D4" t="s">
         <v>209</v>
@@ -3800,21 +3812,21 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>517</v>
+        <v>297</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>509</v>
       </c>
       <c r="H4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="43" t="s">
-        <v>620</v>
+      <c r="B5" s="51" t="s">
+        <v>612</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3826,24 +3838,24 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>302</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>505</v>
+        <v>300</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>498</v>
       </c>
       <c r="H5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="51" t="s">
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -3852,852 +3864,852 @@
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>272</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>258</v>
+        <v>270</v>
+      </c>
+      <c r="G6" s="56" t="s">
+        <v>256</v>
       </c>
       <c r="H6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="43" t="s">
-        <v>456</v>
+      <c r="B7" s="51" t="s">
+        <v>451</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>271</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>525</v>
+        <v>269</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>517</v>
       </c>
       <c r="H7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="43" t="s">
-        <v>408</v>
+      <c r="B8" s="51" t="s">
+        <v>403</v>
       </c>
       <c r="C8" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>440</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>513</v>
+        <v>435</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>505</v>
       </c>
       <c r="H8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>548</v>
+      <c r="B9" s="52" t="s">
+        <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="D9" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>612</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>613</v>
+        <v>604</v>
+      </c>
+      <c r="G9" s="56" t="s">
+        <v>605</v>
       </c>
       <c r="H9" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="43" t="s">
-        <v>619</v>
+      <c r="B10" s="51" t="s">
+        <v>611</v>
       </c>
       <c r="C10" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>282</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>511</v>
+        <v>280</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>503</v>
       </c>
       <c r="H10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>230</v>
+      <c r="B11" s="51" t="s">
+        <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>633</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>420</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>264</v>
+        <v>415</v>
+      </c>
+      <c r="G11" s="56" t="s">
+        <v>262</v>
       </c>
       <c r="H11" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="43" t="s">
-        <v>321</v>
+      <c r="B12" s="51" t="s">
+        <v>319</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>284</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>510</v>
+        <v>282</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>502</v>
       </c>
       <c r="H12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="43" t="s">
-        <v>231</v>
+      <c r="B13" s="51" t="s">
+        <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>286</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>265</v>
+        <v>284</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>263</v>
       </c>
       <c r="H13" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>549</v>
+      <c r="B14" s="52" t="s">
+        <v>541</v>
       </c>
       <c r="C14" t="s">
         <v>133</v>
       </c>
       <c r="D14" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>417</v>
-      </c>
-      <c r="G14" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G14" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H14" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="43" t="s">
-        <v>460</v>
+      <c r="B15" s="51" t="s">
+        <v>635</v>
       </c>
       <c r="C15" t="s">
+        <v>634</v>
+      </c>
+      <c r="D15" t="s">
         <v>253</v>
-      </c>
-      <c r="D15" t="s">
-        <v>255</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>294</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>269</v>
+        <v>292</v>
+      </c>
+      <c r="G15" s="56" t="s">
+        <v>267</v>
       </c>
       <c r="H15" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="C16" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" t="s">
         <v>318</v>
-      </c>
-      <c r="C16" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" t="s">
-        <v>320</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>293</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>256</v>
+        <v>291</v>
+      </c>
+      <c r="G16" s="56" t="s">
+        <v>254</v>
       </c>
       <c r="H16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="43" t="s">
-        <v>250</v>
+      <c r="B17" s="51" t="s">
+        <v>249</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>296</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>507</v>
+        <v>294</v>
+      </c>
+      <c r="G17" s="56" t="s">
+        <v>499</v>
       </c>
       <c r="H17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="43" t="s">
-        <v>251</v>
+      <c r="B18" s="51" t="s">
+        <v>250</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>297</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>301</v>
+        <v>295</v>
+      </c>
+      <c r="G18" s="56" t="s">
+        <v>299</v>
       </c>
       <c r="H18" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
-        <v>450</v>
+      <c r="B19" s="51" t="s">
+        <v>445</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>464</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>514</v>
+        <v>457</v>
+      </c>
+      <c r="G19" s="56" t="s">
+        <v>506</v>
       </c>
       <c r="H19" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="43" t="s">
-        <v>457</v>
+      <c r="B20" s="51" t="s">
+        <v>452</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
       </c>
       <c r="D20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>405</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>512</v>
+        <v>400</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>504</v>
       </c>
       <c r="H20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="43" t="s">
-        <v>452</v>
+      <c r="B21" s="51" t="s">
+        <v>447</v>
       </c>
       <c r="C21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="D21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>278</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>261</v>
+        <v>276</v>
+      </c>
+      <c r="G21" s="56" t="s">
+        <v>259</v>
       </c>
       <c r="H21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="46" t="s">
-        <v>618</v>
+      <c r="B22" s="52" t="s">
+        <v>610</v>
       </c>
       <c r="C22" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D22" t="s">
-        <v>327</v>
-      </c>
-      <c r="E22" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>524</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>617</v>
+        <v>516</v>
+      </c>
+      <c r="G22" s="56" t="s">
+        <v>609</v>
       </c>
       <c r="H22" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="43" t="s">
-        <v>221</v>
+      <c r="B23" s="51" t="s">
+        <v>220</v>
       </c>
       <c r="C23" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E23" t="s">
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>263</v>
+        <v>279</v>
+      </c>
+      <c r="G23" s="56" t="s">
+        <v>261</v>
       </c>
       <c r="H23" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="43" t="s">
-        <v>445</v>
+      <c r="B24" s="51" t="s">
+        <v>440</v>
       </c>
       <c r="C24" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D24" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>279</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>454</v>
+        <v>277</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>449</v>
       </c>
       <c r="H24" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="43" t="s">
-        <v>220</v>
+      <c r="B25" s="51" t="s">
+        <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>280</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>262</v>
+        <v>278</v>
+      </c>
+      <c r="G25" s="56" t="s">
+        <v>260</v>
       </c>
       <c r="H25" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>523</v>
+      <c r="B26" s="52" t="s">
+        <v>515</v>
       </c>
       <c r="C26" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="D26" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>465</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>515</v>
+        <v>458</v>
+      </c>
+      <c r="G26" s="56" t="s">
+        <v>507</v>
       </c>
       <c r="H26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="43" t="s">
-        <v>238</v>
+      <c r="B27" s="51" t="s">
+        <v>237</v>
       </c>
       <c r="C27" t="s">
         <v>203</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>287</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>266</v>
+        <v>285</v>
+      </c>
+      <c r="G27" s="56" t="s">
+        <v>264</v>
       </c>
       <c r="H27" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="43" t="s">
-        <v>322</v>
+      <c r="B28" s="51" t="s">
+        <v>320</v>
       </c>
       <c r="C28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>490</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>509</v>
+        <v>483</v>
+      </c>
+      <c r="G28" s="56" t="s">
+        <v>501</v>
       </c>
       <c r="H28" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="43" t="s">
-        <v>550</v>
+      <c r="B29" s="51" t="s">
+        <v>542</v>
       </c>
       <c r="C29" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>419</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>267</v>
+        <v>414</v>
+      </c>
+      <c r="G29" s="56" t="s">
+        <v>265</v>
       </c>
       <c r="H29" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="43" t="s">
-        <v>239</v>
+      <c r="B30" s="51" t="s">
+        <v>238</v>
       </c>
       <c r="C30" t="s">
         <v>206</v>
       </c>
       <c r="D30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>292</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>268</v>
+        <v>290</v>
+      </c>
+      <c r="G30" s="56" t="s">
+        <v>266</v>
       </c>
       <c r="H30" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="43" t="s">
-        <v>551</v>
+      <c r="B31" s="51" t="s">
+        <v>543</v>
       </c>
       <c r="C31" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D31" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>291</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>508</v>
+        <v>289</v>
+      </c>
+      <c r="G31" s="56" t="s">
+        <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="44" t="s">
-        <v>455</v>
+      <c r="B32" s="53" t="s">
+        <v>450</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D32" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>288</v>
-      </c>
-      <c r="G32" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="G32" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" t="s">
-        <v>462</v>
+      <c r="B33" s="51" t="s">
+        <v>636</v>
       </c>
       <c r="C33" t="s">
-        <v>133</v>
+        <v>637</v>
       </c>
       <c r="D33" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>417</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>133</v>
+        <v>412</v>
+      </c>
+      <c r="G33" s="56" t="s">
+        <v>638</v>
       </c>
       <c r="H33" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="43" t="s">
-        <v>552</v>
+      <c r="B34" s="51" t="s">
+        <v>544</v>
       </c>
       <c r="C34" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E34" t="s">
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>300</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>506</v>
+        <v>298</v>
+      </c>
+      <c r="G34" s="56" t="s">
+        <v>642</v>
       </c>
       <c r="H34" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="43" t="s">
-        <v>520</v>
+      <c r="B35" s="51" t="s">
+        <v>512</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E35" t="s">
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>277</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>260</v>
+        <v>275</v>
+      </c>
+      <c r="G35" s="56" t="s">
+        <v>258</v>
       </c>
       <c r="H35" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="51" t="s">
         <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E36" t="s">
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>275</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>260</v>
+        <v>273</v>
+      </c>
+      <c r="G36" s="56" t="s">
+        <v>258</v>
       </c>
       <c r="H36" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="43" t="s">
-        <v>459</v>
+      <c r="B37" s="51" t="s">
+        <v>454</v>
       </c>
       <c r="C37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>273</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>259</v>
+        <v>271</v>
+      </c>
+      <c r="G37" s="56" t="s">
+        <v>257</v>
       </c>
       <c r="H37" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="43" t="s">
-        <v>621</v>
+      <c r="B38" s="51" t="s">
+        <v>613</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
       </c>
       <c r="D38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E38" t="s">
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>274</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>516</v>
+        <v>272</v>
+      </c>
+      <c r="G38" s="56" t="s">
+        <v>508</v>
       </c>
       <c r="H38" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="51" t="s">
         <v>133</v>
       </c>
       <c r="C39" t="s">
@@ -4707,151 +4719,151 @@
         <v>208</v>
       </c>
       <c r="F39" t="s">
-        <v>270</v>
-      </c>
-      <c r="G39" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G39" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>317</v>
+      <c r="B40" s="54" t="s">
+        <v>315</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E40" t="s">
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>276</v>
-      </c>
-      <c r="G40" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G40" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>229</v>
+      <c r="B41" s="55" t="s">
+        <v>228</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>206</v>
       </c>
       <c r="D41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>283</v>
-      </c>
-      <c r="G41" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G41" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>317</v>
+      <c r="B42" s="54" t="s">
+        <v>315</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F42" t="s">
-        <v>285</v>
-      </c>
-      <c r="G42" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="G42" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>317</v>
+      <c r="B43" s="54" t="s">
+        <v>315</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>289</v>
-      </c>
-      <c r="G43" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G43" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>317</v>
+      <c r="B44" s="54" t="s">
+        <v>315</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>290</v>
-      </c>
-      <c r="G44" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="G44" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>317</v>
+      <c r="B45" s="54" t="s">
+        <v>315</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F45" t="s">
-        <v>295</v>
-      </c>
-      <c r="G45" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G45" s="56" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -5081,13 +5093,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5095,13 +5107,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C3" t="s">
         <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -5109,13 +5121,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>154</v>
       </c>
       <c r="D4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5123,13 +5135,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C5" t="s">
         <v>158</v>
       </c>
       <c r="D5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5137,13 +5149,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C6" t="s">
         <v>158</v>
       </c>
       <c r="D6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5151,13 +5163,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C7" t="s">
         <v>158</v>
       </c>
       <c r="D7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -5192,7 +5204,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5203,7 +5215,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5214,13 +5226,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C4" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5231,10 +5243,10 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5245,10 +5257,10 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5256,13 +5268,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C7" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5270,13 +5282,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C8" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D8" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5284,13 +5296,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D9" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5298,13 +5310,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C10" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D10" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5312,13 +5324,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C11" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D11" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5326,13 +5338,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="C12" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D12" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5340,18 +5352,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C13" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="D13" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5359,13 +5371,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D15" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5373,13 +5385,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="C16" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D16" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5387,13 +5399,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="C17" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D17" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5401,13 +5413,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="C18" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D18" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5415,13 +5427,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C19" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D19" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5429,13 +5441,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="C20" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5443,13 +5455,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
       <c r="C21" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D21" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5457,13 +5469,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="C22" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D22" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5471,13 +5483,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C23" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D23" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5485,13 +5497,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C24" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D24" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5499,13 +5511,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="C25" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D25" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5513,13 +5525,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C26" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D26" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5527,13 +5539,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="C27" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D27" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5541,13 +5553,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="C28" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D28" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5555,13 +5567,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="C29" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D29" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -5744,7 +5756,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5939,7 +5951,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6055,303 +6067,303 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="11"/>
-      <c r="B1" s="12" t="s">
-        <v>611</v>
-      </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
+      <c r="A1" s="10"/>
+      <c r="B1" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
+        <v>552</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="13">
+        <v>46148</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>555</v>
+      </c>
+      <c r="C3" s="15"/>
+      <c r="D3" s="16" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="17"/>
+      <c r="B4" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="13">
+        <v>46149</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>560</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="D5" s="22" t="s">
         <v>561</v>
       </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="14">
-        <v>46148</v>
-      </c>
-      <c r="B3" s="15" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="23" t="s">
         <v>563</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="20" t="s">
         <v>565</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="21" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="14">
-        <v>46149</v>
-      </c>
-      <c r="B5" s="22" t="s">
+      <c r="C8" s="19"/>
+      <c r="D8" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="C5" s="16" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18" t="s">
         <v>568</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="24" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18" t="s">
         <v>570</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="24" t="s">
+      <c r="C10" s="19"/>
+      <c r="D10" s="24" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19" t="s">
+    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="18"/>
+      <c r="B11" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="21" t="s">
+      <c r="C11" s="19"/>
+      <c r="D11" s="24" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="25" t="s">
+      <c r="C12" s="10"/>
+      <c r="D12" s="26" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="25" t="s">
+      <c r="C13" s="10"/>
+      <c r="D13" s="26" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19" t="s">
+      <c r="C14" s="10"/>
+      <c r="D14" s="26" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10" t="s">
         <v>578</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="25" t="s">
+      <c r="C15" s="27"/>
+      <c r="D15" s="28" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="26" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="25" t="s">
+      <c r="C16" s="29"/>
+      <c r="D16" s="30" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="13">
+        <v>46150</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" s="31" t="s">
         <v>582</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="27" t="s">
+      <c r="D17" s="32" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="30" t="s">
         <v>584</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="27" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="27" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11" t="s">
+      <c r="C19" s="10"/>
+      <c r="D19" s="35" t="s">
         <v>586</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="36" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11" t="s">
+      <c r="C20" s="37"/>
+      <c r="D20" s="38" t="s">
         <v>588</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="31" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="10"/>
+      <c r="B21" s="39" t="s">
+        <v>566</v>
+      </c>
+      <c r="C21" s="37"/>
+      <c r="D21" s="38" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="14">
-        <v>46150</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>567</v>
-      </c>
-      <c r="C17" s="32" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="C22" s="10"/>
+      <c r="D22" s="40" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="C23" s="10"/>
+      <c r="D23" s="40" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="40" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="31" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="11"/>
-      <c r="B19" s="35" t="s">
-        <v>593</v>
-      </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="36" t="s">
+      <c r="C25" s="10"/>
+      <c r="D25" s="40" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="37" t="s">
+    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A26" s="10"/>
+      <c r="B26" s="41" t="s">
         <v>595</v>
       </c>
-      <c r="C20" s="38"/>
-      <c r="D20" s="39" t="s">
+      <c r="C26" s="10"/>
+      <c r="D26" s="26" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="11"/>
-      <c r="B21" s="40" t="s">
-        <v>574</v>
-      </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="39" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10" t="s">
         <v>597</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11" t="s">
+      <c r="C27" s="10"/>
+      <c r="D27" s="40" t="s">
         <v>598</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="41" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11" t="s">
+      <c r="C28" s="10"/>
+      <c r="D28" s="26" t="s">
         <v>600</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="41" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10" t="s">
         <v>601</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="41" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11" t="s">
-        <v>578</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="41" t="s">
+      <c r="C29" s="10"/>
+      <c r="D29" s="26" t="s">
         <v>602</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A26" s="11"/>
-      <c r="B26" s="42" t="s">
-        <v>603</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="27" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11" t="s">
-        <v>605</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="41" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11" t="s">
-        <v>607</v>
-      </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="27" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11" t="s">
-        <v>609</v>
-      </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="27" t="s">
-        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -6370,118 +6382,118 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="48"/>
-      <c r="B1" s="48" t="s">
+      <c r="A1" s="45"/>
+      <c r="B1" s="45" t="s">
+        <v>614</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="44"/>
+      <c r="B2" s="47" t="s">
+        <v>616</v>
+      </c>
+      <c r="C2" s="48"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="44">
+        <v>1</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
+      <c r="A4" s="44">
+        <v>2</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>619</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="44">
+        <v>3</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>620</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="44">
+        <v>4</v>
+      </c>
+      <c r="B6" s="44" t="s">
         <v>622</v>
       </c>
-      <c r="C1" s="47" t="s">
+      <c r="C6" s="49" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="47"/>
-      <c r="B2" s="50" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="44">
+        <v>4</v>
+      </c>
+      <c r="B7" s="44" t="s">
         <v>624</v>
       </c>
-      <c r="C2" s="51"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="47">
-        <v>1</v>
-      </c>
-      <c r="B3" s="47" t="s">
+      <c r="C7" s="44" t="s">
         <v>625</v>
       </c>
-      <c r="C3" s="47" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="44">
+        <v>5</v>
+      </c>
+      <c r="B8" s="44" t="s">
         <v>626</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
-      <c r="A4" s="47">
-        <v>2</v>
-      </c>
-      <c r="B4" s="49" t="s">
+      <c r="C8" s="44" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="44">
+        <v>6</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>622</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>627</v>
       </c>
-      <c r="C4" s="47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="47">
-        <v>3</v>
-      </c>
-      <c r="B5" s="47" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="45">
+        <v>7</v>
+      </c>
+      <c r="B10" s="44" t="s">
         <v>628</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C10" s="44" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="47">
-        <v>4</v>
-      </c>
-      <c r="B6" s="47" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="50">
+        <v>8</v>
+      </c>
+      <c r="B11" s="50" t="s">
         <v>630</v>
       </c>
-      <c r="C6" s="52" t="s">
+      <c r="C11" s="50" t="s">
         <v>631</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="47">
-        <v>4</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>632</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="47">
-        <v>5</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>634</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="47">
-        <v>6</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>630</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="48">
-        <v>7</v>
-      </c>
-      <c r="B10" s="47" t="s">
-        <v>636</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="53">
-        <v>8</v>
-      </c>
-      <c r="B11" s="53" t="s">
-        <v>638</v>
-      </c>
-      <c r="C11" s="53" t="s">
-        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="282" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{272F69DA-681F-49FC-ABEF-8566C276D1AA}"/>
+  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D048B89-F79D-457C-82C1-891CA8E8F015}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="646">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -1736,9 +1736,6 @@
     <t>Fr. Dr. Mathew Abraham</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Ronald </t>
-  </si>
-  <si>
     <t>Sr. Adv. Rushila Rebello</t>
   </si>
   <si>
@@ -2043,6 +2040,18 @@
   </si>
   <si>
     <t>Sr. Dr. Helen Mary, SAB, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
+  </si>
+  <si>
+    <t>images/Presenters/Ronald.jpeg</t>
+  </si>
+  <si>
+    <t>Dr. Ronald Anil Fernandes - Academic, journalist, and former KPSC Member (2018–2024), overseeing 5,000+ recruitments including 800 gazetted officers. He has 22+ years with Deccan Herald and taught journalism at St Aloysius College. He holds a PhD in Journalism, MCJ, MA Psychology, LLB, and BSc. Awards include the Sarojini Naidu National Award (2009) and District Rajyotsava Award (2012). He has served as President of Press Club (DK) and held various academic and civic board positions.</t>
+  </si>
+  <si>
+    <t>Academic and Journalist</t>
+  </si>
+  <si>
+    <t>Dr. Ronald Anil Fernandes</t>
   </si>
 </sst>
 </file>
@@ -2289,7 +2298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2419,15 +2428,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3390,7 +3393,7 @@
         <v>524</v>
       </c>
       <c r="E5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3421,7 +3424,7 @@
         <v>443</v>
       </c>
       <c r="D7" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E7" t="s">
         <v>400</v>
@@ -3449,16 +3452,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C9" t="s">
         <v>639</v>
-      </c>
-      <c r="C9" t="s">
-        <v>640</v>
       </c>
       <c r="D9" t="s">
         <v>531</v>
       </c>
       <c r="E9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3466,7 +3469,7 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C10" t="s">
         <v>393</v>
@@ -3509,7 +3512,7 @@
         <v>531</v>
       </c>
       <c r="E12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3707,12 +3710,12 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.08203125" style="51" customWidth="1"/>
+    <col min="2" max="2" width="26.08203125" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
     <col min="4" max="4" width="31.08203125" customWidth="1"/>
     <col min="5" max="5" width="23.25" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="63.33203125" style="56" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" style="52" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="44.1640625" customWidth="1"/>
   </cols>
@@ -3721,7 +3724,7 @@
       <c r="A1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" t="s">
         <v>129</v>
       </c>
       <c r="C1" t="s">
@@ -3736,7 +3739,7 @@
       <c r="F1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="52" t="s">
         <v>132</v>
       </c>
       <c r="H1" t="s">
@@ -3747,11 +3750,11 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="51" t="s">
+      <c r="B2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C2" t="s">
         <v>607</v>
-      </c>
-      <c r="C2" t="s">
-        <v>608</v>
       </c>
       <c r="D2" t="s">
         <v>444</v>
@@ -3762,7 +3765,7 @@
       <c r="F2" t="s">
         <v>456</v>
       </c>
-      <c r="G2" s="56" t="s">
+      <c r="G2" s="52" t="s">
         <v>510</v>
       </c>
       <c r="H2" t="s">
@@ -3773,7 +3776,7 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" t="s">
         <v>446</v>
       </c>
       <c r="C3" t="s">
@@ -3788,7 +3791,7 @@
       <c r="F3" t="s">
         <v>296</v>
       </c>
-      <c r="G3" s="56" t="s">
+      <c r="G3" s="52" t="s">
         <v>255</v>
       </c>
       <c r="H3" t="s">
@@ -3799,7 +3802,7 @@
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" t="s">
         <v>539</v>
       </c>
       <c r="C4" t="s">
@@ -3814,7 +3817,7 @@
       <c r="F4" t="s">
         <v>297</v>
       </c>
-      <c r="G4" s="56" t="s">
+      <c r="G4" s="52" t="s">
         <v>509</v>
       </c>
       <c r="H4" t="s">
@@ -3825,8 +3828,8 @@
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="51" t="s">
-        <v>612</v>
+      <c r="B5" t="s">
+        <v>611</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3840,7 +3843,7 @@
       <c r="F5" t="s">
         <v>300</v>
       </c>
-      <c r="G5" s="56" t="s">
+      <c r="G5" s="52" t="s">
         <v>498</v>
       </c>
       <c r="H5" t="s">
@@ -3851,7 +3854,7 @@
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="51" t="s">
+      <c r="B6" t="s">
         <v>202</v>
       </c>
       <c r="C6" t="s">
@@ -3866,7 +3869,7 @@
       <c r="F6" t="s">
         <v>270</v>
       </c>
-      <c r="G6" s="56" t="s">
+      <c r="G6" s="52" t="s">
         <v>256</v>
       </c>
       <c r="H6" t="s">
@@ -3877,7 +3880,7 @@
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="51" t="s">
+      <c r="B7" t="s">
         <v>451</v>
       </c>
       <c r="C7" t="s">
@@ -3892,7 +3895,7 @@
       <c r="F7" t="s">
         <v>269</v>
       </c>
-      <c r="G7" s="56" t="s">
+      <c r="G7" s="52" t="s">
         <v>517</v>
       </c>
       <c r="H7" t="s">
@@ -3903,7 +3906,7 @@
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" t="s">
         <v>403</v>
       </c>
       <c r="C8" t="s">
@@ -3918,7 +3921,7 @@
       <c r="F8" t="s">
         <v>435</v>
       </c>
-      <c r="G8" s="56" t="s">
+      <c r="G8" s="52" t="s">
         <v>505</v>
       </c>
       <c r="H8" t="s">
@@ -3929,11 +3932,11 @@
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B9" s="9" t="s">
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D9" t="s">
         <v>444</v>
@@ -3942,10 +3945,10 @@
         <v>94</v>
       </c>
       <c r="F9" t="s">
+        <v>603</v>
+      </c>
+      <c r="G9" s="52" t="s">
         <v>604</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>605</v>
       </c>
       <c r="H9" t="s">
         <v>322</v>
@@ -3955,8 +3958,8 @@
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="51" t="s">
-        <v>611</v>
+      <c r="B10" t="s">
+        <v>610</v>
       </c>
       <c r="C10" t="s">
         <v>436</v>
@@ -3970,7 +3973,7 @@
       <c r="F10" t="s">
         <v>280</v>
       </c>
-      <c r="G10" s="56" t="s">
+      <c r="G10" s="52" t="s">
         <v>503</v>
       </c>
       <c r="H10" t="s">
@@ -3981,11 +3984,11 @@
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="51" t="s">
+      <c r="B11" t="s">
         <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -3996,7 +3999,7 @@
       <c r="F11" t="s">
         <v>415</v>
       </c>
-      <c r="G11" s="56" t="s">
+      <c r="G11" s="52" t="s">
         <v>262</v>
       </c>
       <c r="H11" t="s">
@@ -4007,7 +4010,7 @@
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" t="s">
         <v>319</v>
       </c>
       <c r="C12" t="s">
@@ -4022,7 +4025,7 @@
       <c r="F12" t="s">
         <v>282</v>
       </c>
-      <c r="G12" s="56" t="s">
+      <c r="G12" s="52" t="s">
         <v>502</v>
       </c>
       <c r="H12" t="s">
@@ -4033,7 +4036,7 @@
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" t="s">
         <v>230</v>
       </c>
       <c r="C13" t="s">
@@ -4048,22 +4051,22 @@
       <c r="F13" t="s">
         <v>284</v>
       </c>
-      <c r="G13" s="56" t="s">
+      <c r="G13" s="52" t="s">
         <v>263</v>
       </c>
       <c r="H13" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="52" t="s">
-        <v>541</v>
+      <c r="B14" s="9" t="s">
+        <v>645</v>
       </c>
       <c r="C14" t="s">
-        <v>133</v>
+        <v>644</v>
       </c>
       <c r="D14" t="s">
         <v>444</v>
@@ -4072,10 +4075,10 @@
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>412</v>
-      </c>
-      <c r="G14" s="56" t="s">
-        <v>133</v>
+        <v>642</v>
+      </c>
+      <c r="G14" s="52" t="s">
+        <v>643</v>
       </c>
       <c r="H14" t="s">
         <v>322</v>
@@ -4085,11 +4088,11 @@
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="51" t="s">
-        <v>635</v>
+      <c r="B15" t="s">
+        <v>634</v>
       </c>
       <c r="C15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
@@ -4100,7 +4103,7 @@
       <c r="F15" t="s">
         <v>292</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="52" t="s">
         <v>267</v>
       </c>
       <c r="H15" t="s">
@@ -4111,7 +4114,7 @@
       <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" t="s">
         <v>316</v>
       </c>
       <c r="C16" t="s">
@@ -4126,7 +4129,7 @@
       <c r="F16" t="s">
         <v>291</v>
       </c>
-      <c r="G16" s="56" t="s">
+      <c r="G16" s="52" t="s">
         <v>254</v>
       </c>
       <c r="H16" t="s">
@@ -4137,7 +4140,7 @@
       <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" t="s">
         <v>249</v>
       </c>
       <c r="C17" t="s">
@@ -4152,7 +4155,7 @@
       <c r="F17" t="s">
         <v>294</v>
       </c>
-      <c r="G17" s="56" t="s">
+      <c r="G17" s="52" t="s">
         <v>499</v>
       </c>
       <c r="H17" t="s">
@@ -4163,7 +4166,7 @@
       <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" t="s">
         <v>250</v>
       </c>
       <c r="C18" t="s">
@@ -4178,7 +4181,7 @@
       <c r="F18" t="s">
         <v>295</v>
       </c>
-      <c r="G18" s="56" t="s">
+      <c r="G18" s="52" t="s">
         <v>299</v>
       </c>
       <c r="H18" t="s">
@@ -4189,7 +4192,7 @@
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" t="s">
         <v>445</v>
       </c>
       <c r="C19" t="s">
@@ -4204,7 +4207,7 @@
       <c r="F19" t="s">
         <v>457</v>
       </c>
-      <c r="G19" s="56" t="s">
+      <c r="G19" s="52" t="s">
         <v>506</v>
       </c>
       <c r="H19" t="s">
@@ -4215,7 +4218,7 @@
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" t="s">
         <v>452</v>
       </c>
       <c r="C20" t="s">
@@ -4230,7 +4233,7 @@
       <c r="F20" t="s">
         <v>400</v>
       </c>
-      <c r="G20" s="56" t="s">
+      <c r="G20" s="52" t="s">
         <v>504</v>
       </c>
       <c r="H20" t="s">
@@ -4241,7 +4244,7 @@
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" t="s">
         <v>447</v>
       </c>
       <c r="C21" t="s">
@@ -4256,7 +4259,7 @@
       <c r="F21" t="s">
         <v>276</v>
       </c>
-      <c r="G21" s="56" t="s">
+      <c r="G21" s="52" t="s">
         <v>259</v>
       </c>
       <c r="H21" t="s">
@@ -4267,8 +4270,8 @@
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="52" t="s">
-        <v>610</v>
+      <c r="B22" s="9" t="s">
+        <v>609</v>
       </c>
       <c r="C22" t="s">
         <v>324</v>
@@ -4282,8 +4285,8 @@
       <c r="F22" t="s">
         <v>516</v>
       </c>
-      <c r="G22" s="56" t="s">
-        <v>609</v>
+      <c r="G22" s="52" t="s">
+        <v>608</v>
       </c>
       <c r="H22" t="s">
         <v>322</v>
@@ -4293,7 +4296,7 @@
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="51" t="s">
+      <c r="B23" t="s">
         <v>220</v>
       </c>
       <c r="C23" t="s">
@@ -4308,7 +4311,7 @@
       <c r="F23" t="s">
         <v>279</v>
       </c>
-      <c r="G23" s="56" t="s">
+      <c r="G23" s="52" t="s">
         <v>261</v>
       </c>
       <c r="H23" t="s">
@@ -4319,7 +4322,7 @@
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="51" t="s">
+      <c r="B24" t="s">
         <v>440</v>
       </c>
       <c r="C24" t="s">
@@ -4334,7 +4337,7 @@
       <c r="F24" t="s">
         <v>277</v>
       </c>
-      <c r="G24" s="56" t="s">
+      <c r="G24" s="52" t="s">
         <v>449</v>
       </c>
       <c r="H24" t="s">
@@ -4345,7 +4348,7 @@
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="51" t="s">
+      <c r="B25" t="s">
         <v>219</v>
       </c>
       <c r="C25" t="s">
@@ -4360,7 +4363,7 @@
       <c r="F25" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="56" t="s">
+      <c r="G25" s="52" t="s">
         <v>260</v>
       </c>
       <c r="H25" t="s">
@@ -4371,7 +4374,7 @@
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="9" t="s">
         <v>515</v>
       </c>
       <c r="C26" t="s">
@@ -4386,7 +4389,7 @@
       <c r="F26" t="s">
         <v>458</v>
       </c>
-      <c r="G26" s="56" t="s">
+      <c r="G26" s="52" t="s">
         <v>507</v>
       </c>
       <c r="H26" t="s">
@@ -4397,7 +4400,7 @@
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" t="s">
         <v>237</v>
       </c>
       <c r="C27" t="s">
@@ -4412,7 +4415,7 @@
       <c r="F27" t="s">
         <v>285</v>
       </c>
-      <c r="G27" s="56" t="s">
+      <c r="G27" s="52" t="s">
         <v>264</v>
       </c>
       <c r="H27" t="s">
@@ -4423,7 +4426,7 @@
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="51" t="s">
+      <c r="B28" t="s">
         <v>320</v>
       </c>
       <c r="C28" t="s">
@@ -4438,7 +4441,7 @@
       <c r="F28" t="s">
         <v>483</v>
       </c>
-      <c r="G28" s="56" t="s">
+      <c r="G28" s="52" t="s">
         <v>501</v>
       </c>
       <c r="H28" t="s">
@@ -4449,8 +4452,8 @@
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="51" t="s">
-        <v>542</v>
+      <c r="B29" t="s">
+        <v>541</v>
       </c>
       <c r="C29" t="s">
         <v>241</v>
@@ -4464,7 +4467,7 @@
       <c r="F29" t="s">
         <v>414</v>
       </c>
-      <c r="G29" s="56" t="s">
+      <c r="G29" s="52" t="s">
         <v>265</v>
       </c>
       <c r="H29" t="s">
@@ -4475,7 +4478,7 @@
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" t="s">
         <v>238</v>
       </c>
       <c r="C30" t="s">
@@ -4490,7 +4493,7 @@
       <c r="F30" t="s">
         <v>290</v>
       </c>
-      <c r="G30" s="56" t="s">
+      <c r="G30" s="52" t="s">
         <v>266</v>
       </c>
       <c r="H30" t="s">
@@ -4501,8 +4504,8 @@
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="51" t="s">
-        <v>543</v>
+      <c r="B31" t="s">
+        <v>542</v>
       </c>
       <c r="C31" t="s">
         <v>240</v>
@@ -4516,7 +4519,7 @@
       <c r="F31" t="s">
         <v>289</v>
       </c>
-      <c r="G31" s="56" t="s">
+      <c r="G31" s="52" t="s">
         <v>500</v>
       </c>
       <c r="H31" t="s">
@@ -4527,7 +4530,7 @@
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="53" t="s">
+      <c r="B32" s="1" t="s">
         <v>450</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -4542,7 +4545,7 @@
       <c r="F32" t="s">
         <v>286</v>
       </c>
-      <c r="G32" s="56" t="s">
+      <c r="G32" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
@@ -4553,11 +4556,11 @@
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" t="s">
+        <v>635</v>
+      </c>
+      <c r="C33" t="s">
         <v>636</v>
-      </c>
-      <c r="C33" t="s">
-        <v>637</v>
       </c>
       <c r="D33" t="s">
         <v>444</v>
@@ -4568,8 +4571,8 @@
       <c r="F33" t="s">
         <v>412</v>
       </c>
-      <c r="G33" s="56" t="s">
-        <v>638</v>
+      <c r="G33" s="52" t="s">
+        <v>637</v>
       </c>
       <c r="H33" t="s">
         <v>322</v>
@@ -4579,8 +4582,8 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="51" t="s">
-        <v>544</v>
+      <c r="B34" t="s">
+        <v>543</v>
       </c>
       <c r="C34" t="s">
         <v>222</v>
@@ -4594,8 +4597,8 @@
       <c r="F34" t="s">
         <v>298</v>
       </c>
-      <c r="G34" s="56" t="s">
-        <v>642</v>
+      <c r="G34" s="52" t="s">
+        <v>641</v>
       </c>
       <c r="H34" t="s">
         <v>322</v>
@@ -4605,7 +4608,7 @@
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="51" t="s">
+      <c r="B35" t="s">
         <v>512</v>
       </c>
       <c r="C35" t="s">
@@ -4620,7 +4623,7 @@
       <c r="F35" t="s">
         <v>275</v>
       </c>
-      <c r="G35" s="56" t="s">
+      <c r="G35" s="52" t="s">
         <v>258</v>
       </c>
       <c r="H35" t="s">
@@ -4631,7 +4634,7 @@
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="51" t="s">
+      <c r="B36" t="s">
         <v>212</v>
       </c>
       <c r="C36" t="s">
@@ -4646,7 +4649,7 @@
       <c r="F36" t="s">
         <v>273</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="52" t="s">
         <v>258</v>
       </c>
       <c r="H36" t="s">
@@ -4657,7 +4660,7 @@
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" t="s">
         <v>454</v>
       </c>
       <c r="C37" t="s">
@@ -4672,7 +4675,7 @@
       <c r="F37" t="s">
         <v>271</v>
       </c>
-      <c r="G37" s="56" t="s">
+      <c r="G37" s="52" t="s">
         <v>257</v>
       </c>
       <c r="H37" t="s">
@@ -4683,8 +4686,8 @@
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="51" t="s">
-        <v>613</v>
+      <c r="B38" t="s">
+        <v>612</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
@@ -4698,7 +4701,7 @@
       <c r="F38" t="s">
         <v>272</v>
       </c>
-      <c r="G38" s="56" t="s">
+      <c r="G38" s="52" t="s">
         <v>508</v>
       </c>
       <c r="H38" t="s">
@@ -4709,7 +4712,7 @@
       <c r="A39" s="3">
         <v>38</v>
       </c>
-      <c r="B39" s="51" t="s">
+      <c r="B39" t="s">
         <v>133</v>
       </c>
       <c r="C39" t="s">
@@ -4721,7 +4724,7 @@
       <c r="F39" t="s">
         <v>268</v>
       </c>
-      <c r="G39" s="56" t="s">
+      <c r="G39" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
@@ -4732,7 +4735,7 @@
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="54" t="s">
+      <c r="B40" s="51" t="s">
         <v>315</v>
       </c>
       <c r="C40" t="s">
@@ -4747,7 +4750,7 @@
       <c r="F40" t="s">
         <v>274</v>
       </c>
-      <c r="G40" s="56" t="s">
+      <c r="G40" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
@@ -4758,7 +4761,7 @@
       <c r="A41" s="3">
         <v>40</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="5" t="s">
         <v>228</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -4773,7 +4776,7 @@
       <c r="F41" t="s">
         <v>281</v>
       </c>
-      <c r="G41" s="56" t="s">
+      <c r="G41" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
@@ -4784,7 +4787,7 @@
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="54" t="s">
+      <c r="B42" s="51" t="s">
         <v>315</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -4796,7 +4799,7 @@
       <c r="F42" t="s">
         <v>283</v>
       </c>
-      <c r="G42" s="56" t="s">
+      <c r="G42" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
@@ -4807,7 +4810,7 @@
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="54" t="s">
+      <c r="B43" s="51" t="s">
         <v>315</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -4816,7 +4819,7 @@
       <c r="F43" t="s">
         <v>287</v>
       </c>
-      <c r="G43" s="56" t="s">
+      <c r="G43" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
@@ -4827,7 +4830,7 @@
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="54" t="s">
+      <c r="B44" s="51" t="s">
         <v>315</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -4836,7 +4839,7 @@
       <c r="F44" t="s">
         <v>288</v>
       </c>
-      <c r="G44" s="56" t="s">
+      <c r="G44" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
@@ -4847,7 +4850,7 @@
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="54" t="s">
+      <c r="B45" s="51" t="s">
         <v>315</v>
       </c>
       <c r="C45" t="s">
@@ -4859,7 +4862,7 @@
       <c r="F45" t="s">
         <v>293</v>
       </c>
-      <c r="G45" s="56" t="s">
+      <c r="G45" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
@@ -5282,7 +5285,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C8" t="s">
         <v>407</v>
@@ -5525,13 +5528,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C26" t="s">
         <v>411</v>
       </c>
       <c r="D26" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -6069,21 +6072,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>552</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>553</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6091,21 +6094,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6113,123 +6116,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>558</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>559</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="22" t="s">
         <v>560</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6237,133 +6240,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C17" s="31" t="s">
+        <v>581</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>582</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>
@@ -6384,16 +6387,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
+        <v>613</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>614</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6402,10 +6405,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
+        <v>616</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>617</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6413,7 +6416,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>185</v>
@@ -6424,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>620</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6435,10 +6438,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
+        <v>621</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>622</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -6446,10 +6449,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>623</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>624</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -6457,10 +6460,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6468,10 +6471,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -6479,10 +6482,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
+        <v>627</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>628</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -6490,10 +6493,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="50" t="s">
+        <v>629</v>
+      </c>
+      <c r="C11" s="50" t="s">
         <v>630</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="288" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D048B89-F79D-457C-82C1-891CA8E8F015}"/>
+  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5EF43AE-4C80-4FF9-9CB1-042EA4E45BA0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -1096,9 +1096,6 @@
     <t>images/Speakers/Sr. Jane.jpg</t>
   </si>
   <si>
-    <t>images/Speakers/Fr. Saju.jpg</t>
-  </si>
-  <si>
     <t>Example Setting_Value</t>
   </si>
   <si>
@@ -1346,9 +1343,6 @@
   </si>
   <si>
     <t>Volunteer -</t>
-  </si>
-  <si>
-    <t>images/The Invisible Engines/logo.png</t>
   </si>
   <si>
     <t>Mrs. Asha M Albert</t>
@@ -2052,6 +2046,12 @@
   </si>
   <si>
     <t>Dr. Ronald Anil Fernandes</t>
+  </si>
+  <si>
+    <t>images/Presenters/Benny.png</t>
+  </si>
+  <si>
+    <t>images/Speakers/Fr.Saju.jpg</t>
   </si>
 </sst>
 </file>
@@ -2918,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2929,7 +2929,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2951,7 +2951,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -2966,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2974,36 +2974,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D10" t="s">
         <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H10" t="s">
         <v>323</v>
       </c>
       <c r="I10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="H11" t="s">
         <v>323</v>
       </c>
       <c r="I11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>330</v>
-      </c>
       <c r="E12" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H12" t="s">
         <v>323</v>
       </c>
       <c r="I12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3031,186 +3031,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" t="s">
         <v>356</v>
-      </c>
-      <c r="C13" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B14" t="s">
+        <v>357</v>
+      </c>
+      <c r="C14" t="s">
         <v>358</v>
-      </c>
-      <c r="C14" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B15" t="s">
+        <v>359</v>
+      </c>
+      <c r="C15" t="s">
         <v>360</v>
-      </c>
-      <c r="C15" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C16" t="s">
         <v>331</v>
-      </c>
-      <c r="B16" t="s">
-        <v>362</v>
-      </c>
-      <c r="C16" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" t="s">
+        <v>377</v>
+      </c>
+      <c r="C17" t="s">
         <v>341</v>
-      </c>
-      <c r="B17" t="s">
-        <v>378</v>
-      </c>
-      <c r="C17" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" t="s">
         <v>337</v>
-      </c>
-      <c r="B18" t="s">
-        <v>363</v>
-      </c>
-      <c r="C18" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" t="s">
         <v>364</v>
-      </c>
-      <c r="C19" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>338</v>
+      </c>
+      <c r="B20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C20" t="s">
         <v>339</v>
-      </c>
-      <c r="B20" t="s">
-        <v>366</v>
-      </c>
-      <c r="C20" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>332</v>
+      </c>
+      <c r="B21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C21" t="s">
         <v>333</v>
-      </c>
-      <c r="B21" t="s">
-        <v>367</v>
-      </c>
-      <c r="C21" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" t="s">
+        <v>367</v>
+      </c>
+      <c r="C22" t="s">
         <v>335</v>
-      </c>
-      <c r="B22" t="s">
-        <v>368</v>
-      </c>
-      <c r="C22" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B23" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" t="s">
         <v>369</v>
-      </c>
-      <c r="C23" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>346</v>
+      </c>
+      <c r="B24" t="s">
+        <v>370</v>
+      </c>
+      <c r="C24" t="s">
         <v>347</v>
-      </c>
-      <c r="B24" t="s">
-        <v>371</v>
-      </c>
-      <c r="C24" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B25" t="s">
+        <v>371</v>
+      </c>
+      <c r="C25" t="s">
         <v>372</v>
-      </c>
-      <c r="C25" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B26" t="s">
+        <v>373</v>
+      </c>
+      <c r="C26" t="s">
         <v>374</v>
-      </c>
-      <c r="C26" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B27" t="s">
+        <v>375</v>
+      </c>
+      <c r="C27" t="s">
         <v>376</v>
-      </c>
-      <c r="C27" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>342</v>
+      </c>
+      <c r="B28" t="s">
+        <v>488</v>
+      </c>
+      <c r="C28" t="s">
         <v>343</v>
-      </c>
-      <c r="B28" t="s">
-        <v>490</v>
-      </c>
-      <c r="C28" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>344</v>
+      </c>
+      <c r="B29" t="s">
+        <v>489</v>
+      </c>
+      <c r="C29" t="s">
         <v>345</v>
-      </c>
-      <c r="B29" t="s">
-        <v>491</v>
-      </c>
-      <c r="C29" t="s">
-        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -3333,16 +3333,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3350,16 +3350,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C3" t="s">
         <v>383</v>
       </c>
-      <c r="C3" t="s">
-        <v>384</v>
-      </c>
       <c r="D3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3367,16 +3367,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C4" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" t="s">
+        <v>520</v>
+      </c>
+      <c r="E4" t="s">
         <v>416</v>
-      </c>
-      <c r="C4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D4" t="s">
-        <v>522</v>
-      </c>
-      <c r="E4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3384,16 +3384,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3401,16 +3401,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C6" t="s">
         <v>386</v>
       </c>
-      <c r="C6" t="s">
-        <v>387</v>
-      </c>
       <c r="D6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3418,16 +3418,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3438,13 +3438,13 @@
         <v>326</v>
       </c>
       <c r="C8" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E8" t="s">
-        <v>328</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3452,16 +3452,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
+        <v>636</v>
+      </c>
+      <c r="C9" t="s">
+        <v>637</v>
+      </c>
+      <c r="D9" t="s">
+        <v>529</v>
+      </c>
+      <c r="E9" t="s">
         <v>638</v>
-      </c>
-      <c r="C9" t="s">
-        <v>639</v>
-      </c>
-      <c r="D9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E9" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3469,16 +3469,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D10" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3486,13 +3486,13 @@
         <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C11" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D11" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E11" t="s">
         <v>163</v>
@@ -3503,16 +3503,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>527</v>
+      </c>
+      <c r="C12" t="s">
+        <v>528</v>
+      </c>
+      <c r="D12" t="s">
         <v>529</v>
       </c>
-      <c r="C12" t="s">
-        <v>530</v>
-      </c>
-      <c r="D12" t="s">
-        <v>531</v>
-      </c>
       <c r="E12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3520,13 +3520,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
@@ -3537,16 +3537,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -3591,10 +3591,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E2" t="s">
         <v>327</v>
@@ -3605,13 +3605,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3619,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>394</v>
+      </c>
+      <c r="C4" t="s">
         <v>395</v>
       </c>
-      <c r="C4" t="s">
-        <v>396</v>
-      </c>
       <c r="E4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3633,13 +3633,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3647,13 +3647,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3661,13 +3661,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3675,13 +3675,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E8" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3689,13 +3689,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C9" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E9" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3751,22 +3751,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="H2" t="s">
         <v>322</v>
@@ -3777,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="C4" t="s">
         <v>221</v>
@@ -3818,7 +3818,7 @@
         <v>297</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="H4" t="s">
         <v>322</v>
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3844,7 +3844,7 @@
         <v>300</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="H5" t="s">
         <v>322</v>
@@ -3858,7 +3858,7 @@
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -3881,13 +3881,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
@@ -3896,7 +3896,7 @@
         <v>269</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="H7" t="s">
         <v>322</v>
@@ -3907,22 +3907,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H8" t="s">
         <v>322</v>
@@ -3933,22 +3933,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C9" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H9" t="s">
         <v>322</v>
@@ -3959,10 +3959,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D10" t="s">
         <v>231</v>
@@ -3974,7 +3974,7 @@
         <v>280</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="H10" t="s">
         <v>322</v>
@@ -3988,7 +3988,7 @@
         <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -3997,7 +3997,7 @@
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>262</v>
@@ -4026,7 +4026,7 @@
         <v>282</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H12" t="s">
         <v>322</v>
@@ -4040,7 +4040,7 @@
         <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D13" t="s">
         <v>235</v>
@@ -4063,22 +4063,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C14" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D14" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G14" s="52" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H14" t="s">
         <v>322</v>
@@ -4089,10 +4089,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C15" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
@@ -4156,7 +4156,7 @@
         <v>294</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H17" t="s">
         <v>322</v>
@@ -4193,22 +4193,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="H19" t="s">
         <v>322</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
@@ -4231,10 +4231,10 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H20" t="s">
         <v>322</v>
@@ -4245,10 +4245,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C21" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D21" t="s">
         <v>225</v>
@@ -4271,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C22" t="s">
         <v>324</v>
@@ -4283,10 +4283,10 @@
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="G22" s="52" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="H22" t="s">
         <v>322</v>
@@ -4300,7 +4300,7 @@
         <v>220</v>
       </c>
       <c r="C23" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D23" t="s">
         <v>227</v>
@@ -4323,10 +4323,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C24" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D24" t="s">
         <v>313</v>
@@ -4338,7 +4338,7 @@
         <v>277</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H24" t="s">
         <v>322</v>
@@ -4352,7 +4352,7 @@
         <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D25" t="s">
         <v>226</v>
@@ -4375,22 +4375,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C26" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D26" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="H26" t="s">
         <v>322</v>
@@ -4439,10 +4439,10 @@
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G28" s="52" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H28" t="s">
         <v>322</v>
@@ -4453,7 +4453,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C29" t="s">
         <v>241</v>
@@ -4465,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="G29" s="52" t="s">
         <v>265</v>
@@ -4505,7 +4505,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C31" t="s">
         <v>240</v>
@@ -4520,7 +4520,7 @@
         <v>289</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H31" t="s">
         <v>322</v>
@@ -4531,10 +4531,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D32" t="s">
         <v>314</v>
@@ -4557,22 +4557,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C33" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D33" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>412</v>
+        <v>644</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="H33" t="s">
         <v>322</v>
@@ -4583,7 +4583,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="C34" t="s">
         <v>222</v>
@@ -4598,7 +4598,7 @@
         <v>298</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H34" t="s">
         <v>322</v>
@@ -4609,7 +4609,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C35" t="s">
         <v>223</v>
@@ -4638,7 +4638,7 @@
         <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D36" t="s">
         <v>214</v>
@@ -4661,7 +4661,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C37" t="s">
         <v>221</v>
@@ -4687,7 +4687,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
@@ -4702,7 +4702,7 @@
         <v>272</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H38" t="s">
         <v>322</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5218,7 +5218,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5232,7 +5232,7 @@
         <v>305</v>
       </c>
       <c r="C4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D4" t="s">
         <v>285</v>
@@ -5246,7 +5246,7 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D5" t="s">
         <v>276</v>
@@ -5260,7 +5260,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D6" t="s">
         <v>271</v>
@@ -5271,13 +5271,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5285,13 +5285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D8" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5299,13 +5299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D9" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5313,13 +5313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D10" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5327,13 +5327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C11" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D11" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5341,13 +5341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C12" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D12" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5355,18 +5355,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" t="s">
         <v>406</v>
       </c>
-      <c r="C13" t="s">
-        <v>407</v>
-      </c>
       <c r="D13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5374,13 +5374,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D15" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5388,13 +5388,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C16" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5402,13 +5402,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C17" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D17" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5416,13 +5416,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C18" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5430,13 +5430,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D19" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5444,13 +5444,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C20" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5458,13 +5458,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C21" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D21" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5472,13 +5472,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C22" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D22" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5486,13 +5486,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D23" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C24" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D24" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5514,13 +5514,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C25" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D25" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5528,13 +5528,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
+        <v>542</v>
+      </c>
+      <c r="C26" t="s">
+        <v>410</v>
+      </c>
+      <c r="D26" t="s">
         <v>544</v>
-      </c>
-      <c r="C26" t="s">
-        <v>411</v>
-      </c>
-      <c r="D26" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5542,13 +5542,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D27" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5556,13 +5556,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C28" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D28" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5570,13 +5570,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C29" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D29" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5759,7 +5759,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5954,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6072,21 +6072,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6094,21 +6094,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6116,123 +6116,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>556</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>558</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6240,133 +6240,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>
@@ -6387,16 +6387,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6405,10 +6405,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6416,7 +6416,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>185</v>
@@ -6427,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6438,10 +6438,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -6449,10 +6449,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -6460,10 +6460,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6471,10 +6471,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -6482,10 +6482,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -6493,10 +6493,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="291" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5EF43AE-4C80-4FF9-9CB1-042EA4E45BA0}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5892E137-5B1A-4773-8A94-0716C8A90023}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2024,15 +2024,9 @@
 Healthcare leader with 25+ years in management and academics. Oversees seven institutions including a 1,700-bed hospital. Ph.D. in Management (IIM Ahmedabad). President, AHPI Kerala Chapter; Board Member, CHAI Kerala.</t>
   </si>
   <si>
-    <t>Fr. Viju Painadath</t>
-  </si>
-  <si>
     <t>Pro Vice Chancellor, Christ</t>
   </si>
   <si>
-    <t>images/Speakers/Dr Fr Viju P D.jpg</t>
-  </si>
-  <si>
     <t>Sr. Dr. Helen Mary, SAB, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
   </si>
   <si>
@@ -2052,6 +2046,12 @@
   </si>
   <si>
     <t>images/Speakers/Fr.Saju.jpg</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Viju P. Devassy</t>
+  </si>
+  <si>
+    <t>images/Speakers/Fr Viju (1).png</t>
   </si>
 </sst>
 </file>
@@ -3444,7 +3444,7 @@
         <v>529</v>
       </c>
       <c r="E8" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3452,16 +3452,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C9" t="s">
         <v>636</v>
-      </c>
-      <c r="C9" t="s">
-        <v>637</v>
       </c>
       <c r="D9" t="s">
         <v>529</v>
       </c>
       <c r="E9" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4063,10 +4063,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C14" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D14" t="s">
         <v>442</v>
@@ -4075,10 +4075,10 @@
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G14" s="52" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="H14" t="s">
         <v>322</v>
@@ -4569,7 +4569,7 @@
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G33" s="52" t="s">
         <v>635</v>
@@ -4598,7 +4598,7 @@
         <v>298</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H34" t="s">
         <v>322</v>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5892E137-5B1A-4773-8A94-0716C8A90023}"/>
+  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5079FE0D-4A6F-4DB2-B6FC-9B32C59DD113}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1090,9 +1090,6 @@
     <t>New Education Policy</t>
   </si>
   <si>
-    <t xml:space="preserve">Fr. Saju Chackalakkal </t>
-  </si>
-  <si>
     <t>images/Speakers/Sr. Jane.jpg</t>
   </si>
   <si>
@@ -2052,6 +2049,9 @@
   </si>
   <si>
     <t>images/Speakers/Fr Viju (1).png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fr. Saju Chackalackal </t>
   </si>
 </sst>
 </file>
@@ -2918,7 +2918,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2929,7 +2929,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2951,7 +2951,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -2966,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2974,36 +2974,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D10" t="s">
         <v>322</v>
       </c>
       <c r="E10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H10" t="s">
         <v>323</v>
       </c>
       <c r="I10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H11" t="s">
         <v>323</v>
       </c>
       <c r="I11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3011,19 +3011,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>329</v>
-      </c>
       <c r="E12" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H12" t="s">
         <v>323</v>
       </c>
       <c r="I12" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3031,186 +3031,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C13" t="s">
         <v>355</v>
-      </c>
-      <c r="C13" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" t="s">
         <v>357</v>
-      </c>
-      <c r="C14" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B15" t="s">
+        <v>358</v>
+      </c>
+      <c r="C15" t="s">
         <v>359</v>
-      </c>
-      <c r="C15" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>329</v>
+      </c>
+      <c r="B16" t="s">
+        <v>360</v>
+      </c>
+      <c r="C16" t="s">
         <v>330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C16" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>339</v>
+      </c>
+      <c r="B17" t="s">
+        <v>376</v>
+      </c>
+      <c r="C17" t="s">
         <v>340</v>
-      </c>
-      <c r="B17" t="s">
-        <v>377</v>
-      </c>
-      <c r="C17" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>335</v>
+      </c>
+      <c r="B18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C18" t="s">
         <v>336</v>
-      </c>
-      <c r="B18" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B19" t="s">
+        <v>362</v>
+      </c>
+      <c r="C19" t="s">
         <v>363</v>
-      </c>
-      <c r="C19" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C20" t="s">
         <v>338</v>
-      </c>
-      <c r="B20" t="s">
-        <v>365</v>
-      </c>
-      <c r="C20" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C21" t="s">
         <v>332</v>
-      </c>
-      <c r="B21" t="s">
-        <v>366</v>
-      </c>
-      <c r="C21" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" t="s">
+        <v>366</v>
+      </c>
+      <c r="C22" t="s">
         <v>334</v>
-      </c>
-      <c r="B22" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B23" t="s">
+        <v>367</v>
+      </c>
+      <c r="C23" t="s">
         <v>368</v>
-      </c>
-      <c r="C23" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>345</v>
+      </c>
+      <c r="B24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C24" t="s">
         <v>346</v>
-      </c>
-      <c r="B24" t="s">
-        <v>370</v>
-      </c>
-      <c r="C24" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B25" t="s">
+        <v>370</v>
+      </c>
+      <c r="C25" t="s">
         <v>371</v>
-      </c>
-      <c r="C25" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B26" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" t="s">
         <v>373</v>
-      </c>
-      <c r="C26" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B27" t="s">
+        <v>374</v>
+      </c>
+      <c r="C27" t="s">
         <v>375</v>
-      </c>
-      <c r="C27" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>341</v>
+      </c>
+      <c r="B28" t="s">
+        <v>487</v>
+      </c>
+      <c r="C28" t="s">
         <v>342</v>
-      </c>
-      <c r="B28" t="s">
-        <v>488</v>
-      </c>
-      <c r="C28" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" t="s">
+        <v>488</v>
+      </c>
+      <c r="C29" t="s">
         <v>344</v>
-      </c>
-      <c r="B29" t="s">
-        <v>489</v>
-      </c>
-      <c r="C29" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3333,16 +3333,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3350,16 +3350,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C3" t="s">
         <v>382</v>
       </c>
-      <c r="C3" t="s">
-        <v>383</v>
-      </c>
       <c r="D3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3367,16 +3367,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C4" t="s">
         <v>414</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>519</v>
+      </c>
+      <c r="E4" t="s">
         <v>415</v>
-      </c>
-      <c r="D4" t="s">
-        <v>520</v>
-      </c>
-      <c r="E4" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3384,16 +3384,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C5" t="s">
+        <v>520</v>
+      </c>
+      <c r="D5" t="s">
         <v>521</v>
       </c>
-      <c r="D5" t="s">
-        <v>522</v>
-      </c>
       <c r="E5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3401,16 +3401,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" t="s">
         <v>385</v>
       </c>
-      <c r="C6" t="s">
-        <v>386</v>
-      </c>
       <c r="D6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3418,16 +3418,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D7" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3435,16 +3435,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>326</v>
+        <v>645</v>
       </c>
       <c r="C8" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3452,16 +3452,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
+        <v>643</v>
+      </c>
+      <c r="C9" t="s">
+        <v>635</v>
+      </c>
+      <c r="D9" t="s">
+        <v>528</v>
+      </c>
+      <c r="E9" t="s">
         <v>644</v>
-      </c>
-      <c r="C9" t="s">
-        <v>636</v>
-      </c>
-      <c r="D9" t="s">
-        <v>529</v>
-      </c>
-      <c r="E9" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3469,16 +3469,16 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -3486,13 +3486,13 @@
         <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E11" t="s">
         <v>163</v>
@@ -3503,16 +3503,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>526</v>
+      </c>
+      <c r="C12" t="s">
         <v>527</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>528</v>
       </c>
-      <c r="D12" t="s">
-        <v>529</v>
-      </c>
       <c r="E12" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3520,13 +3520,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C13" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
@@ -3537,16 +3537,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D14" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -3591,13 +3591,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3605,13 +3605,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3619,13 +3619,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C4" t="s">
         <v>394</v>
       </c>
-      <c r="C4" t="s">
-        <v>395</v>
-      </c>
       <c r="E4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3633,13 +3633,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E5" t="s">
         <v>417</v>
-      </c>
-      <c r="E5" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3647,13 +3647,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3661,13 +3661,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3675,13 +3675,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C8" t="s">
+        <v>510</v>
+      </c>
+      <c r="E8" t="s">
         <v>511</v>
-      </c>
-      <c r="E8" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3689,13 +3689,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C9" t="s">
+        <v>421</v>
+      </c>
+      <c r="E9" t="s">
         <v>422</v>
-      </c>
-      <c r="E9" t="s">
-        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -3751,22 +3751,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C2" t="s">
         <v>604</v>
       </c>
-      <c r="C2" t="s">
-        <v>605</v>
-      </c>
       <c r="D2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2" t="s">
         <v>322</v>
@@ -3777,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C4" t="s">
         <v>221</v>
@@ -3818,7 +3818,7 @@
         <v>297</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H4" t="s">
         <v>322</v>
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3844,7 +3844,7 @@
         <v>300</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H5" t="s">
         <v>322</v>
@@ -3858,7 +3858,7 @@
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -3881,13 +3881,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
@@ -3896,7 +3896,7 @@
         <v>269</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H7" t="s">
         <v>322</v>
@@ -3907,22 +3907,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H8" t="s">
         <v>322</v>
@@ -3933,22 +3933,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
+        <v>600</v>
+      </c>
+      <c r="G9" s="52" t="s">
         <v>601</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>602</v>
       </c>
       <c r="H9" t="s">
         <v>322</v>
@@ -3959,10 +3959,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D10" t="s">
         <v>231</v>
@@ -3974,7 +3974,7 @@
         <v>280</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H10" t="s">
         <v>322</v>
@@ -3988,7 +3988,7 @@
         <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -3997,7 +3997,7 @@
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>262</v>
@@ -4026,7 +4026,7 @@
         <v>282</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H12" t="s">
         <v>322</v>
@@ -4040,7 +4040,7 @@
         <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D13" t="s">
         <v>235</v>
@@ -4063,22 +4063,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C14" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
+        <v>637</v>
+      </c>
+      <c r="G14" s="52" t="s">
         <v>638</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>639</v>
       </c>
       <c r="H14" t="s">
         <v>322</v>
@@ -4089,10 +4089,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
@@ -4156,7 +4156,7 @@
         <v>294</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H17" t="s">
         <v>322</v>
@@ -4193,22 +4193,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H19" t="s">
         <v>322</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
@@ -4231,10 +4231,10 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H20" t="s">
         <v>322</v>
@@ -4245,10 +4245,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>444</v>
+      </c>
+      <c r="C21" t="s">
         <v>445</v>
-      </c>
-      <c r="C21" t="s">
-        <v>446</v>
       </c>
       <c r="D21" t="s">
         <v>225</v>
@@ -4271,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C22" t="s">
         <v>324</v>
@@ -4283,10 +4283,10 @@
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G22" s="52" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H22" t="s">
         <v>322</v>
@@ -4300,7 +4300,7 @@
         <v>220</v>
       </c>
       <c r="C23" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D23" t="s">
         <v>227</v>
@@ -4323,10 +4323,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C24" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D24" t="s">
         <v>313</v>
@@ -4338,7 +4338,7 @@
         <v>277</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H24" t="s">
         <v>322</v>
@@ -4352,7 +4352,7 @@
         <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D25" t="s">
         <v>226</v>
@@ -4375,22 +4375,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C26" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="D26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H26" t="s">
         <v>322</v>
@@ -4439,10 +4439,10 @@
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G28" s="52" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H28" t="s">
         <v>322</v>
@@ -4453,7 +4453,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C29" t="s">
         <v>241</v>
@@ -4465,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G29" s="52" t="s">
         <v>265</v>
@@ -4505,7 +4505,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C31" t="s">
         <v>240</v>
@@ -4520,7 +4520,7 @@
         <v>289</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H31" t="s">
         <v>322</v>
@@ -4531,10 +4531,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D32" t="s">
         <v>314</v>
@@ -4557,22 +4557,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>632</v>
+      </c>
+      <c r="C33" t="s">
         <v>633</v>
       </c>
-      <c r="C33" t="s">
-        <v>634</v>
-      </c>
       <c r="D33" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H33" t="s">
         <v>322</v>
@@ -4583,7 +4583,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C34" t="s">
         <v>222</v>
@@ -4598,7 +4598,7 @@
         <v>298</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H34" t="s">
         <v>322</v>
@@ -4609,7 +4609,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C35" t="s">
         <v>223</v>
@@ -4638,7 +4638,7 @@
         <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D36" t="s">
         <v>214</v>
@@ -4661,7 +4661,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C37" t="s">
         <v>221</v>
@@ -4687,7 +4687,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
@@ -4702,7 +4702,7 @@
         <v>272</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H38" t="s">
         <v>322</v>
@@ -5207,7 +5207,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5218,7 +5218,7 @@
         <v>185</v>
       </c>
       <c r="C3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5232,7 +5232,7 @@
         <v>305</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D4" t="s">
         <v>285</v>
@@ -5246,7 +5246,7 @@
         <v>175</v>
       </c>
       <c r="C5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
         <v>276</v>
@@ -5260,7 +5260,7 @@
         <v>181</v>
       </c>
       <c r="C6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D6" t="s">
         <v>271</v>
@@ -5271,13 +5271,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5285,13 +5285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C8" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D8" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5299,13 +5299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5313,13 +5313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5327,13 +5327,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C11" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5341,13 +5341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>492</v>
+      </c>
+      <c r="C12" t="s">
+        <v>405</v>
+      </c>
+      <c r="D12" t="s">
         <v>493</v>
-      </c>
-      <c r="C12" t="s">
-        <v>406</v>
-      </c>
-      <c r="D12" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5355,18 +5355,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C13" t="s">
         <v>405</v>
       </c>
-      <c r="C13" t="s">
-        <v>406</v>
-      </c>
       <c r="D13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5374,13 +5374,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5388,13 +5388,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5402,13 +5402,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C17" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5416,13 +5416,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C18" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D18" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5430,13 +5430,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C19" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5444,13 +5444,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5458,13 +5458,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C21" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D21" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5472,13 +5472,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C22" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5486,13 +5486,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
+        <v>485</v>
+      </c>
+      <c r="C24" t="s">
+        <v>409</v>
+      </c>
+      <c r="D24" t="s">
         <v>486</v>
-      </c>
-      <c r="C24" t="s">
-        <v>410</v>
-      </c>
-      <c r="D24" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5514,13 +5514,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
+        <v>490</v>
+      </c>
+      <c r="C25" t="s">
+        <v>409</v>
+      </c>
+      <c r="D25" t="s">
         <v>491</v>
-      </c>
-      <c r="C25" t="s">
-        <v>410</v>
-      </c>
-      <c r="D25" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5528,13 +5528,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D26" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5542,13 +5542,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D27" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5556,13 +5556,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C28" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D28" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5570,13 +5570,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C29" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D29" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -5759,7 +5759,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5954,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6072,21 +6072,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>549</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>550</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6094,21 +6094,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6116,123 +6116,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>555</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>556</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="22" t="s">
         <v>557</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6240,133 +6240,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C17" s="31" t="s">
+        <v>578</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>579</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -6387,16 +6387,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
+        <v>610</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>611</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6405,10 +6405,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
+        <v>613</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>614</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6416,7 +6416,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>185</v>
@@ -6427,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
+        <v>616</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>617</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6438,10 +6438,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>619</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -6449,10 +6449,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>620</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>621</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -6460,10 +6460,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6471,10 +6471,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -6482,10 +6482,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
+        <v>624</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>625</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -6493,10 +6493,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="50" t="s">
+        <v>626</v>
+      </c>
+      <c r="C11" s="50" t="s">
         <v>627</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="294" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5079FE0D-4A6F-4DB2-B6FC-9B32C59DD113}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72BE2557-47B6-44F5-8A28-15BC5915D497}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -1402,9 +1402,6 @@
     <t>Spped</t>
   </si>
   <si>
-    <t>CERRA</t>
-  </si>
-  <si>
     <t>A Synodal Path toward Authentic Consecrated Living: Perceived Stress and the Role of Social Support &amp; Accompaniment among Perpetually Professed Sisters in India</t>
   </si>
   <si>
@@ -2052,6 +2049,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fr. Saju Chackalackal </t>
+  </si>
+  <si>
+    <t>Excecutive Director CERRA</t>
   </si>
 </sst>
 </file>
@@ -3196,7 +3196,7 @@
         <v>341</v>
       </c>
       <c r="B28" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C28" t="s">
         <v>342</v>
@@ -3207,7 +3207,7 @@
         <v>343</v>
       </c>
       <c r="B29" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C29" t="s">
         <v>344</v>
@@ -3339,7 +3339,7 @@
         <v>383</v>
       </c>
       <c r="D2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E2" t="s">
         <v>386</v>
@@ -3356,7 +3356,7 @@
         <v>382</v>
       </c>
       <c r="D3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E3" t="s">
         <v>388</v>
@@ -3373,7 +3373,7 @@
         <v>414</v>
       </c>
       <c r="D4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E4" t="s">
         <v>415</v>
@@ -3384,16 +3384,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C5" t="s">
+        <v>519</v>
+      </c>
+      <c r="D5" t="s">
         <v>520</v>
       </c>
-      <c r="D5" t="s">
-        <v>521</v>
-      </c>
       <c r="E5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3407,7 +3407,7 @@
         <v>385</v>
       </c>
       <c r="D6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E6" t="s">
         <v>389</v>
@@ -3418,13 +3418,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D7" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E7" t="s">
         <v>398</v>
@@ -3435,16 +3435,16 @@
         <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C8" t="s">
         <v>392</v>
       </c>
       <c r="D8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3452,16 +3452,16 @@
         <v>191</v>
       </c>
       <c r="B9" t="s">
+        <v>642</v>
+      </c>
+      <c r="C9" t="s">
+        <v>634</v>
+      </c>
+      <c r="D9" t="s">
+        <v>527</v>
+      </c>
+      <c r="E9" t="s">
         <v>643</v>
-      </c>
-      <c r="C9" t="s">
-        <v>635</v>
-      </c>
-      <c r="D9" t="s">
-        <v>528</v>
-      </c>
-      <c r="E9" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3469,13 +3469,13 @@
         <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C10" t="s">
         <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E10" t="s">
         <v>390</v>
@@ -3486,13 +3486,13 @@
         <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E11" t="s">
         <v>163</v>
@@ -3503,16 +3503,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>525</v>
+      </c>
+      <c r="C12" t="s">
         <v>526</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>527</v>
       </c>
-      <c r="D12" t="s">
-        <v>528</v>
-      </c>
       <c r="E12" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3520,13 +3520,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E13" t="s">
         <v>166</v>
@@ -3540,10 +3540,10 @@
         <v>378</v>
       </c>
       <c r="C14" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D14" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E14" t="s">
         <v>387</v>
@@ -3591,7 +3591,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C2" t="s">
         <v>396</v>
@@ -3633,7 +3633,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C5" t="s">
         <v>416</v>
@@ -3647,10 +3647,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C6" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E6" t="s">
         <v>418</v>
@@ -3661,10 +3661,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C7" t="s">
-        <v>430</v>
+        <v>645</v>
       </c>
       <c r="E7" t="s">
         <v>419</v>
@@ -3675,13 +3675,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C8" t="s">
+        <v>509</v>
+      </c>
+      <c r="E8" t="s">
         <v>510</v>
-      </c>
-      <c r="E8" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3689,7 +3689,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C9" t="s">
         <v>421</v>
@@ -3751,22 +3751,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C2" t="s">
         <v>603</v>
       </c>
-      <c r="C2" t="s">
-        <v>604</v>
-      </c>
       <c r="D2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2" t="s">
         <v>322</v>
@@ -3777,7 +3777,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C3" t="s">
         <v>205</v>
@@ -3803,7 +3803,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C4" t="s">
         <v>221</v>
@@ -3818,7 +3818,7 @@
         <v>297</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H4" t="s">
         <v>322</v>
@@ -3829,7 +3829,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C5" t="s">
         <v>204</v>
@@ -3844,7 +3844,7 @@
         <v>300</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H5" t="s">
         <v>322</v>
@@ -3858,7 +3858,7 @@
         <v>202</v>
       </c>
       <c r="C6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D6" t="s">
         <v>211</v>
@@ -3881,13 +3881,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
         <v>203</v>
       </c>
       <c r="D7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
@@ -3896,7 +3896,7 @@
         <v>269</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H7" t="s">
         <v>322</v>
@@ -3913,16 +3913,16 @@
         <v>407</v>
       </c>
       <c r="D8" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H8" t="s">
         <v>322</v>
@@ -3933,22 +3933,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
+        <v>599</v>
+      </c>
+      <c r="G9" s="52" t="s">
         <v>600</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>601</v>
       </c>
       <c r="H9" t="s">
         <v>322</v>
@@ -3959,10 +3959,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C10" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D10" t="s">
         <v>231</v>
@@ -3974,7 +3974,7 @@
         <v>280</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H10" t="s">
         <v>322</v>
@@ -3988,7 +3988,7 @@
         <v>229</v>
       </c>
       <c r="C11" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D11" t="s">
         <v>234</v>
@@ -4026,7 +4026,7 @@
         <v>282</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H12" t="s">
         <v>322</v>
@@ -4040,7 +4040,7 @@
         <v>230</v>
       </c>
       <c r="C13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D13" t="s">
         <v>235</v>
@@ -4063,22 +4063,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C14" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
+        <v>636</v>
+      </c>
+      <c r="G14" s="52" t="s">
         <v>637</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>638</v>
       </c>
       <c r="H14" t="s">
         <v>322</v>
@@ -4089,10 +4089,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C15" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D15" t="s">
         <v>253</v>
@@ -4156,7 +4156,7 @@
         <v>294</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H17" t="s">
         <v>322</v>
@@ -4193,22 +4193,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H19" t="s">
         <v>322</v>
@@ -4219,7 +4219,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C20" t="s">
         <v>203</v>
@@ -4234,7 +4234,7 @@
         <v>398</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H20" t="s">
         <v>322</v>
@@ -4245,10 +4245,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>443</v>
+      </c>
+      <c r="C21" t="s">
         <v>444</v>
-      </c>
-      <c r="C21" t="s">
-        <v>445</v>
       </c>
       <c r="D21" t="s">
         <v>225</v>
@@ -4271,7 +4271,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C22" t="s">
         <v>324</v>
@@ -4283,10 +4283,10 @@
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G22" s="52" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H22" t="s">
         <v>322</v>
@@ -4300,7 +4300,7 @@
         <v>220</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D23" t="s">
         <v>227</v>
@@ -4323,10 +4323,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C24" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D24" t="s">
         <v>313</v>
@@ -4338,7 +4338,7 @@
         <v>277</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H24" t="s">
         <v>322</v>
@@ -4352,7 +4352,7 @@
         <v>219</v>
       </c>
       <c r="C25" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D25" t="s">
         <v>226</v>
@@ -4375,22 +4375,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C26" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D26" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H26" t="s">
         <v>322</v>
@@ -4439,10 +4439,10 @@
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G28" s="52" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H28" t="s">
         <v>322</v>
@@ -4453,7 +4453,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C29" t="s">
         <v>241</v>
@@ -4505,7 +4505,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C31" t="s">
         <v>240</v>
@@ -4520,7 +4520,7 @@
         <v>289</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H31" t="s">
         <v>322</v>
@@ -4531,10 +4531,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D32" t="s">
         <v>314</v>
@@ -4557,22 +4557,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>631</v>
+      </c>
+      <c r="C33" t="s">
         <v>632</v>
       </c>
-      <c r="C33" t="s">
-        <v>633</v>
-      </c>
       <c r="D33" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H33" t="s">
         <v>322</v>
@@ -4583,7 +4583,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C34" t="s">
         <v>222</v>
@@ -4598,7 +4598,7 @@
         <v>298</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H34" t="s">
         <v>322</v>
@@ -4609,7 +4609,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C35" t="s">
         <v>223</v>
@@ -4638,7 +4638,7 @@
         <v>212</v>
       </c>
       <c r="C36" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D36" t="s">
         <v>214</v>
@@ -4661,7 +4661,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C37" t="s">
         <v>221</v>
@@ -4687,7 +4687,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C38" t="s">
         <v>206</v>
@@ -4702,7 +4702,7 @@
         <v>272</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H38" t="s">
         <v>322</v>
@@ -5277,7 +5277,7 @@
         <v>405</v>
       </c>
       <c r="D7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5285,13 +5285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C8" t="s">
         <v>405</v>
       </c>
       <c r="D8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5305,7 +5305,7 @@
         <v>405</v>
       </c>
       <c r="D9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5319,7 +5319,7 @@
         <v>405</v>
       </c>
       <c r="D10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5333,7 +5333,7 @@
         <v>405</v>
       </c>
       <c r="D11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5341,13 +5341,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C12" t="s">
         <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5361,7 +5361,7 @@
         <v>405</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -5374,13 +5374,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C15" t="s">
         <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5388,13 +5388,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C16" t="s">
         <v>409</v>
       </c>
       <c r="D16" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5402,13 +5402,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C17" t="s">
         <v>409</v>
       </c>
       <c r="D17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5416,13 +5416,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C18" t="s">
         <v>409</v>
       </c>
       <c r="D18" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5430,13 +5430,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C19" t="s">
         <v>409</v>
       </c>
       <c r="D19" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5444,13 +5444,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C20" t="s">
         <v>409</v>
       </c>
       <c r="D20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5458,13 +5458,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C21" t="s">
         <v>409</v>
       </c>
       <c r="D21" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5472,13 +5472,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C22" t="s">
         <v>409</v>
       </c>
       <c r="D22" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5486,13 +5486,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s">
         <v>409</v>
       </c>
       <c r="D23" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5500,13 +5500,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C24" t="s">
         <v>409</v>
       </c>
       <c r="D24" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5514,13 +5514,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C25" t="s">
         <v>409</v>
       </c>
       <c r="D25" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5528,13 +5528,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C26" t="s">
         <v>409</v>
       </c>
       <c r="D26" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5542,13 +5542,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C27" t="s">
         <v>409</v>
       </c>
       <c r="D27" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5556,13 +5556,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C28" t="s">
         <v>409</v>
       </c>
       <c r="D28" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5570,13 +5570,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C29" t="s">
         <v>409</v>
       </c>
       <c r="D29" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -5759,7 +5759,7 @@
         <v>196</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5954,7 +5954,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6072,21 +6072,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>548</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>549</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6094,21 +6094,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6116,123 +6116,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>555</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="22" t="s">
         <v>556</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6240,133 +6240,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C17" s="31" t="s">
+        <v>577</v>
+      </c>
+      <c r="D17" s="32" t="s">
         <v>578</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6387,16 +6387,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
+        <v>609</v>
+      </c>
+      <c r="C1" s="44" t="s">
         <v>610</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6405,10 +6405,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
+        <v>612</v>
+      </c>
+      <c r="C3" s="44" t="s">
         <v>613</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6416,7 +6416,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>185</v>
@@ -6427,10 +6427,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
+        <v>615</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>616</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6438,10 +6438,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
+        <v>617</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>618</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -6449,10 +6449,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
+        <v>619</v>
+      </c>
+      <c r="C7" s="44" t="s">
         <v>620</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -6460,10 +6460,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6471,10 +6471,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -6482,10 +6482,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
+        <v>623</v>
+      </c>
+      <c r="C10" s="44" t="s">
         <v>624</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -6493,10 +6493,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="50" t="s">
+        <v>625</v>
+      </c>
+      <c r="C11" s="50" t="s">
         <v>626</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>627</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72BE2557-47B6-44F5-8A28-15BC5915D497}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB23C6CB-ADD6-4804-A20B-621896259FD1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="649">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -559,9 +559,6 @@
     <t>images/Council/Dr. Sr. Aruna Jose CHF.jpg</t>
   </si>
   <si>
-    <t>Sr. Audrey D'Souza</t>
-  </si>
-  <si>
     <t>Secretary</t>
   </si>
   <si>
@@ -571,9 +568,6 @@
     <t>images/Council/Sr. Audrey D'Souza.jpg</t>
   </si>
   <si>
-    <t>Sr. Celine Fathima</t>
-  </si>
-  <si>
     <t>Treasurer</t>
   </si>
   <si>
@@ -593,9 +587,6 @@
   </si>
   <si>
     <t>images/Council/Sr. Maria Goretti.jpg</t>
-  </si>
-  <si>
-    <t>Dr. D.J. Margaret FMS</t>
   </si>
   <si>
     <t>Salesian Sister</t>
@@ -2052,6 +2043,24 @@
   </si>
   <si>
     <t>Excecutive Director CERRA</t>
+  </si>
+  <si>
+    <t>Dr. D.J. Margaret FMA</t>
+  </si>
+  <si>
+    <t>Sr. Celine Fathima SSAM</t>
+  </si>
+  <si>
+    <t>Sr. Audrey D'Souza FDCC</t>
+  </si>
+  <si>
+    <t>Mr. Alessandro Cassinerio</t>
+  </si>
+  <si>
+    <t>images/Speakers/Mr. Alessandro Cassinerio.png</t>
+  </si>
+  <si>
+    <t>Grants Program Manager, Anna Trust</t>
   </si>
 </sst>
 </file>
@@ -2918,7 +2927,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2929,7 +2938,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2951,13 +2960,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>0</v>
@@ -2966,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2974,36 +2983,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B10" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E10" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I11" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3011,19 +3020,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H12" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I12" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3031,186 +3040,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C14" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B15" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C15" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B16" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C17" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B18" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C18" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B19" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C19" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B20" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C20" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B22" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B23" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C23" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B24" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C24" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B25" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C25" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B26" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C26" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C27" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B28" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C28" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B29" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -3333,16 +3342,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" t="s">
         <v>380</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E2" t="s">
         <v>383</v>
-      </c>
-      <c r="D2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3350,16 +3359,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3367,16 +3376,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3384,16 +3393,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E5" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3401,16 +3410,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E6" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3418,84 +3427,84 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="C7" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D7" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D8" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E8" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C9" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D9" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="D10" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C11" t="s">
         <v>521</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>524</v>
       </c>
-      <c r="D11" t="s">
-        <v>527</v>
-      </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -3503,16 +3512,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="C12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D12" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E12" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3520,16 +3529,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C13" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" t="s">
         <v>524</v>
       </c>
-      <c r="D13" t="s">
-        <v>527</v>
-      </c>
       <c r="E13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -3537,16 +3546,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E14" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -3561,7 +3570,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F408643-EE4E-4A6C-A3B2-9DA3CE87AD80}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.58203125" bestFit="1" customWidth="1"/>
@@ -3591,13 +3600,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3605,13 +3614,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C3" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3619,13 +3628,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" t="s">
         <v>394</v>
-      </c>
-      <c r="E4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3633,13 +3642,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E5" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3647,13 +3656,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E6" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3661,13 +3670,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C7" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E7" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3675,13 +3684,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C8" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E8" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3689,13 +3698,27 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E9" t="s">
-        <v>422</v>
+        <v>419</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>646</v>
+      </c>
+      <c r="C10" t="s">
+        <v>648</v>
+      </c>
+      <c r="E10" t="s">
+        <v>647</v>
       </c>
     </row>
   </sheetData>
@@ -3743,7 +3766,7 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3751,25 +3774,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3777,25 +3800,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E3" t="s">
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G3" s="52" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3803,25 +3826,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="C4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E4" t="s">
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="H4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3829,25 +3852,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E5" t="s">
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3855,25 +3878,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E6" t="s">
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3881,25 +3904,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="H7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3907,25 +3930,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3933,25 +3956,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C9" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3959,25 +3982,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="H10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3985,25 +4008,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="D11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4011,25 +4034,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4037,25 +4060,25 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G13" s="52" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H13" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
@@ -4063,25 +4086,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G14" s="52" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="H14" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4089,25 +4112,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C15" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D15" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G15" s="52" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H15" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4115,25 +4138,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D16" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G16" s="52" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H16" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -4141,25 +4164,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C17" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H17" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4167,25 +4190,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C18" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D18" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G18" s="52" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="H18" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4193,25 +4216,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="H19" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4219,25 +4242,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C20" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H20" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4245,25 +4268,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C21" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D21" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="G21" s="52" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="H21" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4271,25 +4294,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C22" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="G22" s="52" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="H22" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4297,25 +4320,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D23" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E23" t="s">
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H23" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4323,25 +4346,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C24" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H24" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4349,25 +4372,25 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D25" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G25" s="52" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H25" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4375,25 +4398,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C26" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D26" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H26" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4401,25 +4424,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G27" s="52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H27" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4427,25 +4450,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D28" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="G28" s="52" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H28" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4453,25 +4476,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C29" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D29" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G29" s="52" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H29" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4479,25 +4502,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D30" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G30" s="52" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H30" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4505,25 +4528,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="H31" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -4531,25 +4554,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G32" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -4557,25 +4580,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C33" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D33" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="H33" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4583,25 +4606,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D34" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E34" t="s">
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="H34" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4609,25 +4632,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D35" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E35" t="s">
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G35" s="52" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H35" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4635,25 +4658,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C36" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D36" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E36" t="s">
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G36" s="52" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4661,25 +4684,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C37" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="G37" s="52" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H37" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4687,25 +4710,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E38" t="s">
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H38" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4719,16 +4742,16 @@
         <v>133</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F39" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G39" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -4736,25 +4759,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E40" t="s">
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G40" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4762,25 +4785,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="G41" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4788,22 +4811,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G42" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -4811,19 +4834,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G43" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -4831,19 +4854,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G44" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -4851,22 +4874,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F45" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G45" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4980,16 +5003,16 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C3" t="s">
         <v>149</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>150</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>151</v>
-      </c>
-      <c r="E3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4997,16 +5020,16 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" t="s">
         <v>153</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>154</v>
-      </c>
-      <c r="D4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5014,16 +5037,16 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D5" t="s">
         <v>157</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>158</v>
-      </c>
-      <c r="D5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E5" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5031,16 +5054,16 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>643</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5048,23 +5071,23 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E2 A7:E7 A6 C6:E6 A5:E5 A4 C4:E4 A3 C3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5096,13 +5119,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5110,13 +5133,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -5124,13 +5147,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5138,13 +5161,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5152,13 +5175,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5166,13 +5189,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5207,7 +5230,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5215,10 +5238,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5229,13 +5252,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5243,13 +5266,13 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5257,13 +5280,13 @@
         <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5271,13 +5294,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5285,13 +5308,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C8" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D8" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5299,13 +5322,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C9" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5313,13 +5336,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>399</v>
+      </c>
+      <c r="C10" t="s">
         <v>402</v>
       </c>
-      <c r="C10" t="s">
-        <v>405</v>
-      </c>
       <c r="D10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5327,13 +5350,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C11" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D11" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5341,13 +5364,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="C12" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D12" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5355,18 +5378,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5374,13 +5397,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D15" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5388,13 +5411,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C16" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D16" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5402,13 +5425,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C17" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D17" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5416,13 +5439,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C18" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5430,13 +5453,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C19" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D19" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5444,13 +5467,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C20" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D20" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5458,13 +5481,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="C21" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D21" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5472,13 +5495,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C22" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D22" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5486,13 +5509,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="C23" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D23" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5500,13 +5523,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C24" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5514,13 +5537,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C25" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D25" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5528,13 +5551,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C26" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D26" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5542,13 +5565,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D27" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5556,13 +5579,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C28" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D28" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5570,13 +5593,13 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C29" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D29" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
   </sheetData>
@@ -5600,16 +5623,16 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s">
         <v>167</v>
-      </c>
-      <c r="C1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E1" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -5617,16 +5640,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" t="s">
         <v>171</v>
-      </c>
-      <c r="C2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5634,16 +5657,16 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5651,13 +5674,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
@@ -5668,13 +5691,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
         <v>128</v>
@@ -5685,13 +5708,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" t="s">
         <v>180</v>
       </c>
-      <c r="C6" t="s">
-        <v>183</v>
-      </c>
       <c r="D6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E6" t="s">
         <v>128</v>
@@ -5702,13 +5725,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E7" t="s">
         <v>128</v>
@@ -5716,16 +5739,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" t="s">
         <v>187</v>
-      </c>
-      <c r="B8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" t="s">
-        <v>190</v>
       </c>
       <c r="E8" t="s">
         <v>128</v>
@@ -5733,16 +5756,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E9" t="s">
         <v>128</v>
@@ -5750,16 +5773,16 @@
     </row>
     <row r="10" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5767,16 +5790,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" t="s">
         <v>197</v>
-      </c>
-      <c r="B11" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" t="s">
-        <v>199</v>
-      </c>
-      <c r="D11" t="s">
-        <v>200</v>
       </c>
       <c r="E11" t="s">
         <v>128</v>
@@ -5954,7 +5977,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6041,7 +6064,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
@@ -6072,21 +6095,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6094,21 +6117,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6116,123 +6139,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6240,133 +6263,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>
@@ -6387,16 +6410,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6405,10 +6428,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6416,10 +6439,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -6427,10 +6450,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6438,10 +6461,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -6449,10 +6472,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -6460,10 +6483,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -6471,10 +6494,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -6482,10 +6505,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -6493,10 +6516,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB23C6CB-ADD6-4804-A20B-621896259FD1}"/>
+  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF851A88-4849-4BA3-88D0-CD74A7DFE102}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <sheet name="Contacts_And_Footer" sheetId="13" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Presenters!$E$1:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">Presenters!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="654">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -796,9 +796,6 @@
     <t>Dr. Pretesh Kiran</t>
   </si>
   <si>
-    <t xml:space="preserve">Pilgrims of Hope in Healing Ministries: The TREASURE Model for Mental Health and Holistic Wellbeing of Women Religious in India </t>
-  </si>
-  <si>
     <t xml:space="preserve">Addressing mental health, burnout, and holistic well-being of sisters in healthcare. </t>
   </si>
   <si>
@@ -811,9 +808,6 @@
     <t xml:space="preserve">Expanding faith-rooted responses to maternal, child, and geriatric health needs. </t>
   </si>
   <si>
-    <t>Compassionate Healing: Consecrated Women as Healers and Caregivers Continuing the Compassionate Mission of Christ.</t>
-  </si>
-  <si>
     <t>Sr. Dr. Doris D Souza</t>
   </si>
   <si>
@@ -1201,12 +1195,6 @@
     <t>Guest Lecturers</t>
   </si>
   <si>
-    <t>Our Presenters</t>
-  </si>
-  <si>
-    <t>Research from our sisters</t>
-  </si>
-  <si>
     <t>Changes the text under "Speakers and Presenters"</t>
   </si>
   <si>
@@ -1295,9 +1283,6 @@
   </si>
   <si>
     <t>images/Speakers/Marco.jpg</t>
-  </si>
-  <si>
-    <t>images/Speakers/Sr. Nirmalini2.jpg</t>
   </si>
   <si>
     <t>images/Speakers/sabrina-wong.jpg</t>
@@ -2009,9 +1994,6 @@
 Healthcare leader with 25+ years in management and academics. Oversees seven institutions including a 1,700-bed hospital. Ph.D. in Management (IIM Ahmedabad). President, AHPI Kerala Chapter; Board Member, CHAI Kerala.</t>
   </si>
   <si>
-    <t>Pro Vice Chancellor, Christ</t>
-  </si>
-  <si>
     <t>Sr. Dr. Helen Mary, SAB, is an Obstetrician and Gynecologist with an MBBS and MD from St. John’s Medical College and has served as Chief Medical Officer at Nirmala Health Centre, Bangalore, since 2002.</t>
   </si>
   <si>
@@ -2033,12 +2015,6 @@
     <t>images/Speakers/Fr.Saju.jpg</t>
   </si>
   <si>
-    <t>Fr. Dr. Viju P. Devassy</t>
-  </si>
-  <si>
-    <t>images/Speakers/Fr Viju (1).png</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fr. Saju Chackalackal </t>
   </si>
   <si>
@@ -2061,6 +2037,45 @@
   </si>
   <si>
     <t>Grants Program Manager, Anna Trust</t>
+  </si>
+  <si>
+    <t>Surprise Surprise</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>Research from Our Presenters</t>
+  </si>
+  <si>
+    <t>“Explore the profiles below - Click on each category to view them.</t>
+  </si>
+  <si>
+    <t>Holistic Care as Vocation, Presence and Meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Treasure Model for Mental Health and Holistic Wellbeing of Women Religious in India </t>
+  </si>
+  <si>
+    <t>Fr. Dr. Joseph C C</t>
+  </si>
+  <si>
+    <t>Vice Chancellor, Christ</t>
+  </si>
+  <si>
+    <t>images/Speakers/Fr. Jseph.jpg</t>
+  </si>
+  <si>
+    <t>Sr. Maneesha</t>
+  </si>
+  <si>
+    <t>images/Volunteers/Sr. Maneesha.jpeg</t>
+  </si>
+  <si>
+    <t>images/Speakers/Marria Nirmalini.png</t>
+  </si>
+  <si>
+    <t>images/Speakers/Sr. Nirmalini.png</t>
   </si>
 </sst>
 </file>
@@ -2927,7 +2942,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2938,7 +2953,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2960,13 +2975,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>0</v>
@@ -2975,7 +2990,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2983,36 +2998,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B10" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E10" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="H10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I10" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H11" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I11" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3020,19 +3035,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E12" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="H12" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I12" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3040,186 +3055,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B15" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B16" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B17" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B18" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C18" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B19" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C19" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B20" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C20" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B21" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C21" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B22" t="s">
-        <v>363</v>
+        <v>643</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B23" t="s">
-        <v>364</v>
+        <v>644</v>
       </c>
       <c r="C23" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B24" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C24" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B25" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C25" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B26" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C26" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B27" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C27" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B28" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C28" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B29" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C29" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -3342,16 +3357,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3359,16 +3374,16 @@
         <v>40</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="D3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3376,16 +3391,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D4" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E4" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3393,16 +3408,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C5" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D5" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E5" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -3410,16 +3425,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" t="s">
+        <v>509</v>
+      </c>
+      <c r="E6" t="s">
         <v>382</v>
-      </c>
-      <c r="D6" t="s">
-        <v>514</v>
-      </c>
-      <c r="E6" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3427,115 +3442,115 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C7" t="s">
+        <v>431</v>
+      </c>
+      <c r="D7" t="s">
+        <v>537</v>
+      </c>
+      <c r="E7" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>647</v>
+      </c>
+      <c r="C8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D8" t="s">
         <v>519</v>
       </c>
-      <c r="C7" t="s">
-        <v>436</v>
-      </c>
-      <c r="D7" t="s">
-        <v>542</v>
-      </c>
-      <c r="E7" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="B8" t="s">
-        <v>641</v>
-      </c>
-      <c r="C8" t="s">
-        <v>389</v>
-      </c>
-      <c r="D8" t="s">
-        <v>524</v>
-      </c>
       <c r="E8" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>188</v>
+      <c r="A9" s="3">
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C9" t="s">
-        <v>631</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E9" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B10" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C10" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D10" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E10" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C11" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D11" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>11</v>
+      <c r="A12" s="3" t="s">
+        <v>194</v>
       </c>
       <c r="B12" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="C12" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E12" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D13" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E13" t="s">
         <v>163</v>
@@ -3543,19 +3558,19 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C14" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="D14" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="E14" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3600,13 +3615,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3614,13 +3629,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3628,13 +3643,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E4" t="s">
         <v>390</v>
-      </c>
-      <c r="C4" t="s">
-        <v>391</v>
-      </c>
-      <c r="E4" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3642,13 +3657,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3656,13 +3671,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C6" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
@@ -3670,13 +3685,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="43" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C7" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E7" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3684,13 +3699,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="E8" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3698,13 +3713,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C9" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="E9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3712,13 +3727,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="C10" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E10" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -3766,7 +3781,7 @@
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3774,25 +3789,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C2" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D2" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3800,7 +3815,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -3812,13 +3827,13 @@
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G3" s="52" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3826,7 +3841,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C4" t="s">
         <v>218</v>
@@ -3838,13 +3853,13 @@
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G4" s="52" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="H4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3852,7 +3867,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C5" t="s">
         <v>201</v>
@@ -3864,13 +3879,13 @@
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="H5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3881,7 +3896,7 @@
         <v>199</v>
       </c>
       <c r="C6" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D6" t="s">
         <v>208</v>
@@ -3890,13 +3905,13 @@
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G6" s="52" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3904,25 +3919,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C7" t="s">
         <v>200</v>
       </c>
       <c r="D7" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="H7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3930,25 +3945,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C8" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D8" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="G8" s="52" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3956,25 +3971,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C9" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D9" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G9" s="52" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="H9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3982,25 +3997,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C10" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>646</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G10" s="52" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="H10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4011,22 +4026,22 @@
         <v>226</v>
       </c>
       <c r="C11" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="D11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G11" s="52" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H11" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4034,25 +4049,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C12" t="s">
         <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>233</v>
+        <v>645</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="H12" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4063,22 +4078,22 @@
         <v>227</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G13" s="52" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
@@ -4086,25 +4101,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C14" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="D14" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="G14" s="52" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="H14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4112,25 +4127,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="C15" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D15" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G15" s="52" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H15" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4138,25 +4153,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>311</v>
+      </c>
+      <c r="C16" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" t="s">
         <v>313</v>
-      </c>
-      <c r="C16" t="s">
-        <v>248</v>
-      </c>
-      <c r="D16" t="s">
-        <v>315</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G16" s="52" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H16" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -4164,25 +4179,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C17" t="s">
         <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G17" s="52" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="H17" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4190,25 +4205,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" t="s">
         <v>247</v>
       </c>
-      <c r="C18" t="s">
-        <v>249</v>
-      </c>
       <c r="D18" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G18" s="52" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4216,25 +4231,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="G19" s="52" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="H19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4242,7 +4257,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
         <v>200</v>
@@ -4254,13 +4269,13 @@
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>395</v>
+        <v>652</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="H20" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4268,10 +4283,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C21" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="D21" t="s">
         <v>222</v>
@@ -4280,13 +4295,13 @@
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G21" s="52" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H21" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4294,25 +4309,25 @@
         <v>21</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C22" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D22" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G22" s="52" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="H22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4323,7 +4338,7 @@
         <v>217</v>
       </c>
       <c r="C23" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D23" t="s">
         <v>224</v>
@@ -4332,13 +4347,13 @@
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G23" s="52" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H23" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4346,25 +4361,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C24" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="D24" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G24" s="52" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="H24" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4375,7 +4390,7 @@
         <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D25" t="s">
         <v>223</v>
@@ -4384,13 +4399,13 @@
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G25" s="52" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H25" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4398,25 +4413,25 @@
         <v>25</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C26" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D26" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="G26" s="52" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="H26" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4424,25 +4439,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
         <v>200</v>
       </c>
       <c r="D27" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G27" s="52" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H27" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4450,25 +4465,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G28" s="52" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="H28" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4476,25 +4491,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C29" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D29" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G29" s="52" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H29" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4502,25 +4517,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C30" t="s">
         <v>203</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G30" s="52" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H30" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4528,25 +4543,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="C31" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D31" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G31" s="52" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H31" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -4554,25 +4569,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D32" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G32" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -4580,25 +4595,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="C33" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="D33" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="G33" s="52" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="H33" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4606,7 +4621,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C34" t="s">
         <v>219</v>
@@ -4618,13 +4633,13 @@
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G34" s="52" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="H34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4632,7 +4647,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="C35" t="s">
         <v>220</v>
@@ -4644,13 +4659,13 @@
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G35" s="52" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H35" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4661,7 +4676,7 @@
         <v>209</v>
       </c>
       <c r="C36" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D36" t="s">
         <v>211</v>
@@ -4670,13 +4685,13 @@
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G36" s="52" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H36" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4684,7 +4699,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C37" t="s">
         <v>218</v>
@@ -4696,13 +4711,13 @@
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G37" s="52" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H37" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4710,7 +4725,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C38" t="s">
         <v>203</v>
@@ -4722,13 +4737,13 @@
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G38" s="52" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="H38" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4745,13 +4760,13 @@
         <v>205</v>
       </c>
       <c r="F39" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G39" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -4759,7 +4774,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
@@ -4771,13 +4786,13 @@
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G40" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4791,19 +4806,19 @@
         <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G41" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4811,22 +4826,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F42" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G42" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -4834,19 +4849,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G43" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -4854,19 +4869,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G44" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
@@ -4874,26 +4889,26 @@
         <v>44</v>
       </c>
       <c r="B45" s="51" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F45" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G45" s="52" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E45" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
+  <autoFilter ref="A1:F45" xr:uid="{00000000-0001-0000-0900-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -5003,7 +5018,7 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C3" t="s">
         <v>149</v>
@@ -5020,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="C4" t="s">
         <v>152</v>
@@ -5054,7 +5069,7 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="C6" t="s">
         <v>156</v>
@@ -5119,13 +5134,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5133,13 +5148,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
         <v>149</v>
       </c>
       <c r="D3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -5147,13 +5162,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>152</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5161,13 +5176,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C5" t="s">
         <v>156</v>
       </c>
       <c r="D5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5175,13 +5190,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C6" t="s">
         <v>156</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5189,13 +5204,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C7" t="s">
         <v>156</v>
       </c>
       <c r="D7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -5206,7 +5221,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE87D73C-0C6D-4F11-B208-F394024872E3}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.58203125" style="3"/>
@@ -5230,7 +5245,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5241,7 +5256,7 @@
         <v>182</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5252,13 +5267,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5269,10 +5284,10 @@
         <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5283,10 +5298,10 @@
         <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5294,13 +5309,13 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D7" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -5308,13 +5323,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="C8" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D8" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -5322,13 +5337,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C9" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D9" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -5336,13 +5351,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D10" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -5350,13 +5365,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D11" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -5364,13 +5379,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C12" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D12" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -5378,18 +5393,18 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C13" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D13" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -5397,13 +5412,13 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C15" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D15" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -5411,13 +5426,13 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C16" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D16" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -5425,13 +5440,13 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C17" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -5439,13 +5454,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C18" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D18" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -5453,13 +5468,13 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C19" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D19" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -5467,13 +5482,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C20" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D20" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -5481,13 +5496,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C21" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D21" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -5495,13 +5510,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C22" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D22" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -5509,13 +5524,13 @@
         <v>9</v>
       </c>
       <c r="B23" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C23" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D23" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -5523,13 +5538,13 @@
         <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C24" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D24" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -5537,13 +5552,13 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C25" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D25" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -5551,13 +5566,13 @@
         <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C26" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D26" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -5565,13 +5580,13 @@
         <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>461</v>
+        <v>650</v>
       </c>
       <c r="C27" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D27" t="s">
-        <v>473</v>
+        <v>651</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -5579,13 +5594,13 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C28" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D28" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -5593,13 +5608,27 @@
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="C29" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D29" t="s">
-        <v>474</v>
+        <v>470</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>460</v>
+      </c>
+      <c r="C30" t="s">
+        <v>401</v>
+      </c>
+      <c r="D30" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5782,7 +5811,7 @@
         <v>193</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5977,7 +6006,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6095,21 +6124,21 @@
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="10"/>
       <c r="B1" s="11" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -6117,21 +6146,21 @@
         <v>46148</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="16" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="17"/>
       <c r="B4" s="18" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="20" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -6139,123 +6168,123 @@
         <v>46149</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="17"/>
       <c r="B6" s="18" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="23" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="18"/>
       <c r="B7" s="18" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="20" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="18"/>
       <c r="B8" s="18" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="24" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="18"/>
       <c r="B9" s="18" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="24" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="18"/>
       <c r="B10" s="18" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="24" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A11" s="18"/>
       <c r="B11" s="25" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C11" s="19"/>
       <c r="D11" s="24" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="10" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="26" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="10"/>
       <c r="B13" s="10" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="26" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="10"/>
       <c r="B14" s="10" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="26" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="10"/>
       <c r="B15" s="10" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="C15" s="27"/>
       <c r="D15" s="28" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="10"/>
       <c r="B16" s="10" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -6263,133 +6292,133 @@
         <v>46150</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="10"/>
       <c r="B18" s="10" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="C18" s="33"/>
       <c r="D18" s="30" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="10"/>
       <c r="B19" s="34" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C19" s="10"/>
       <c r="D19" s="35" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10"/>
       <c r="B20" s="36" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C20" s="37"/>
       <c r="D20" s="38" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="10"/>
       <c r="B21" s="39" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="C21" s="37"/>
       <c r="D21" s="38" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="10"/>
       <c r="B22" s="10" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="C22" s="10"/>
       <c r="D22" s="40" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="10"/>
       <c r="B23" s="10" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="40" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="10"/>
       <c r="B24" s="10" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="40" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="10"/>
       <c r="B25" s="10" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="40" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
       <c r="A26" s="10"/>
       <c r="B26" s="41" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C26" s="10"/>
       <c r="D26" s="26" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="10"/>
       <c r="B27" s="10" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C27" s="10"/>
       <c r="D27" s="40" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="10"/>
       <c r="B28" s="10" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C28" s="10"/>
       <c r="D28" s="26" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="10"/>
       <c r="B29" s="10" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="C29" s="10"/>
       <c r="D29" s="26" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -6399,7 +6428,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE4A1D8B-6AAB-48EA-AC2A-7DED15787E74}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="1.75" bestFit="1" customWidth="1"/>
@@ -6410,16 +6439,16 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="45"/>
       <c r="B1" s="45" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="44"/>
       <c r="B2" s="47" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C2" s="48"/>
     </row>
@@ -6428,10 +6457,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -6439,7 +6468,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>182</v>
@@ -6450,10 +6479,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -6461,65 +6490,76 @@
         <v>4</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>618</v>
+        <v>641</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="44">
+        <v>5</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>613</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="44">
         <v>6</v>
       </c>
-      <c r="B9" s="44" t="s">
+      <c r="B10" s="44" t="s">
+        <v>609</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>614</v>
       </c>
-      <c r="C9" s="45" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="45">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="45">
         <v>7</v>
       </c>
-      <c r="B10" s="44" t="s">
-        <v>620</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="50">
+      <c r="B11" s="44" t="s">
+        <v>615</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="50">
         <v>8</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>622</v>
-      </c>
-      <c r="C11" s="50" t="s">
-        <v>623</v>
+      <c r="B12" s="50" t="s">
+        <v>617</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>

--- a/website_data.xlsx
+++ b/website_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://crwindia-my.sharepoint.com/personal/fin_crwi_org_in/Documents/Jomit_clean/crwisymposium/crwisymposium-new7-4-26/crwisymposium-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="356" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF851A88-4849-4BA3-88D0-CD74A7DFE102}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="13_ncr:1_{43A54E2A-C15B-4049-9416-409D91501929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8143177-6154-4782-9AE1-8D430DA04FE1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="9" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="747" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Global_Settings" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="959" uniqueCount="661">
   <si>
     <t>Setting_Key</t>
   </si>
@@ -547,9 +547,6 @@
     <t>Congregation</t>
   </si>
   <si>
-    <t>Dr. Sr. Aruna Jose CHF</t>
-  </si>
-  <si>
     <t>Vice President</t>
   </si>
   <si>
@@ -595,9 +592,6 @@
     <t>images/Council/Dr. D.J. Margaret.jpg</t>
   </si>
   <si>
-    <t>Dr. Sr. Sheela Nicholas SAB</t>
-  </si>
-  <si>
     <t>Sisters of St. Anne</t>
   </si>
   <si>
@@ -1225,9 +1219,6 @@
     <t>/images/Hero/Hero.jpg</t>
   </si>
   <si>
-    <t>Br. Santhosh P J</t>
-  </si>
-  <si>
     <t>Ms. Sabrina Wong</t>
   </si>
   <si>
@@ -1243,9 +1234,6 @@
     <t>Cardinal, Metropolitan Archbishop of Hyderabad</t>
   </si>
   <si>
-    <t>Rev. Dr. Mathew Koikkal</t>
-  </si>
-  <si>
     <t>Deputy Secretary General Of The CBCI</t>
   </si>
   <si>
@@ -1297,18 +1285,6 @@
     <t>Mr. Abey Jose</t>
   </si>
   <si>
-    <t xml:space="preserve">Mr. Pavil </t>
-  </si>
-  <si>
-    <t>Mr. Jomit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRWI Staff - </t>
-  </si>
-  <si>
-    <t>CRWI Trustee</t>
-  </si>
-  <si>
     <t>CRWI Staff</t>
   </si>
   <si>
@@ -1336,9 +1312,6 @@
     <t>images/Speakers/Most Rev. Elias Gonsalves.png</t>
   </si>
   <si>
-    <t>Executive director at CARA</t>
-  </si>
-  <si>
     <t>images/Speakers/Thomas P. Gaunt.webp</t>
   </si>
   <si>
@@ -1465,33 +1438,12 @@
     <t>images/Volunteers/Jomit.jpeg</t>
   </si>
   <si>
-    <t>Sr. Jenita Mary</t>
-  </si>
-  <si>
-    <t>Sr. Biji Mathew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Ragina </t>
-  </si>
-  <si>
-    <t>Sr. Anthony Rani</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mr. Sanjay KS </t>
   </si>
   <si>
     <t>Mrs. Sowmya</t>
   </si>
   <si>
-    <t>Sr. Angela Bey</t>
-  </si>
-  <si>
-    <t>Sr. Banpynsuk</t>
-  </si>
-  <si>
-    <t>Sr. Praveena M N</t>
-  </si>
-  <si>
     <t>Ms. Riya C V</t>
   </si>
   <si>
@@ -1531,18 +1483,9 @@
     <t>images/Volunteers/Sr. Piholi Leena.jpeg</t>
   </si>
   <si>
-    <t>Sr. Piholi Leena</t>
-  </si>
-  <si>
     <t>images/Volunteers/Sr.Simera G Momin.jpeg</t>
   </si>
   <si>
-    <t>Sr. Simera G Momin</t>
-  </si>
-  <si>
-    <t>Sr. Eusebia Rynshon</t>
-  </si>
-  <si>
     <t>images/Volunteers/Sr.Eusebia Rynshon.jpeg</t>
   </si>
   <si>
@@ -1555,21 +1498,12 @@
     <t>CHRIST (Deemed to be University), Central Campus,Dharmaram College Post, Hosur Road, Bengaluru - 560029, Karnataka, India</t>
   </si>
   <si>
-    <t>Sr. Juli mate</t>
-  </si>
-  <si>
     <t>images/Volunteers/Sr. Juli mate.jpeg</t>
   </si>
   <si>
-    <t>Mr. Arun</t>
-  </si>
-  <si>
     <t>images/Volunteers/Arun.jpeg</t>
   </si>
   <si>
-    <t>images/Volunteers/Sr, Grecy.jpeg</t>
-  </si>
-  <si>
     <t>Fr. V. Antony Bhyju, CMF, is a Claretian Missionary with wide experience in initial and ongoing formation, currently serving at the General Curia in Rome as Assistant to the General Consultors for Formation and Spirituality.</t>
   </si>
   <si>
@@ -1609,16 +1543,7 @@
     <t>Fr. Jerin Peter Palatty is a philosopher‑theologian and priest, serving as Head of the Department of Philosophy at Kristu Jyoti College, Bangalore, with advanced studies from Dharmaram Vidya Kshetram and the Pontifical Gregorian University, Rome, and is a published author in philosophy, theology, and spirituality.</t>
   </si>
   <si>
-    <t xml:space="preserve">Research Associate CARA, Vietnam  </t>
-  </si>
-  <si>
     <t>Sr. Dr. Alphonsa K. K.</t>
-  </si>
-  <si>
-    <t>Research Associate</t>
-  </si>
-  <si>
-    <t>images/Speakers/Bibina.jpg</t>
   </si>
   <si>
     <t>Dr. Fr. Joye James</t>
@@ -1652,48 +1577,21 @@
     <t>Chief Guest - Inaugural Function</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr. DJ Margaret </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Maria Nirmalini </t>
-  </si>
-  <si>
     <t>Most Rev. Johannes Gorantla</t>
   </si>
   <si>
     <t>Executive Council CRWI</t>
   </si>
   <si>
-    <t>Sr. Molly Attully</t>
-  </si>
-  <si>
     <t>Mother General - CCR</t>
   </si>
   <si>
-    <t>Guest of Honor</t>
-  </si>
-  <si>
-    <t>Sr. Sheela Nicholas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Dr. Jane Wakahiu  </t>
-  </si>
-  <si>
     <t>Fr. Dr. Thomas P. Gaunt, SJ.</t>
   </si>
   <si>
-    <t>Sr.Dr.  Thu T. Do</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Dr.Candida   Mukundi </t>
-  </si>
-  <si>
     <t>Sr. Dr. Bibiana Munini Ngundo</t>
   </si>
   <si>
-    <t>Fr. Dr Luis Fernando Falcó, MsPs.</t>
-  </si>
-  <si>
     <t>Sr. Dr. Jincy Maria</t>
   </si>
   <si>
@@ -1709,16 +1607,7 @@
     <t>Sr. Dr. Helen Mary</t>
   </si>
   <si>
-    <t>Sr.Stella Zimik</t>
-  </si>
-  <si>
-    <t>Fr.Dr. Varghese K J</t>
-  </si>
-  <si>
     <t>images/Volunteers/Sr.Stella Zimik.jpeg</t>
-  </si>
-  <si>
-    <t>Sr. Grecy Lily</t>
   </si>
   <si>
     <t>images/Speakers/Most Rev. Johannes Gorantla.jpeg</t>
@@ -1897,9 +1786,6 @@
     <t>C.Ss.R.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dr. Fr. Jerin </t>
-  </si>
-  <si>
     <t>SDB</t>
   </si>
   <si>
@@ -2015,15 +1901,6 @@
     <t>images/Speakers/Fr.Saju.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Fr. Saju Chackalackal </t>
-  </si>
-  <si>
-    <t>Excecutive Director CERRA</t>
-  </si>
-  <si>
-    <t>Dr. D.J. Margaret FMA</t>
-  </si>
-  <si>
     <t>Sr. Celine Fathima SSAM</t>
   </si>
   <si>
@@ -2057,18 +1934,12 @@
     <t xml:space="preserve">The Treasure Model for Mental Health and Holistic Wellbeing of Women Religious in India </t>
   </si>
   <si>
-    <t>Fr. Dr. Joseph C C</t>
-  </si>
-  <si>
     <t>Vice Chancellor, Christ</t>
   </si>
   <si>
     <t>images/Speakers/Fr. Jseph.jpg</t>
   </si>
   <si>
-    <t>Sr. Maneesha</t>
-  </si>
-  <si>
     <t>images/Volunteers/Sr. Maneesha.jpeg</t>
   </si>
   <si>
@@ -2076,6 +1947,156 @@
   </si>
   <si>
     <t>images/Speakers/Sr. Nirmalini.png</t>
+  </si>
+  <si>
+    <t>Sr. Biji Mathew MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Praveena M N FMA</t>
+  </si>
+  <si>
+    <t>Sr. Ragina  SMMI</t>
+  </si>
+  <si>
+    <t>Sr. Anthony Rani PHJC</t>
+  </si>
+  <si>
+    <t>Sr. Piholi Leena MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Angela Bey MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Banpynsuk MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Simera G Momin MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Eusebia Rynshon MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Juli mate MSMHC</t>
+  </si>
+  <si>
+    <t>Sr.Stella Zimik MSMHC</t>
+  </si>
+  <si>
+    <t>Sr. Maneesha AC</t>
+  </si>
+  <si>
+    <t>Sr. Jenita Mary AC</t>
+  </si>
+  <si>
+    <t>Research Consultant</t>
+  </si>
+  <si>
+    <t>Lead Researcher</t>
+  </si>
+  <si>
+    <t>Research Co-ordinator</t>
+  </si>
+  <si>
+    <t>MIS Co-ordinator</t>
+  </si>
+  <si>
+    <t>Data and Communication</t>
+  </si>
+  <si>
+    <t>Accountant</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Fr.(Dr.) Paul Pudussery CSC</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Doris D Souza AC</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Mary Paul FCC</t>
+  </si>
+  <si>
+    <t>Sr. Vijo Arul Selvi CFMSS</t>
+  </si>
+  <si>
+    <t>Mr. Jomit Mathew</t>
+  </si>
+  <si>
+    <t>Mr. Arun Joji</t>
+  </si>
+  <si>
+    <t>Mr. Pavil Nithin R</t>
+  </si>
+  <si>
+    <t>Media Co-ordinator</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Jane Wakahiu  LSOSF</t>
+  </si>
+  <si>
+    <t>Sr.Dr.  Thu T. Do LHC</t>
+  </si>
+  <si>
+    <t>Sr. Dr.Candida   Mukundi  ASN</t>
+  </si>
+  <si>
+    <t>Fr. Saju Chackalackal CMI</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Joseph C C CMI</t>
+  </si>
+  <si>
+    <t>Fr. Dr. Varghese K J CMI</t>
+  </si>
+  <si>
+    <t>Sr. DJ Margaret FMA</t>
+  </si>
+  <si>
+    <t>Sr. Molly Attully CCR</t>
+  </si>
+  <si>
+    <t>Sr. Sheela Nicholas SAB</t>
+  </si>
+  <si>
+    <t>Br. Santhosh P J CSC</t>
+  </si>
+  <si>
+    <t>Rev. Dr. Mathew Koyickal</t>
+  </si>
+  <si>
+    <t>Guest of Honour</t>
+  </si>
+  <si>
+    <t>Fr. Jerin Peter</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Sheela Nicholas SAB</t>
+  </si>
+  <si>
+    <t>Sr. Dr. Aruna Jose CHF</t>
+  </si>
+  <si>
+    <t>Sr. Dr. D.J. Margaret FMA</t>
+  </si>
+  <si>
+    <t>images/Speakers/Bibiana.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Associate CARA, USA  </t>
+  </si>
+  <si>
+    <t>Executive director at CARA, USA</t>
+  </si>
+  <si>
+    <t>Excecutive Director CERRA - Africa</t>
+  </si>
+  <si>
+    <t>Research Associate CERRA - Africa</t>
+  </si>
+  <si>
+    <t>Fr. Dr Luis Fernando Falcó, MSpS.</t>
   </si>
 </sst>
 </file>
@@ -2085,7 +2106,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2127,12 +2148,6 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
@@ -2322,7 +2337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2338,117 +2353,111 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="18" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="18" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="18" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="18" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2942,7 +2951,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
@@ -2953,7 +2962,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -2975,13 +2984,13 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>0</v>
@@ -2990,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="N9" t="s">
         <v>19</v>
@@ -2998,36 +3007,36 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="C10" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="D10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E10" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="H10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I10" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="H11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I11" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -3035,19 +3044,19 @@
         <v>0</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E12" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="H12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="I12" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -3055,186 +3064,186 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B14" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C14" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C15" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C16" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B17" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C17" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B18" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B19" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B20" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B21" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C21" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B22" t="s">
-        <v>643</v>
+        <v>602</v>
       </c>
       <c r="C22" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B23" t="s">
-        <v>644</v>
+        <v>603</v>
       </c>
       <c r="C23" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B24" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C24" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B25" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B26" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C26" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B28" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="C28" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="C29" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -3251,6 +3260,9 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3329,7 +3341,7 @@
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="38.25" customWidth="1"/>
+    <col min="2" max="2" width="25.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.75" customWidth="1"/>
     <col min="4" max="4" width="27.83203125" customWidth="1"/>
     <col min="486" max="486" width="2.1640625" customWidth="1"/>
@@ -3357,84 +3369,84 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2" t="s">
         <v>373</v>
       </c>
-      <c r="C2" t="s">
-        <v>376</v>
-      </c>
       <c r="D2" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
       <c r="E2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>374</v>
+      <c r="B3" t="s">
+        <v>371</v>
       </c>
       <c r="C3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D3" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="E3" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>405</v>
+      <c r="B4" t="s">
+        <v>397</v>
       </c>
       <c r="C4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>510</v>
+        <v>485</v>
       </c>
       <c r="E4" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>515</v>
+      <c r="B5" t="s">
+        <v>488</v>
       </c>
       <c r="C5" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="E5" t="s">
-        <v>536</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>377</v>
+      <c r="B6" t="s">
+        <v>649</v>
       </c>
       <c r="C6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E6" t="s">
         <v>378</v>
-      </c>
-      <c r="D6" t="s">
-        <v>509</v>
-      </c>
-      <c r="E6" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -3442,16 +3454,16 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>514</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="D7" t="s">
-        <v>537</v>
+        <v>500</v>
       </c>
       <c r="E7" t="s">
-        <v>653</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -3459,16 +3471,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="C8" t="s">
-        <v>648</v>
+        <v>606</v>
       </c>
       <c r="D8" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E8" t="s">
-        <v>649</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -3476,67 +3488,67 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="C9" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E9" t="s">
-        <v>632</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>533</v>
+        <v>644</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D10" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E10" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B11" t="s">
-        <v>513</v>
+        <v>645</v>
       </c>
       <c r="C11" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="D11" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>517</v>
+        <v>646</v>
       </c>
       <c r="C12" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
       <c r="D12" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E12" t="s">
-        <v>538</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -3544,16 +3556,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>520</v>
+        <v>647</v>
       </c>
       <c r="C13" t="s">
-        <v>516</v>
+        <v>489</v>
       </c>
       <c r="D13" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -3561,20 +3573,20 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>371</v>
+        <v>648</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="D14" t="s">
-        <v>519</v>
+        <v>650</v>
       </c>
       <c r="E14" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -3590,7 +3602,7 @@
   <cols>
     <col min="1" max="1" width="2.58203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.08203125" customWidth="1"/>
-    <col min="3" max="3" width="19.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="62.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -3615,13 +3627,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>521</v>
+        <v>639</v>
       </c>
       <c r="C2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3629,13 +3641,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C3" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -3643,13 +3655,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" t="s">
         <v>386</v>
-      </c>
-      <c r="C4" t="s">
-        <v>387</v>
-      </c>
-      <c r="E4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -3657,69 +3669,69 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>522</v>
+        <v>491</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>657</v>
       </c>
       <c r="E5" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="43" t="s">
-        <v>523</v>
+      <c r="B6" s="41" t="s">
+        <v>640</v>
       </c>
       <c r="C6" t="s">
-        <v>499</v>
+        <v>656</v>
       </c>
       <c r="E6" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="43" t="s">
-        <v>524</v>
+      <c r="B7" s="41" t="s">
+        <v>641</v>
       </c>
       <c r="C7" t="s">
-        <v>634</v>
+        <v>658</v>
       </c>
       <c r="E7" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="42" t="s">
-        <v>525</v>
+      <c r="B8" s="40" t="s">
+        <v>492</v>
       </c>
       <c r="C8" t="s">
-        <v>501</v>
+        <v>659</v>
       </c>
       <c r="E8" t="s">
-        <v>502</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>526</v>
+      <c r="B9" s="40" t="s">
+        <v>660</v>
       </c>
       <c r="C9" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E9" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -3727,13 +3739,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>638</v>
+        <v>597</v>
       </c>
       <c r="C10" t="s">
-        <v>640</v>
+        <v>599</v>
       </c>
       <c r="E10" t="s">
-        <v>639</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -3753,7 +3765,7 @@
     <col min="4" max="4" width="31.08203125" customWidth="1"/>
     <col min="5" max="5" width="23.25" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
-    <col min="7" max="7" width="63.33203125" style="52" customWidth="1"/>
+    <col min="7" max="7" width="63.33203125" style="50" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
     <col min="9" max="9" width="44.1640625" customWidth="1"/>
   </cols>
@@ -3777,11 +3789,11 @@
       <c r="F1" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="50" t="s">
         <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3789,25 +3801,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>594</v>
+        <v>651</v>
       </c>
       <c r="C2" t="s">
-        <v>595</v>
+        <v>557</v>
       </c>
       <c r="D2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E2" t="s">
         <v>88</v>
       </c>
       <c r="F2" t="s">
-        <v>444</v>
-      </c>
-      <c r="G2" s="52" t="s">
-        <v>498</v>
+        <v>435</v>
+      </c>
+      <c r="G2" s="50" t="s">
+        <v>476</v>
       </c>
       <c r="H2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -3815,25 +3827,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="C3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" t="s">
         <v>202</v>
-      </c>
-      <c r="D3" t="s">
-        <v>204</v>
       </c>
       <c r="E3" t="s">
         <v>88</v>
       </c>
       <c r="F3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G3" s="52" t="s">
-        <v>250</v>
+        <v>289</v>
+      </c>
+      <c r="G3" s="50" t="s">
+        <v>248</v>
       </c>
       <c r="H3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3841,25 +3853,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="C4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E4" t="s">
         <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>292</v>
-      </c>
-      <c r="G4" s="52" t="s">
-        <v>497</v>
+        <v>290</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>475</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3867,25 +3879,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>599</v>
+        <v>561</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E5" t="s">
         <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>295</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>486</v>
+        <v>293</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>464</v>
       </c>
       <c r="H5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3893,25 +3905,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C6" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E6" t="s">
         <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
-      </c>
-      <c r="G6" s="52" t="s">
-        <v>251</v>
+        <v>263</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>249</v>
       </c>
       <c r="H6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -3919,25 +3931,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D7" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
       <c r="E7" t="s">
         <v>88</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>505</v>
+        <v>262</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>480</v>
       </c>
       <c r="H7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3945,51 +3957,51 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C8" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D8" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="E8" t="s">
         <v>88</v>
       </c>
       <c r="F8" t="s">
-        <v>423</v>
-      </c>
-      <c r="G8" s="52" t="s">
-        <v>493</v>
+        <v>414</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>471</v>
       </c>
       <c r="H8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>528</v>
+      <c r="B9" s="7" t="s">
+        <v>494</v>
       </c>
       <c r="C9" t="s">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="D9" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E9" t="s">
         <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>591</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>592</v>
+        <v>554</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>555</v>
       </c>
       <c r="H9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -3997,25 +4009,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>598</v>
+        <v>560</v>
       </c>
       <c r="C10" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D10" t="s">
-        <v>646</v>
+        <v>605</v>
       </c>
       <c r="E10" t="s">
         <v>94</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
-      </c>
-      <c r="G10" s="52" t="s">
-        <v>491</v>
+        <v>273</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>469</v>
       </c>
       <c r="H10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4023,25 +4035,25 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>620</v>
+        <v>582</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E11" t="s">
         <v>94</v>
       </c>
       <c r="F11" t="s">
-        <v>404</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>257</v>
+        <v>396</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>255</v>
       </c>
       <c r="H11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4049,25 +4061,25 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D12" t="s">
-        <v>645</v>
+        <v>604</v>
       </c>
       <c r="E12" t="s">
         <v>94</v>
       </c>
       <c r="F12" t="s">
-        <v>277</v>
-      </c>
-      <c r="G12" s="52" t="s">
-        <v>490</v>
+        <v>275</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>468</v>
       </c>
       <c r="H12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4075,51 +4087,51 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C13" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="D13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s">
         <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>258</v>
+        <v>277</v>
+      </c>
+      <c r="G13" s="50" t="s">
+        <v>256</v>
       </c>
       <c r="H13" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>630</v>
+      <c r="B14" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="C14" t="s">
-        <v>629</v>
+        <v>591</v>
       </c>
       <c r="D14" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E14" t="s">
         <v>104</v>
       </c>
       <c r="F14" t="s">
-        <v>627</v>
-      </c>
-      <c r="G14" s="52" t="s">
-        <v>628</v>
+        <v>589</v>
+      </c>
+      <c r="G14" s="50" t="s">
+        <v>590</v>
       </c>
       <c r="H14" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4127,25 +4139,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>622</v>
+        <v>584</v>
       </c>
       <c r="C15" t="s">
-        <v>621</v>
+        <v>583</v>
       </c>
       <c r="D15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E15" t="s">
         <v>104</v>
       </c>
       <c r="F15" t="s">
-        <v>287</v>
-      </c>
-      <c r="G15" s="52" t="s">
-        <v>262</v>
+        <v>285</v>
+      </c>
+      <c r="G15" s="50" t="s">
+        <v>260</v>
       </c>
       <c r="H15" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4153,25 +4165,25 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" t="s">
+        <v>244</v>
+      </c>
+      <c r="D16" t="s">
         <v>311</v>
-      </c>
-      <c r="C16" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" t="s">
-        <v>313</v>
       </c>
       <c r="E16" t="s">
         <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>286</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>249</v>
+        <v>284</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>247</v>
       </c>
       <c r="H16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="93" x14ac:dyDescent="0.35">
@@ -4179,25 +4191,25 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D17" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s">
         <v>104</v>
       </c>
       <c r="F17" t="s">
-        <v>289</v>
-      </c>
-      <c r="G17" s="52" t="s">
-        <v>487</v>
+        <v>287</v>
+      </c>
+      <c r="G17" s="50" t="s">
+        <v>465</v>
       </c>
       <c r="H17" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4205,25 +4217,25 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" t="s">
         <v>245</v>
       </c>
-      <c r="C18" t="s">
-        <v>247</v>
-      </c>
       <c r="D18" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E18" t="s">
         <v>104</v>
       </c>
       <c r="F18" t="s">
-        <v>290</v>
-      </c>
-      <c r="G18" s="52" t="s">
-        <v>294</v>
+        <v>288</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>292</v>
       </c>
       <c r="H18" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4231,25 +4243,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="C19" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E19" t="s">
         <v>91</v>
       </c>
       <c r="F19" t="s">
-        <v>445</v>
-      </c>
-      <c r="G19" s="52" t="s">
-        <v>494</v>
+        <v>436</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>472</v>
       </c>
       <c r="H19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4257,25 +4269,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E20" t="s">
         <v>91</v>
       </c>
       <c r="F20" t="s">
-        <v>652</v>
-      </c>
-      <c r="G20" s="52" t="s">
-        <v>492</v>
+        <v>609</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>470</v>
       </c>
       <c r="H20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4283,51 +4295,51 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="C21" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="D21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
       </c>
       <c r="F21" t="s">
-        <v>271</v>
-      </c>
-      <c r="G21" s="52" t="s">
-        <v>254</v>
+        <v>269</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>252</v>
       </c>
       <c r="H21" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="9" t="s">
-        <v>597</v>
+      <c r="B22" s="7" t="s">
+        <v>559</v>
       </c>
       <c r="C22" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D22" t="s">
-        <v>320</v>
-      </c>
-      <c r="E22" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>91</v>
       </c>
       <c r="F22" t="s">
-        <v>504</v>
-      </c>
-      <c r="G22" s="52" t="s">
-        <v>596</v>
+        <v>479</v>
+      </c>
+      <c r="G22" s="50" t="s">
+        <v>558</v>
       </c>
       <c r="H22" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4335,25 +4347,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C23" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D23" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E23" t="s">
         <v>91</v>
       </c>
       <c r="F23" t="s">
-        <v>274</v>
-      </c>
-      <c r="G23" s="52" t="s">
-        <v>256</v>
+        <v>272</v>
+      </c>
+      <c r="G23" s="50" t="s">
+        <v>254</v>
       </c>
       <c r="H23" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4361,25 +4373,25 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="C24" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D24" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E24" t="s">
         <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>272</v>
-      </c>
-      <c r="G24" s="52" t="s">
-        <v>437</v>
+        <v>270</v>
+      </c>
+      <c r="G24" s="50" t="s">
+        <v>428</v>
       </c>
       <c r="H24" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4387,51 +4399,51 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="D25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E25" t="s">
         <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>273</v>
-      </c>
-      <c r="G25" s="52" t="s">
-        <v>255</v>
+        <v>271</v>
+      </c>
+      <c r="G25" s="50" t="s">
+        <v>253</v>
       </c>
       <c r="H25" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="9" t="s">
-        <v>503</v>
+      <c r="B26" s="7" t="s">
+        <v>478</v>
       </c>
       <c r="C26" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D26" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E26" t="s">
         <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>446</v>
-      </c>
-      <c r="G26" s="52" t="s">
-        <v>495</v>
+        <v>437</v>
+      </c>
+      <c r="G26" s="50" t="s">
+        <v>473</v>
       </c>
       <c r="H26" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4439,25 +4451,25 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C27" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E27" t="s">
         <v>100</v>
       </c>
       <c r="F27" t="s">
-        <v>280</v>
-      </c>
-      <c r="G27" s="52" t="s">
-        <v>259</v>
+        <v>278</v>
+      </c>
+      <c r="G27" s="50" t="s">
+        <v>257</v>
       </c>
       <c r="H27" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4465,25 +4477,25 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D28" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E28" t="s">
         <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>471</v>
-      </c>
-      <c r="G28" s="52" t="s">
-        <v>489</v>
+        <v>455</v>
+      </c>
+      <c r="G28" s="50" t="s">
+        <v>467</v>
       </c>
       <c r="H28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4491,25 +4503,25 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>529</v>
+        <v>495</v>
       </c>
       <c r="C29" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E29" t="s">
         <v>100</v>
       </c>
       <c r="F29" t="s">
-        <v>403</v>
-      </c>
-      <c r="G29" s="52" t="s">
-        <v>260</v>
+        <v>395</v>
+      </c>
+      <c r="G29" s="50" t="s">
+        <v>258</v>
       </c>
       <c r="H29" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4517,25 +4529,25 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D30" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E30" t="s">
         <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>285</v>
-      </c>
-      <c r="G30" s="52" t="s">
-        <v>261</v>
+        <v>283</v>
+      </c>
+      <c r="G30" s="50" t="s">
+        <v>259</v>
       </c>
       <c r="H30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4543,25 +4555,25 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="C31" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D31" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E31" t="s">
         <v>100</v>
       </c>
       <c r="F31" t="s">
-        <v>284</v>
-      </c>
-      <c r="G31" s="52" t="s">
-        <v>488</v>
+        <v>282</v>
+      </c>
+      <c r="G31" s="50" t="s">
+        <v>466</v>
       </c>
       <c r="H31" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
@@ -4569,25 +4581,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D32" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E32" t="s">
         <v>100</v>
       </c>
       <c r="F32" t="s">
-        <v>281</v>
-      </c>
-      <c r="G32" s="52" t="s">
+        <v>279</v>
+      </c>
+      <c r="G32" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H32" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="77.5" x14ac:dyDescent="0.35">
@@ -4595,25 +4607,25 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>623</v>
+        <v>585</v>
       </c>
       <c r="C33" t="s">
-        <v>624</v>
+        <v>586</v>
       </c>
       <c r="D33" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>631</v>
-      </c>
-      <c r="G33" s="52" t="s">
-        <v>625</v>
+        <v>593</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>587</v>
       </c>
       <c r="H33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4621,25 +4633,25 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="C34" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D34" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E34" t="s">
         <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>293</v>
-      </c>
-      <c r="G34" s="52" t="s">
-        <v>626</v>
+        <v>291</v>
+      </c>
+      <c r="G34" s="50" t="s">
+        <v>588</v>
       </c>
       <c r="H34" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4647,25 +4659,25 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="C35" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E35" t="s">
         <v>97</v>
       </c>
       <c r="F35" t="s">
-        <v>270</v>
-      </c>
-      <c r="G35" s="52" t="s">
-        <v>253</v>
+        <v>268</v>
+      </c>
+      <c r="G35" s="50" t="s">
+        <v>251</v>
       </c>
       <c r="H35" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4673,25 +4685,25 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>207</v>
+      </c>
+      <c r="C36" t="s">
+        <v>417</v>
+      </c>
+      <c r="D36" t="s">
         <v>209</v>
-      </c>
-      <c r="C36" t="s">
-        <v>426</v>
-      </c>
-      <c r="D36" t="s">
-        <v>211</v>
       </c>
       <c r="E36" t="s">
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>268</v>
-      </c>
-      <c r="G36" s="52" t="s">
-        <v>253</v>
+        <v>266</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>251</v>
       </c>
       <c r="H36" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4699,25 +4711,25 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C37" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E37" t="s">
         <v>97</v>
       </c>
       <c r="F37" t="s">
-        <v>266</v>
-      </c>
-      <c r="G37" s="52" t="s">
-        <v>252</v>
+        <v>264</v>
+      </c>
+      <c r="G37" s="50" t="s">
+        <v>250</v>
       </c>
       <c r="H37" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="62" x14ac:dyDescent="0.35">
@@ -4725,25 +4737,25 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>600</v>
+        <v>562</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E38" t="s">
         <v>97</v>
       </c>
       <c r="F38" t="s">
-        <v>267</v>
-      </c>
-      <c r="G38" s="52" t="s">
-        <v>496</v>
+        <v>265</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>474</v>
       </c>
       <c r="H38" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
@@ -4757,42 +4769,42 @@
         <v>133</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F39" t="s">
-        <v>263</v>
-      </c>
-      <c r="G39" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="G39" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H39" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="3">
         <v>39</v>
       </c>
-      <c r="B40" s="51" t="s">
-        <v>310</v>
+      <c r="B40" s="49" t="s">
+        <v>308</v>
       </c>
       <c r="C40" t="s">
         <v>133</v>
       </c>
       <c r="D40" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E40" t="s">
         <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>269</v>
-      </c>
-      <c r="G40" s="52" t="s">
+        <v>267</v>
+      </c>
+      <c r="G40" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H40" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4800,111 +4812,111 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E41" t="s">
         <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>276</v>
-      </c>
-      <c r="G41" s="52" t="s">
+        <v>274</v>
+      </c>
+      <c r="G41" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A42" s="3">
         <v>41</v>
       </c>
-      <c r="B42" s="51" t="s">
-        <v>310</v>
+      <c r="B42" s="49" t="s">
+        <v>308</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F42" t="s">
-        <v>278</v>
-      </c>
-      <c r="G42" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="G42" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H42" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="3">
         <v>42</v>
       </c>
-      <c r="B43" s="51" t="s">
-        <v>310</v>
+      <c r="B43" s="49" t="s">
+        <v>308</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F43" t="s">
-        <v>282</v>
-      </c>
-      <c r="G43" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="G43" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H43" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="3">
         <v>43</v>
       </c>
-      <c r="B44" s="51" t="s">
-        <v>310</v>
+      <c r="B44" s="49" t="s">
+        <v>308</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>283</v>
-      </c>
-      <c r="G44" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="G44" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="3">
         <v>44</v>
       </c>
-      <c r="B45" s="51" t="s">
-        <v>310</v>
+      <c r="B45" s="49" t="s">
+        <v>308</v>
       </c>
       <c r="C45" t="s">
         <v>133</v>
       </c>
       <c r="D45" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F45" t="s">
-        <v>288</v>
-      </c>
-      <c r="G45" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="G45" s="50" t="s">
         <v>133</v>
       </c>
       <c r="H45" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -5001,16 +5013,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C2" t="s">
         <v>145</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>146</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>147</v>
-      </c>
-      <c r="E2" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5018,16 +5030,16 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>637</v>
+        <v>596</v>
       </c>
       <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
         <v>149</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>150</v>
-      </c>
-      <c r="E3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5035,16 +5047,16 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>636</v>
+        <v>595</v>
       </c>
       <c r="C4" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" t="s">
         <v>152</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>153</v>
-      </c>
-      <c r="E4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5052,16 +5064,16 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
         <v>155</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>156</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>157</v>
-      </c>
-      <c r="E5" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5069,16 +5081,16 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E6" t="s">
         <v>159</v>
-      </c>
-      <c r="E6" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5086,23 +5098,23 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
+        <v>652</v>
+      </c>
+      <c r="C7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E7" t="s">
         <v>161</v>
-      </c>
-      <c r="C7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="11" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E2 A7:E7 A6 C6:E6 A5:E5 A4 C4:E4 A3 C3:E3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 A7 A6 C6:E6 A5:E5 A4 C4:E4 A3 C3:E3 C7:E7 A2 C2:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5134,13 +5146,13 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5148,13 +5160,13 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -5162,13 +5174,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5176,13 +5188,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5190,13 +5202,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5204,13 +5216,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -5221,7 +5233,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE87D73C-0C6D-4F11-B208-F394024872E3}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.58203125" style="3"/>
@@ -5245,7 +5257,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -5253,10 +5265,10 @@
         <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>397</v>
+        <v>173</v>
       </c>
       <c r="D3" t="s">
         <v>85</v>
@@ -5267,13 +5279,13 @@
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>632</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>624</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -5281,13 +5293,13 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>631</v>
       </c>
       <c r="C5" t="s">
-        <v>397</v>
+        <v>625</v>
       </c>
       <c r="D5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -5295,13 +5307,13 @@
         <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>178</v>
+        <v>633</v>
       </c>
       <c r="C6" t="s">
-        <v>397</v>
+        <v>626</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -5309,330 +5321,316 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C7" t="s">
+        <v>626</v>
+      </c>
+      <c r="D7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>627</v>
+      </c>
+      <c r="D8" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" t="s">
+        <v>628</v>
+      </c>
+      <c r="D9" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" t="s">
+        <v>637</v>
+      </c>
+      <c r="C10" t="s">
+        <v>638</v>
+      </c>
+      <c r="D10" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B11" t="s">
+        <v>636</v>
+      </c>
+      <c r="C11" t="s">
+        <v>629</v>
+      </c>
+      <c r="D11" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B12" t="s">
+        <v>635</v>
+      </c>
+      <c r="C12" t="s">
+        <v>630</v>
+      </c>
+      <c r="D12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>623</v>
+      </c>
+      <c r="C14" t="s">
         <v>393</v>
       </c>
-      <c r="C7" t="s">
-        <v>397</v>
-      </c>
-      <c r="D7" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>535</v>
-      </c>
-      <c r="C8" t="s">
-        <v>397</v>
-      </c>
-      <c r="D8" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>402</v>
-      </c>
-      <c r="C9" t="s">
-        <v>397</v>
-      </c>
-      <c r="D9" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>394</v>
-      </c>
-      <c r="C10" t="s">
-        <v>397</v>
-      </c>
-      <c r="D10" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>395</v>
-      </c>
-      <c r="C11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D11" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>483</v>
-      </c>
-      <c r="C12" t="s">
-        <v>397</v>
-      </c>
-      <c r="D12" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>396</v>
-      </c>
-      <c r="C13" t="s">
-        <v>397</v>
-      </c>
-      <c r="D13" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>400</v>
+      <c r="D14" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>451</v>
+        <v>611</v>
       </c>
       <c r="C15" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D15" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>452</v>
+        <v>612</v>
       </c>
       <c r="C16" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D16" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>459</v>
+        <v>613</v>
       </c>
       <c r="C17" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D17" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>453</v>
+        <v>614</v>
       </c>
       <c r="C18" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D18" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>454</v>
+        <v>615</v>
       </c>
       <c r="C19" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D19" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>473</v>
+        <v>616</v>
       </c>
       <c r="C20" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D20" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>457</v>
+        <v>617</v>
       </c>
       <c r="C21" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D21" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B22" t="s">
-        <v>458</v>
+        <v>618</v>
       </c>
       <c r="C22" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D22" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>475</v>
+        <v>619</v>
       </c>
       <c r="C23" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D23" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>476</v>
+        <v>620</v>
       </c>
       <c r="C24" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D24" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>481</v>
+        <v>621</v>
       </c>
       <c r="C25" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D25" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>532</v>
+        <v>622</v>
       </c>
       <c r="C26" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D26" t="s">
-        <v>534</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>650</v>
+        <v>443</v>
       </c>
       <c r="C27" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D27" t="s">
-        <v>651</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="C28" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D28" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="C29" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="D29" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="3">
-        <v>16</v>
-      </c>
-      <c r="B30" t="s">
-        <v>460</v>
-      </c>
-      <c r="C30" t="s">
-        <v>401</v>
-      </c>
-      <c r="D30" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -5652,16 +5650,16 @@
         <v>21</v>
       </c>
       <c r="B1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" t="s">
         <v>164</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>165</v>
-      </c>
-      <c r="D1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -5669,16 +5667,16 @@
         <v>28</v>
       </c>
       <c r="B2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" t="s">
         <v>168</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>169</v>
-      </c>
-      <c r="D2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5686,16 +5684,16 @@
         <v>40</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E3" t="s">
         <v>172</v>
-      </c>
-      <c r="D3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5703,13 +5701,13 @@
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
@@ -5720,13 +5718,13 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
         <v>177</v>
-      </c>
-      <c r="C5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" t="s">
-        <v>179</v>
       </c>
       <c r="E5" t="s">
         <v>128</v>
@@ -5737,13 +5735,13 @@
         <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E6" t="s">
         <v>128</v>
@@ -5754,13 +5752,13 @@
         <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
         <v>128</v>
@@ -5768,16 +5766,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" t="s">
         <v>184</v>
       </c>
-      <c r="B8" t="s">
+      <c r="D8" t="s">
         <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>187</v>
       </c>
       <c r="E8" t="s">
         <v>128</v>
@@ -5785,16 +5783,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" t="s">
         <v>188</v>
-      </c>
-      <c r="B9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C9" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" t="s">
-        <v>190</v>
       </c>
       <c r="E9" t="s">
         <v>128</v>
@@ -5802,16 +5800,16 @@
     </row>
     <row r="10" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
         <v>191</v>
       </c>
-      <c r="B10" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" t="s">
-        <v>193</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E10" t="s">
         <v>128</v>
@@ -5819,16 +5817,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" t="s">
         <v>194</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" t="s">
         <v>195</v>
-      </c>
-      <c r="C11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" t="s">
-        <v>197</v>
       </c>
       <c r="E11" t="s">
         <v>128</v>
@@ -6006,7 +6004,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>51</v>
@@ -6093,7 +6091,7 @@
         <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
@@ -6122,303 +6120,303 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="10"/>
-      <c r="B1" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
+        <v>46148</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="15"/>
+      <c r="B4" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="18" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
+        <v>46149</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="21" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="16"/>
+      <c r="B7" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="18" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="22" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="16"/>
+      <c r="B9" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="22" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="16"/>
+      <c r="B10" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="22" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="16"/>
+      <c r="B11" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="22" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="26" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="28" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <v>46150</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>532</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="28" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="8"/>
+      <c r="B19" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="C19" s="8"/>
+      <c r="D19" s="33" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="8"/>
+      <c r="B20" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="36" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="8"/>
+      <c r="B21" s="37" t="s">
+        <v>516</v>
+      </c>
+      <c r="C21" s="35"/>
+      <c r="D21" s="36" t="s">
         <v>539</v>
       </c>
-      <c r="B2" s="12" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12" t="s">
+      <c r="C22" s="8"/>
+      <c r="D22" s="38" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="13">
-        <v>46148</v>
-      </c>
-      <c r="B3" s="14" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="38" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18" t="s">
+      <c r="C24" s="8"/>
+      <c r="D24" s="38" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="C25" s="8"/>
+      <c r="D25" s="38" t="s">
         <v>544</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20" t="s">
+    </row>
+    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
+      <c r="A26" s="8"/>
+      <c r="B26" s="39" t="s">
         <v>545</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="13">
-        <v>46149</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="C26" s="8"/>
+      <c r="D26" s="24" t="s">
         <v>546</v>
       </c>
-      <c r="C5" s="15" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="C27" s="8"/>
+      <c r="D27" s="38" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="23" t="s">
+      <c r="C28" s="8"/>
+      <c r="D28" s="24" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8" t="s">
         <v>551</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20" t="s">
+      <c r="C29" s="8"/>
+      <c r="D29" s="24" t="s">
         <v>552</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="24" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18" t="s">
-        <v>555</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="24" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18" t="s">
-        <v>557</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="24" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="18"/>
-      <c r="B11" s="25" t="s">
-        <v>559</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="24" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10" t="s">
-        <v>561</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="26" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10" t="s">
-        <v>563</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="26" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10" t="s">
-        <v>564</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="26" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10" t="s">
-        <v>565</v>
-      </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10" t="s">
-        <v>567</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
-        <v>46150</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>546</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>569</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10" t="s">
-        <v>549</v>
-      </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="30" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="10"/>
-      <c r="B19" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="35" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="42.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="10"/>
-      <c r="B20" s="36" t="s">
-        <v>574</v>
-      </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="38" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="10"/>
-      <c r="B21" s="39" t="s">
-        <v>553</v>
-      </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="38" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="40" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10" t="s">
-        <v>579</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="40" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10" t="s">
-        <v>580</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="40" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10" t="s">
-        <v>557</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="40" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="31" x14ac:dyDescent="0.35">
-      <c r="A26" s="10"/>
-      <c r="B26" s="41" t="s">
-        <v>582</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="26" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10" t="s">
-        <v>584</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="40" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10" t="s">
-        <v>586</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="26" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10" t="s">
-        <v>588</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="26" t="s">
-        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -6437,129 +6435,129 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="45"/>
-      <c r="B1" s="45" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="43" t="s">
+        <v>563</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="42"/>
+      <c r="B2" s="45" t="s">
+        <v>565</v>
+      </c>
+      <c r="C2" s="46"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="42">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
+      <c r="A4" s="42">
+        <v>2</v>
+      </c>
+      <c r="B4" s="44" t="s">
+        <v>568</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="42">
+        <v>3</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>569</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="42">
+        <v>4</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="42">
+        <v>5</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>573</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="42">
+        <v>6</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="C8" s="42" t="s">
         <v>601</v>
       </c>
-      <c r="C1" s="44" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="44"/>
-      <c r="B2" s="47" t="s">
-        <v>603</v>
-      </c>
-      <c r="C2" s="48"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="44">
-        <v>1</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>604</v>
-      </c>
-      <c r="C3" s="44" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="31" x14ac:dyDescent="0.35">
-      <c r="A4" s="44">
-        <v>2</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>606</v>
-      </c>
-      <c r="C4" s="44" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="44">
-        <v>3</v>
-      </c>
-      <c r="B5" s="44" t="s">
-        <v>607</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="44">
-        <v>4</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>609</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="44">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="42">
         <v>5</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>611</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="44">
+      <c r="B9" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="42">
         <v>6</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>641</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="44">
-        <v>5</v>
-      </c>
-      <c r="B9" s="44" t="s">
-        <v>613</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="44">
-        <v>6</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>609</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>614</v>
+      <c r="B10" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="45">
+      <c r="A11" s="43">
         <v>7</v>
       </c>
-      <c r="B11" s="44" t="s">
-        <v>615</v>
-      </c>
-      <c r="C11" s="44" t="s">
-        <v>616</v>
+      <c r="B11" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="50">
+      <c r="A12" s="48">
         <v>8</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>617</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>618</v>
+      <c r="B12" s="48" t="s">
+        <v>579</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
